--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R2" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,69 +767,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R3" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,71 +890,64 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381486</v>
+        <v>133383841</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635569</v>
+        <v>635692</v>
       </c>
       <c r="R4" t="n">
-        <v>6998651</v>
+        <v>6998659</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,30 +1013,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1272,46 +1266,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133383841</v>
+        <v>133381486</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635692</v>
+        <v>635569</v>
       </c>
       <c r="R7" t="n">
-        <v>6998659</v>
+        <v>6998651</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1362,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1865,32 +1865,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133381503</v>
+        <v>133383857</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635782</v>
+        <v>635848</v>
       </c>
       <c r="R12" t="n">
-        <v>6998397</v>
+        <v>6998513</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,44 +1968,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133383857</v>
+        <v>133381503</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635848</v>
+        <v>635782</v>
       </c>
       <c r="R13" t="n">
-        <v>6998513</v>
+        <v>6998397</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,12 +2083,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2309,48 +2309,60 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133381484</v>
+        <v>133383825</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635574</v>
+        <v>635595</v>
       </c>
       <c r="R16" t="n">
-        <v>6998638</v>
+        <v>6998619</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2391,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2401,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,78 +2410,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383825</v>
+        <v>133381484</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635595</v>
+        <v>635574</v>
       </c>
       <c r="R17" t="n">
-        <v>6998619</v>
+        <v>6998638</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2498,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,29 +2518,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133383823</v>
+        <v>133381505</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,31 +2547,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2579,13 +2574,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635652</v>
+        <v>635742</v>
       </c>
       <c r="R18" t="n">
-        <v>6998555</v>
+        <v>6998412</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,28 +2628,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381501</v>
+        <v>133381480</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,42 +2673,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635890</v>
+        <v>635598</v>
       </c>
       <c r="R19" t="n">
-        <v>6998459</v>
+        <v>6998614</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2729,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,8 +2754,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2766,7 +2788,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381480</v>
+        <v>133381493</v>
       </c>
       <c r="B20" t="n">
         <v>91918</v>
@@ -2804,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635598</v>
+        <v>635756</v>
       </c>
       <c r="R20" t="n">
-        <v>6998614</v>
+        <v>6998647</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2839,7 +2861,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2849,7 +2871,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,10 +2914,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133381493</v>
+        <v>133383823</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,26 +2925,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2930,13 +2957,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635756</v>
+        <v>635652</v>
       </c>
       <c r="R21" t="n">
-        <v>6998647</v>
+        <v>6998555</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2965,7 +2992,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2975,7 +3002,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,44 +3011,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381505</v>
+        <v>133381501</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,37 +3040,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635742</v>
+        <v>635890</v>
       </c>
       <c r="R22" t="n">
-        <v>6998412</v>
+        <v>6998459</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3091,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,24 +3126,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383837</v>
+        <v>133381506</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,37 +3155,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635681</v>
+        <v>635731</v>
       </c>
       <c r="R23" t="n">
-        <v>6998667</v>
+        <v>6998450</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3214,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3227,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,71 +3236,79 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383854</v>
+        <v>133383859</v>
       </c>
       <c r="B24" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635783</v>
+        <v>635892</v>
       </c>
       <c r="R24" t="n">
-        <v>6998545</v>
+        <v>6998470</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3329,7 +3340,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3339,7 +3350,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,56 +3377,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383845</v>
+        <v>133383862</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635723</v>
+        <v>635771</v>
       </c>
       <c r="R25" t="n">
-        <v>6998687</v>
+        <v>6998407</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3444,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,12 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3486,10 +3484,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133381506</v>
+        <v>133383854</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,26 +3495,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3524,13 +3527,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635731</v>
+        <v>635783</v>
       </c>
       <c r="R26" t="n">
-        <v>6998450</v>
+        <v>6998545</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3559,7 +3562,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3569,7 +3572,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3578,66 +3581,50 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383859</v>
+        <v>133383837</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3647,10 +3634,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635892</v>
+        <v>635681</v>
       </c>
       <c r="R27" t="n">
-        <v>6998470</v>
+        <v>6998667</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3682,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3692,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3719,48 +3706,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383862</v>
+        <v>133383845</v>
       </c>
       <c r="B28" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635771</v>
+        <v>635723</v>
       </c>
       <c r="R28" t="n">
-        <v>6998407</v>
+        <v>6998687</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3794,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,42 +3826,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133381479</v>
+        <v>133383871</v>
       </c>
       <c r="B29" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3869,13 +3864,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635609</v>
+        <v>635666</v>
       </c>
       <c r="R29" t="n">
-        <v>6998605</v>
+        <v>6998564</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3904,7 +3899,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3914,7 +3909,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3923,28 +3918,44 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133381498</v>
+        <v>133383835</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,45 +3963,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635811</v>
+        <v>635674</v>
       </c>
       <c r="R30" t="n">
-        <v>6998569</v>
+        <v>6998672</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4019,7 +4025,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4029,12 +4035,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4043,28 +4044,44 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383869</v>
+        <v>133383848</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>91918</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,42 +4089,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635723</v>
+        <v>635765</v>
       </c>
       <c r="R31" t="n">
-        <v>6998486</v>
+        <v>6998624</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4139,7 +4148,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4158,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,10 +4185,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133383848</v>
+        <v>133381498</v>
       </c>
       <c r="B32" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,37 +4196,45 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635765</v>
+        <v>635811</v>
       </c>
       <c r="R32" t="n">
-        <v>6998624</v>
+        <v>6998569</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4246,7 +4263,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4256,7 +4273,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4271,22 +4293,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383871</v>
+        <v>133383869</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>56522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,26 +4316,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4321,10 +4348,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635666</v>
+        <v>635723</v>
       </c>
       <c r="R33" t="n">
-        <v>6998564</v>
+        <v>6998486</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4356,7 +4383,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4366,7 +4393,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4375,24 +4402,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4409,37 +4420,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133383835</v>
+        <v>133381479</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4447,13 +4463,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635674</v>
+        <v>635609</v>
       </c>
       <c r="R34" t="n">
-        <v>6998672</v>
+        <v>6998605</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4482,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4492,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4501,41 +4517,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381496</v>
+        <v>133381504</v>
       </c>
       <c r="B35" t="n">
         <v>79333</v>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635761</v>
+        <v>635773</v>
       </c>
       <c r="R35" t="n">
-        <v>6998603</v>
+        <v>6998405</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4633,17 +4633,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4661,7 +4661,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381504</v>
+        <v>133381496</v>
       </c>
       <c r="B36" t="n">
         <v>79333</v>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635773</v>
+        <v>635761</v>
       </c>
       <c r="R36" t="n">
-        <v>6998405</v>
+        <v>6998603</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4787,48 +4787,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133383831</v>
+        <v>133381477</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635587</v>
+        <v>635611</v>
       </c>
       <c r="R37" t="n">
-        <v>6998661</v>
+        <v>6998529</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4857,7 +4865,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4867,7 +4875,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4882,68 +4890,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381477</v>
+        <v>133383831</v>
       </c>
       <c r="B38" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635611</v>
+        <v>635587</v>
       </c>
       <c r="R38" t="n">
-        <v>6998529</v>
+        <v>6998661</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4997,60 +4997,63 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133383873</v>
+        <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635593</v>
+        <v>635781</v>
       </c>
       <c r="R39" t="n">
-        <v>6998584</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5089,7 +5092,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5098,69 +5101,82 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133381502</v>
+        <v>133383873</v>
       </c>
       <c r="B40" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635781</v>
+        <v>635593</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998584</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5208,34 +5224,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381512</v>
+        <v>133383867</v>
       </c>
       <c r="B43" t="n">
         <v>57145</v>
@@ -5508,7 +5508,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5518,13 +5518,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635708</v>
+        <v>635701</v>
       </c>
       <c r="R43" t="n">
-        <v>6998578</v>
+        <v>6998483</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5583,19 +5583,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381478</v>
+        <v>133381512</v>
       </c>
       <c r="B44" t="n">
         <v>57145</v>
@@ -5628,7 +5628,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635628</v>
+        <v>635708</v>
       </c>
       <c r="R44" t="n">
-        <v>6998554</v>
+        <v>6998578</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,7 +5683,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5710,7 +5715,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133383867</v>
+        <v>133381478</v>
       </c>
       <c r="B45" t="n">
         <v>57145</v>
@@ -5743,7 +5748,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5753,13 +5758,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635701</v>
+        <v>635628</v>
       </c>
       <c r="R45" t="n">
-        <v>6998483</v>
+        <v>6998554</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5798,12 +5803,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,12 +5818,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6082,46 +6082,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133383830</v>
+        <v>133381509</v>
       </c>
       <c r="B48" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6129,13 +6125,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635569</v>
+        <v>635725</v>
       </c>
       <c r="R48" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6164,7 +6160,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6183,26 +6179,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381509</v>
+        <v>133381491</v>
       </c>
       <c r="B49" t="n">
         <v>57145</v>
@@ -6235,7 +6230,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6245,10 +6240,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635725</v>
+        <v>635695</v>
       </c>
       <c r="R49" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6280,7 +6275,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6290,7 +6285,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6317,42 +6312,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133381491</v>
+        <v>133383830</v>
       </c>
       <c r="B50" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6360,13 +6359,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635695</v>
+        <v>635569</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6395,7 +6394,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6405,7 +6404,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6414,28 +6413,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383828</v>
+        <v>133383836</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,34 +6443,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635586</v>
+        <v>635678</v>
       </c>
       <c r="R51" t="n">
-        <v>6998633</v>
+        <v>6998668</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6502,7 +6505,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,7 +6515,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6521,8 +6524,24 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6646,7 +6665,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383836</v>
+        <v>133383824</v>
       </c>
       <c r="B53" t="n">
         <v>79333</v>
@@ -6684,10 +6703,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635678</v>
+        <v>635647</v>
       </c>
       <c r="R53" t="n">
-        <v>6998668</v>
+        <v>6998562</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6719,7 +6738,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6729,7 +6748,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6772,10 +6791,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383824</v>
+        <v>133383828</v>
       </c>
       <c r="B54" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6783,37 +6802,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635647</v>
+        <v>635586</v>
       </c>
       <c r="R54" t="n">
-        <v>6998562</v>
+        <v>6998633</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6845,7 +6861,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6855,7 +6871,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6864,24 +6880,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7384,27 +7384,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381482</v>
+        <v>133381508</v>
       </c>
       <c r="B59" t="n">
-        <v>56522</v>
+        <v>57145</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635585</v>
+        <v>635708</v>
       </c>
       <c r="R59" t="n">
-        <v>6998647</v>
+        <v>6998507</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7499,27 +7499,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381508</v>
+        <v>133381482</v>
       </c>
       <c r="B60" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635708</v>
+        <v>635585</v>
       </c>
       <c r="R60" t="n">
-        <v>6998507</v>
+        <v>6998647</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7734,42 +7734,46 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133381492</v>
+        <v>133383829</v>
       </c>
       <c r="B62" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7777,13 +7781,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635679</v>
+        <v>635584</v>
       </c>
       <c r="R62" t="n">
-        <v>6998680</v>
+        <v>6998640</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7812,7 +7816,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,7 +7826,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7831,28 +7835,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133381495</v>
+        <v>133383849</v>
       </c>
       <c r="B63" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7860,16 +7865,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7882,7 +7887,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7897,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635759</v>
+        <v>635737</v>
       </c>
       <c r="R63" t="n">
-        <v>6998610</v>
+        <v>6998616</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,7 +7942,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7952,44 +7962,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B64" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7997,7 +8007,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8007,13 +8017,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R64" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8042,7 +8052,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8052,12 +8062,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8072,58 +8077,54 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133383829</v>
+        <v>133381495</v>
       </c>
       <c r="B65" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8131,13 +8132,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635584</v>
+        <v>635759</v>
       </c>
       <c r="R65" t="n">
-        <v>6998640</v>
+        <v>6998610</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8166,7 +8167,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8176,7 +8177,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8185,29 +8186,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133381516</v>
+        <v>133383840</v>
       </c>
       <c r="B66" t="n">
-        <v>57145</v>
+        <v>91881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8215,45 +8215,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635613</v>
+        <v>635687</v>
       </c>
       <c r="R66" t="n">
-        <v>6998551</v>
+        <v>6998644</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8282,7 +8274,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8292,12 +8284,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre spillning med tarmtömning.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8312,12 +8299,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8450,10 +8437,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133383840</v>
+        <v>133381516</v>
       </c>
       <c r="B68" t="n">
-        <v>91881</v>
+        <v>57145</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8461,37 +8448,45 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635687</v>
+        <v>635613</v>
       </c>
       <c r="R68" t="n">
-        <v>6998644</v>
+        <v>6998551</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8520,7 +8515,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8530,7 +8525,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre spillning med tarmtömning.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8545,22 +8545,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381515</v>
+        <v>133381513</v>
       </c>
       <c r="B69" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8568,31 +8568,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8600,13 +8595,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635614</v>
+        <v>635632</v>
       </c>
       <c r="R69" t="n">
-        <v>6998564</v>
+        <v>6998603</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8635,7 +8630,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8645,7 +8640,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8654,8 +8649,24 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8672,51 +8683,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133381513</v>
+        <v>133383843</v>
       </c>
       <c r="B70" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635632</v>
+        <v>635701</v>
       </c>
       <c r="R70" t="n">
-        <v>6998603</v>
+        <v>6998689</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8745,7 +8753,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8755,7 +8763,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8764,82 +8772,74 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133383843</v>
+        <v>133381515</v>
       </c>
       <c r="B71" t="n">
-        <v>91881</v>
+        <v>57136</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635701</v>
+        <v>635614</v>
       </c>
       <c r="R71" t="n">
-        <v>6998689</v>
+        <v>6998564</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8893,12 +8893,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381481</v>
+        <v>133381486</v>
       </c>
       <c r="B5" t="n">
-        <v>97995</v>
+        <v>91881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,27 +1039,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635587</v>
+        <v>635569</v>
       </c>
       <c r="R5" t="n">
-        <v>6998640</v>
+        <v>6998651</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,6 +1123,21 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1266,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133381486</v>
+        <v>133381481</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>97995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,26 +1291,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635569</v>
+        <v>635587</v>
       </c>
       <c r="R7" t="n">
-        <v>6998651</v>
+        <v>6998640</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,21 +1376,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,56 +1392,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133383855</v>
+        <v>133383833</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635821</v>
+        <v>635598</v>
       </c>
       <c r="R8" t="n">
-        <v>6998575</v>
+        <v>6998686</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,12 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133383838</v>
+        <v>133383858</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,31 +1510,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1555,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635697</v>
+        <v>635878</v>
       </c>
       <c r="R9" t="n">
-        <v>6998678</v>
+        <v>6998469</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1590,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,12 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,8 +1591,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1632,48 +1625,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133383833</v>
+        <v>133383855</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635598</v>
+        <v>635821</v>
       </c>
       <c r="R10" t="n">
-        <v>6998686</v>
+        <v>6998575</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1713,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133383858</v>
+        <v>133383838</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,26 +1756,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1777,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635878</v>
+        <v>635697</v>
       </c>
       <c r="R11" t="n">
-        <v>6998469</v>
+        <v>6998678</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1812,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,24 +1847,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2309,60 +2309,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133383825</v>
+        <v>133381484</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635595</v>
+        <v>635574</v>
       </c>
       <c r="R16" t="n">
-        <v>6998619</v>
+        <v>6998638</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2391,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2401,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,67 +2398,78 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133381484</v>
+        <v>133383825</v>
       </c>
       <c r="B17" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635574</v>
+        <v>635595</v>
       </c>
       <c r="R17" t="n">
-        <v>6998638</v>
+        <v>6998619</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,28 +2517,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133381505</v>
+        <v>133381480</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635742</v>
+        <v>635598</v>
       </c>
       <c r="R18" t="n">
-        <v>6998412</v>
+        <v>6998614</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,17 +2634,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381480</v>
+        <v>133381493</v>
       </c>
       <c r="B19" t="n">
         <v>91918</v>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635598</v>
+        <v>635756</v>
       </c>
       <c r="R19" t="n">
-        <v>6998614</v>
+        <v>6998647</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2788,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381493</v>
+        <v>133383823</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,26 +2799,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2826,13 +2831,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635756</v>
+        <v>635652</v>
       </c>
       <c r="R20" t="n">
-        <v>6998647</v>
+        <v>6998555</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2861,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2871,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2880,41 +2885,25 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133383823</v>
+        <v>133381501</v>
       </c>
       <c r="B21" t="n">
         <v>57955</v>
@@ -2947,23 +2936,23 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635652</v>
+        <v>635890</v>
       </c>
       <c r="R21" t="n">
-        <v>6998555</v>
+        <v>6998459</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2992,7 +2981,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3002,7 +2991,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3017,22 +3006,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381501</v>
+        <v>133381505</v>
       </c>
       <c r="B22" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,42 +3029,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635890</v>
+        <v>635742</v>
       </c>
       <c r="R22" t="n">
-        <v>6998459</v>
+        <v>6998412</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3107,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,7 +3101,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,8 +3110,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133381506</v>
+        <v>133383837</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,40 +3155,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635731</v>
+        <v>635681</v>
       </c>
       <c r="R23" t="n">
-        <v>6998450</v>
+        <v>6998667</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3217,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,7 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,82 +3233,69 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383859</v>
+        <v>133381506</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635892</v>
+        <v>635731</v>
       </c>
       <c r="R24" t="n">
-        <v>6998470</v>
+        <v>6998450</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3340,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3350,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,63 +3343,87 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383862</v>
+        <v>133383854</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635771</v>
+        <v>635783</v>
       </c>
       <c r="R25" t="n">
-        <v>6998407</v>
+        <v>6998545</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3447,7 +3455,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3465,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,10 +3492,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B26" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,16 +3503,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3527,13 +3535,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R26" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3562,7 +3570,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3572,7 +3580,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,32 +3612,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383837</v>
+        <v>133383859</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3634,10 +3647,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635681</v>
+        <v>635892</v>
       </c>
       <c r="R27" t="n">
-        <v>6998667</v>
+        <v>6998470</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3669,7 +3682,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3692,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,56 +3719,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383845</v>
+        <v>133383862</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635723</v>
+        <v>635771</v>
       </c>
       <c r="R28" t="n">
-        <v>6998687</v>
+        <v>6998407</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3784,7 +3789,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3794,12 +3799,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383871</v>
+        <v>133381498</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,40 +3837,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635666</v>
+        <v>635811</v>
       </c>
       <c r="R29" t="n">
-        <v>6998564</v>
+        <v>6998569</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3899,7 +3904,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3909,7 +3914,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3918,44 +3928,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383835</v>
+        <v>133383848</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3963,37 +3957,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635674</v>
+        <v>635765</v>
       </c>
       <c r="R30" t="n">
-        <v>6998672</v>
+        <v>6998624</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4025,7 +4016,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4035,7 +4026,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4044,24 +4035,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4078,10 +4053,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383848</v>
+        <v>133383871</v>
       </c>
       <c r="B31" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4089,34 +4064,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635765</v>
+        <v>635666</v>
       </c>
       <c r="R31" t="n">
-        <v>6998624</v>
+        <v>6998564</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4148,7 +4126,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4158,7 +4136,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4167,8 +4145,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4185,10 +4179,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133381498</v>
+        <v>133383835</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4196,45 +4190,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635811</v>
+        <v>635674</v>
       </c>
       <c r="R32" t="n">
-        <v>6998569</v>
+        <v>6998672</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4263,7 +4252,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4273,12 +4262,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4287,45 +4271,61 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383869</v>
+        <v>133381479</v>
       </c>
       <c r="B33" t="n">
-        <v>56522</v>
+        <v>57145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4338,7 +4338,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635723</v>
+        <v>635609</v>
       </c>
       <c r="R33" t="n">
-        <v>6998486</v>
+        <v>6998605</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,39 +4408,39 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133381479</v>
+        <v>133383869</v>
       </c>
       <c r="B34" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635609</v>
+        <v>635723</v>
       </c>
       <c r="R34" t="n">
-        <v>6998605</v>
+        <v>6998486</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,22 +4523,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381504</v>
+        <v>133383831</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,40 +4546,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635773</v>
+        <v>635587</v>
       </c>
       <c r="R35" t="n">
-        <v>6998405</v>
+        <v>6998661</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4608,7 +4605,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4618,7 +4615,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4627,41 +4624,25 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381496</v>
+        <v>133381504</v>
       </c>
       <c r="B36" t="n">
         <v>79333</v>
@@ -4699,10 +4680,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635761</v>
+        <v>635773</v>
       </c>
       <c r="R36" t="n">
-        <v>6998603</v>
+        <v>6998405</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4734,7 +4715,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4744,7 +4725,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4759,17 +4740,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4787,42 +4768,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381477</v>
+        <v>133381496</v>
       </c>
       <c r="B37" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4830,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635611</v>
+        <v>635761</v>
       </c>
       <c r="R37" t="n">
-        <v>6998529</v>
+        <v>6998603</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4865,7 +4841,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4875,7 +4851,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,8 +4860,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4902,48 +4894,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133383831</v>
+        <v>133381477</v>
       </c>
       <c r="B38" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635587</v>
+        <v>635611</v>
       </c>
       <c r="R38" t="n">
-        <v>6998661</v>
+        <v>6998529</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4997,12 +4997,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5135,32 +5135,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383873</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5170,13 +5170,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635593</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998584</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5242,32 +5242,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383832</v>
+        <v>133383873</v>
       </c>
       <c r="B41" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635589</v>
+        <v>635593</v>
       </c>
       <c r="R41" t="n">
-        <v>6998667</v>
+        <v>6998584</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6432,10 +6432,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383836</v>
+        <v>133383828</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,37 +6443,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635678</v>
+        <v>635586</v>
       </c>
       <c r="R51" t="n">
-        <v>6998668</v>
+        <v>6998633</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6505,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6515,7 +6512,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6524,24 +6521,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6791,10 +6772,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383828</v>
+        <v>133383836</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6802,34 +6783,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635586</v>
+        <v>635678</v>
       </c>
       <c r="R54" t="n">
-        <v>6998633</v>
+        <v>6998668</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6861,7 +6845,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6871,7 +6855,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6880,8 +6864,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6898,7 +6898,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383844</v>
+        <v>133383846</v>
       </c>
       <c r="B55" t="n">
         <v>57958</v>
@@ -6931,7 +6931,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6941,13 +6941,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635724</v>
+        <v>635727</v>
       </c>
       <c r="R55" t="n">
-        <v>6998682</v>
+        <v>6998685</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6986,12 +6986,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,7 +7018,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383846</v>
+        <v>133383844</v>
       </c>
       <c r="B56" t="n">
         <v>57958</v>
@@ -7051,7 +7051,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7061,13 +7061,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635727</v>
+        <v>635724</v>
       </c>
       <c r="R56" t="n">
-        <v>6998685</v>
+        <v>6998682</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,37 +7138,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383863</v>
+        <v>133381487</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7176,13 +7185,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635750</v>
+        <v>635566</v>
       </c>
       <c r="R57" t="n">
-        <v>6998423</v>
+        <v>6998671</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7211,7 +7220,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7221,7 +7230,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7234,40 +7243,25 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133383860</v>
+        <v>133381482</v>
       </c>
       <c r="B58" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7275,21 +7269,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7297,7 +7291,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7307,13 +7301,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635875</v>
+        <v>635585</v>
       </c>
       <c r="R58" t="n">
-        <v>6998347</v>
+        <v>6998647</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,7 +7336,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7352,12 +7346,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7372,54 +7361,49 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381508</v>
+        <v>133383863</v>
       </c>
       <c r="B59" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7427,13 +7411,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635708</v>
+        <v>635750</v>
       </c>
       <c r="R59" t="n">
-        <v>6998507</v>
+        <v>6998423</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7462,7 +7446,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7456,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7481,28 +7465,44 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381482</v>
+        <v>133383860</v>
       </c>
       <c r="B60" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7532,7 +7532,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7542,13 +7542,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635585</v>
+        <v>635875</v>
       </c>
       <c r="R60" t="n">
-        <v>6998647</v>
+        <v>6998347</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7587,7 +7587,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7602,58 +7607,54 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381487</v>
+        <v>133381508</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7661,10 +7662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635566</v>
+        <v>635708</v>
       </c>
       <c r="R61" t="n">
-        <v>6998671</v>
+        <v>6998507</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7696,7 +7697,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7706,7 +7707,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7715,7 +7716,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7734,46 +7734,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133383829</v>
+        <v>133381495</v>
       </c>
       <c r="B62" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7781,13 +7777,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635584</v>
+        <v>635759</v>
       </c>
       <c r="R62" t="n">
-        <v>6998640</v>
+        <v>6998610</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7816,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7826,7 +7822,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7835,51 +7831,50 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7887,7 +7882,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7897,13 +7892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R63" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7932,7 +7927,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7942,12 +7937,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7962,44 +7952,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133381492</v>
+        <v>133383849</v>
       </c>
       <c r="B64" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8007,7 +7997,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8017,13 +8007,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635679</v>
+        <v>635737</v>
       </c>
       <c r="R64" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8052,7 +8042,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8062,7 +8052,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8077,54 +8072,58 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133381495</v>
+        <v>133383829</v>
       </c>
       <c r="B65" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8132,13 +8131,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635759</v>
+        <v>635584</v>
       </c>
       <c r="R65" t="n">
-        <v>6998610</v>
+        <v>6998640</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8167,7 +8166,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8177,7 +8176,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8186,28 +8185,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133383840</v>
+        <v>133381516</v>
       </c>
       <c r="B66" t="n">
-        <v>91881</v>
+        <v>57145</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8215,37 +8215,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635687</v>
+        <v>635613</v>
       </c>
       <c r="R66" t="n">
-        <v>6998644</v>
+        <v>6998551</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8274,7 +8282,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8284,7 +8292,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre spillning med tarmtömning.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8299,12 +8312,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8437,10 +8450,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133381516</v>
+        <v>133383840</v>
       </c>
       <c r="B68" t="n">
-        <v>57145</v>
+        <v>91881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8448,45 +8461,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635613</v>
+        <v>635687</v>
       </c>
       <c r="R68" t="n">
-        <v>6998551</v>
+        <v>6998644</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8515,7 +8520,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8525,12 +8530,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre spillning med tarmtömning.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8545,12 +8545,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R2" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,82 +764,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R3" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,64 +874,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133383841</v>
+        <v>133381486</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635692</v>
+        <v>635569</v>
       </c>
       <c r="R4" t="n">
-        <v>6998659</v>
+        <v>6998651</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,47 +1004,62 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381486</v>
+        <v>133381485</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635569</v>
+        <v>635571</v>
       </c>
       <c r="R5" t="n">
-        <v>6998651</v>
+        <v>6998656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,37 +1160,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381485</v>
+        <v>133383841</v>
       </c>
       <c r="B6" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635571</v>
+        <v>635692</v>
       </c>
       <c r="R6" t="n">
-        <v>6998656</v>
+        <v>6998659</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,30 +1265,15 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1392,48 +1392,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133383833</v>
+        <v>133383838</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635598</v>
+        <v>635697</v>
       </c>
       <c r="R8" t="n">
-        <v>6998686</v>
+        <v>6998678</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1480,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133383858</v>
+        <v>133383855</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,26 +1523,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1537,10 +1555,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635878</v>
+        <v>635821</v>
       </c>
       <c r="R9" t="n">
-        <v>6998469</v>
+        <v>6998575</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1572,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1600,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,24 +1614,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1625,56 +1632,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133383855</v>
+        <v>133383833</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635821</v>
+        <v>635598</v>
       </c>
       <c r="R10" t="n">
-        <v>6998575</v>
+        <v>6998686</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,7 +1702,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1712,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1739,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133383838</v>
+        <v>133383858</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,31 +1750,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1788,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635697</v>
+        <v>635878</v>
       </c>
       <c r="R11" t="n">
-        <v>6998678</v>
+        <v>6998469</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1823,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,8 +1831,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2309,48 +2309,60 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133381484</v>
+        <v>133383825</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635574</v>
+        <v>635595</v>
       </c>
       <c r="R16" t="n">
-        <v>6998638</v>
+        <v>6998619</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2391,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2401,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,78 +2410,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383825</v>
+        <v>133381484</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635595</v>
+        <v>635574</v>
       </c>
       <c r="R17" t="n">
-        <v>6998619</v>
+        <v>6998638</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2498,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,29 +2518,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133381480</v>
+        <v>133381505</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635598</v>
+        <v>635742</v>
       </c>
       <c r="R18" t="n">
-        <v>6998614</v>
+        <v>6998412</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,17 +2634,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381493</v>
+        <v>133381480</v>
       </c>
       <c r="B19" t="n">
         <v>91918</v>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635756</v>
+        <v>635598</v>
       </c>
       <c r="R19" t="n">
-        <v>6998647</v>
+        <v>6998614</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2788,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133383823</v>
+        <v>133381493</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,31 +2799,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2831,13 +2826,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635652</v>
+        <v>635756</v>
       </c>
       <c r="R20" t="n">
-        <v>6998555</v>
+        <v>6998647</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2866,7 +2861,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2871,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,25 +2880,41 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133381501</v>
+        <v>133383823</v>
       </c>
       <c r="B21" t="n">
         <v>57955</v>
@@ -2936,23 +2947,23 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635890</v>
+        <v>635652</v>
       </c>
       <c r="R21" t="n">
-        <v>6998459</v>
+        <v>6998555</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2981,7 +2992,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2991,7 +3002,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3006,22 +3017,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381505</v>
+        <v>133381501</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,37 +3040,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635742</v>
+        <v>635890</v>
       </c>
       <c r="R22" t="n">
-        <v>6998412</v>
+        <v>6998459</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3091,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,24 +3126,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3144,32 +3144,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383837</v>
+        <v>133383862</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635681</v>
+        <v>635771</v>
       </c>
       <c r="R23" t="n">
-        <v>6998667</v>
+        <v>6998407</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3377,53 +3377,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383854</v>
+        <v>133383859</v>
       </c>
       <c r="B25" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635783</v>
+        <v>635892</v>
       </c>
       <c r="R25" t="n">
-        <v>6998545</v>
+        <v>6998470</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3455,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3465,7 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3492,10 +3484,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383845</v>
+        <v>133383854</v>
       </c>
       <c r="B26" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,16 +3495,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3535,13 +3527,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635723</v>
+        <v>635783</v>
       </c>
       <c r="R26" t="n">
-        <v>6998687</v>
+        <v>6998545</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3570,7 +3562,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3580,12 +3572,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3612,32 +3599,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383859</v>
+        <v>133383837</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3647,10 +3634,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635892</v>
+        <v>635681</v>
       </c>
       <c r="R27" t="n">
-        <v>6998470</v>
+        <v>6998667</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3682,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3692,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3719,48 +3706,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383862</v>
+        <v>133383845</v>
       </c>
       <c r="B28" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635771</v>
+        <v>635723</v>
       </c>
       <c r="R28" t="n">
-        <v>6998407</v>
+        <v>6998687</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3794,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133381498</v>
+        <v>133383869</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3859,23 +3859,23 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635811</v>
+        <v>635723</v>
       </c>
       <c r="R29" t="n">
-        <v>6998569</v>
+        <v>6998486</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3914,12 +3914,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3934,22 +3929,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383848</v>
+        <v>133381498</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,37 +3952,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635765</v>
+        <v>635811</v>
       </c>
       <c r="R30" t="n">
-        <v>6998624</v>
+        <v>6998569</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4016,7 +4019,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4026,7 +4029,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4041,12 +4049,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4305,56 +4313,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133381479</v>
+        <v>133383848</v>
       </c>
       <c r="B33" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635609</v>
+        <v>635765</v>
       </c>
       <c r="R33" t="n">
-        <v>6998605</v>
+        <v>6998624</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,39 +4408,39 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133383869</v>
+        <v>133381479</v>
       </c>
       <c r="B34" t="n">
-        <v>56522</v>
+        <v>57145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635723</v>
+        <v>635609</v>
       </c>
       <c r="R34" t="n">
-        <v>6998486</v>
+        <v>6998605</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,60 +4523,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133383831</v>
+        <v>133381477</v>
       </c>
       <c r="B35" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635587</v>
+        <v>635611</v>
       </c>
       <c r="R35" t="n">
-        <v>6998661</v>
+        <v>6998529</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4605,7 +4613,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4623,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,19 +4638,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381504</v>
+        <v>133381496</v>
       </c>
       <c r="B36" t="n">
         <v>79333</v>
@@ -4680,10 +4688,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635773</v>
+        <v>635761</v>
       </c>
       <c r="R36" t="n">
-        <v>6998405</v>
+        <v>6998603</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4715,7 +4723,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4725,7 +4733,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4740,17 +4748,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4768,7 +4776,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381496</v>
+        <v>133381504</v>
       </c>
       <c r="B37" t="n">
         <v>79333</v>
@@ -4806,10 +4814,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635761</v>
+        <v>635773</v>
       </c>
       <c r="R37" t="n">
-        <v>6998603</v>
+        <v>6998405</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4841,7 +4849,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4851,7 +4859,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4866,17 +4874,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4894,56 +4902,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381477</v>
+        <v>133383831</v>
       </c>
       <c r="B38" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635611</v>
+        <v>635587</v>
       </c>
       <c r="R38" t="n">
-        <v>6998529</v>
+        <v>6998661</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4997,22 +4997,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,40 +5020,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R39" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5082,7 +5079,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5092,7 +5089,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5101,44 +5098,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B40" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5146,37 +5127,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5189,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5199,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5224,18 +5208,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5349,37 +5349,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381489</v>
+        <v>133383867</v>
       </c>
       <c r="B42" t="n">
-        <v>92217</v>
+        <v>57145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5387,13 +5392,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635687</v>
+        <v>635701</v>
       </c>
       <c r="R42" t="n">
-        <v>6998661</v>
+        <v>6998483</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5422,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5432,7 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5441,76 +5451,55 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133383867</v>
+        <v>133381489</v>
       </c>
       <c r="B43" t="n">
-        <v>57145</v>
+        <v>92217</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5518,13 +5507,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635701</v>
+        <v>635687</v>
       </c>
       <c r="R43" t="n">
-        <v>6998483</v>
+        <v>6998661</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5553,7 +5542,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5563,12 +5552,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5577,18 +5561,34 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6197,42 +6197,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381491</v>
+        <v>133383830</v>
       </c>
       <c r="B49" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6240,13 +6244,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635695</v>
+        <v>635569</v>
       </c>
       <c r="R49" t="n">
         <v>6998652</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6275,7 +6279,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6285,7 +6289,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6294,64 +6298,61 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133383830</v>
+        <v>133381491</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6359,13 +6360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635569</v>
+        <v>635695</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6394,7 +6395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6404,7 +6405,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6413,29 +6414,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383828</v>
+        <v>133383824</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,34 +6443,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635586</v>
+        <v>635647</v>
       </c>
       <c r="R51" t="n">
-        <v>6998633</v>
+        <v>6998562</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6502,7 +6505,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,7 +6515,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6521,8 +6524,24 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6539,10 +6558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383852</v>
+        <v>133383836</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6550,34 +6569,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635765</v>
+        <v>635678</v>
       </c>
       <c r="R52" t="n">
-        <v>6998580</v>
+        <v>6998668</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6609,7 +6631,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6619,7 +6641,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6628,8 +6650,24 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6646,10 +6684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383824</v>
+        <v>133383828</v>
       </c>
       <c r="B53" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6657,37 +6695,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635647</v>
+        <v>635586</v>
       </c>
       <c r="R53" t="n">
-        <v>6998562</v>
+        <v>6998633</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6719,7 +6754,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6729,7 +6764,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6738,24 +6773,8 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6772,10 +6791,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383836</v>
+        <v>133383852</v>
       </c>
       <c r="B54" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6783,37 +6802,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635678</v>
+        <v>635765</v>
       </c>
       <c r="R54" t="n">
-        <v>6998668</v>
+        <v>6998580</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6845,7 +6861,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6855,7 +6871,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6864,24 +6880,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6898,7 +6898,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383846</v>
+        <v>133383844</v>
       </c>
       <c r="B55" t="n">
         <v>57958</v>
@@ -6931,7 +6931,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6941,13 +6941,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635727</v>
+        <v>635724</v>
       </c>
       <c r="R55" t="n">
-        <v>6998685</v>
+        <v>6998682</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6986,12 +6986,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,7 +7018,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383844</v>
+        <v>133383846</v>
       </c>
       <c r="B56" t="n">
         <v>57958</v>
@@ -7051,7 +7051,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7061,13 +7061,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635724</v>
+        <v>635727</v>
       </c>
       <c r="R56" t="n">
-        <v>6998682</v>
+        <v>6998685</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,46 +7138,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133381487</v>
+        <v>133383863</v>
       </c>
       <c r="B57" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7185,13 +7176,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635566</v>
+        <v>635750</v>
       </c>
       <c r="R57" t="n">
-        <v>6998671</v>
+        <v>6998423</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7220,7 +7211,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7230,7 +7221,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7243,25 +7234,40 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381482</v>
+        <v>133383860</v>
       </c>
       <c r="B58" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7269,21 +7275,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7291,7 +7297,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7301,13 +7307,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635585</v>
+        <v>635875</v>
       </c>
       <c r="R58" t="n">
-        <v>6998647</v>
+        <v>6998347</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7336,7 +7342,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7346,7 +7352,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7361,49 +7372,58 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133383863</v>
+        <v>133381487</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7411,13 +7431,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635750</v>
+        <v>635566</v>
       </c>
       <c r="R59" t="n">
-        <v>6998423</v>
+        <v>6998671</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7446,7 +7466,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7456,7 +7476,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7469,62 +7489,47 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133383860</v>
+        <v>133381508</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7532,7 +7537,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7542,13 +7547,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635875</v>
+        <v>635708</v>
       </c>
       <c r="R60" t="n">
-        <v>6998347</v>
+        <v>6998507</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7577,7 +7582,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7587,12 +7592,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7607,39 +7607,39 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381508</v>
+        <v>133381482</v>
       </c>
       <c r="B61" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635708</v>
+        <v>635585</v>
       </c>
       <c r="R61" t="n">
-        <v>6998507</v>
+        <v>6998647</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7849,32 +7849,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133381492</v>
+        <v>133383849</v>
       </c>
       <c r="B63" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635679</v>
+        <v>635737</v>
       </c>
       <c r="R63" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,7 +7937,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7952,44 +7957,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B64" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7997,7 +8002,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8007,13 +8012,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R64" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8042,7 +8047,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8052,12 +8057,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8072,12 +8072,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8557,51 +8557,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381513</v>
+        <v>133383843</v>
       </c>
       <c r="B69" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635632</v>
+        <v>635701</v>
       </c>
       <c r="R69" t="n">
-        <v>6998603</v>
+        <v>6998689</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8630,7 +8627,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8640,7 +8637,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8649,82 +8646,69 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133383843</v>
+        <v>133381513</v>
       </c>
       <c r="B70" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635701</v>
+        <v>635632</v>
       </c>
       <c r="R70" t="n">
-        <v>6998689</v>
+        <v>6998603</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8753,7 +8737,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8763,7 +8747,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8772,18 +8756,34 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R2" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,69 +767,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R3" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,71 +890,64 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381486</v>
+        <v>133383841</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635569</v>
+        <v>635692</v>
       </c>
       <c r="R4" t="n">
-        <v>6998651</v>
+        <v>6998659</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,67 +1013,53 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381485</v>
+        <v>133381481</v>
       </c>
       <c r="B5" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635571</v>
+        <v>635587</v>
       </c>
       <c r="R5" t="n">
-        <v>6998656</v>
+        <v>6998640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,21 +1124,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1160,46 +1140,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133383841</v>
+        <v>133381485</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635692</v>
+        <v>635571</v>
       </c>
       <c r="R6" t="n">
-        <v>6998659</v>
+        <v>6998656</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,25 +1236,40 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133381481</v>
+        <v>133381486</v>
       </c>
       <c r="B7" t="n">
-        <v>97995</v>
+        <v>91881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,27 +1277,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635587</v>
+        <v>635569</v>
       </c>
       <c r="R7" t="n">
-        <v>6998640</v>
+        <v>6998651</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,6 +1361,21 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,56 +1392,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133383838</v>
+        <v>133383833</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635697</v>
+        <v>635598</v>
       </c>
       <c r="R8" t="n">
-        <v>6998678</v>
+        <v>6998686</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,12 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133383855</v>
+        <v>133383858</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,31 +1510,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1555,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635821</v>
+        <v>635878</v>
       </c>
       <c r="R9" t="n">
-        <v>6998575</v>
+        <v>6998469</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1590,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,12 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,8 +1591,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1632,48 +1625,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133383833</v>
+        <v>133383855</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635598</v>
+        <v>635821</v>
       </c>
       <c r="R10" t="n">
-        <v>6998686</v>
+        <v>6998575</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1713,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133383858</v>
+        <v>133383838</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,26 +1756,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1777,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635878</v>
+        <v>635697</v>
       </c>
       <c r="R11" t="n">
-        <v>6998469</v>
+        <v>6998678</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1812,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,24 +1847,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2536,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133381505</v>
+        <v>133381480</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635742</v>
+        <v>635598</v>
       </c>
       <c r="R18" t="n">
-        <v>6998412</v>
+        <v>6998614</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,17 +2634,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381480</v>
+        <v>133381505</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,21 +2673,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635598</v>
+        <v>635742</v>
       </c>
       <c r="R19" t="n">
-        <v>6998614</v>
+        <v>6998412</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3144,48 +3144,51 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383862</v>
+        <v>133381506</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635771</v>
+        <v>635731</v>
       </c>
       <c r="R23" t="n">
-        <v>6998407</v>
+        <v>6998450</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3214,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3227,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,28 +3236,44 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133381506</v>
+        <v>133383837</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,40 +3281,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635731</v>
+        <v>635681</v>
       </c>
       <c r="R24" t="n">
-        <v>6998450</v>
+        <v>6998667</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3324,7 +3340,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3350,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3343,34 +3359,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3484,53 +3484,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383854</v>
+        <v>133383862</v>
       </c>
       <c r="B26" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635783</v>
+        <v>635771</v>
       </c>
       <c r="R26" t="n">
-        <v>6998545</v>
+        <v>6998407</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3562,7 +3554,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3572,7 +3564,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383837</v>
+        <v>133383854</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,34 +3602,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635681</v>
+        <v>635783</v>
       </c>
       <c r="R27" t="n">
-        <v>6998667</v>
+        <v>6998545</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383869</v>
+        <v>133381498</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3859,23 +3859,23 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635723</v>
+        <v>635811</v>
       </c>
       <c r="R29" t="n">
-        <v>6998486</v>
+        <v>6998569</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3914,7 +3914,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3929,22 +3934,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133381498</v>
+        <v>133383871</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,45 +3957,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635811</v>
+        <v>635666</v>
       </c>
       <c r="R30" t="n">
-        <v>6998569</v>
+        <v>6998564</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4029,12 +4029,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4043,28 +4038,44 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383871</v>
+        <v>133383848</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,37 +4083,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635666</v>
+        <v>635765</v>
       </c>
       <c r="R31" t="n">
-        <v>6998564</v>
+        <v>6998624</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4134,7 +4142,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4144,7 +4152,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,24 +4161,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4313,48 +4305,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383848</v>
+        <v>133381479</v>
       </c>
       <c r="B33" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635765</v>
+        <v>635609</v>
       </c>
       <c r="R33" t="n">
-        <v>6998624</v>
+        <v>6998605</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,39 +4408,39 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133381479</v>
+        <v>133383869</v>
       </c>
       <c r="B34" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635609</v>
+        <v>635723</v>
       </c>
       <c r="R34" t="n">
-        <v>6998605</v>
+        <v>6998486</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,54 +4523,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381477</v>
+        <v>133381504</v>
       </c>
       <c r="B35" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4578,10 +4573,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635611</v>
+        <v>635773</v>
       </c>
       <c r="R35" t="n">
-        <v>6998529</v>
+        <v>6998405</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4613,7 +4608,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4623,7 +4618,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4632,8 +4627,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4650,10 +4661,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381496</v>
+        <v>133383831</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,40 +4672,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635761</v>
+        <v>635587</v>
       </c>
       <c r="R36" t="n">
-        <v>6998603</v>
+        <v>6998661</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4723,7 +4731,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4733,7 +4741,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4742,41 +4750,25 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381504</v>
+        <v>133381496</v>
       </c>
       <c r="B37" t="n">
         <v>79333</v>
@@ -4814,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635773</v>
+        <v>635761</v>
       </c>
       <c r="R37" t="n">
-        <v>6998405</v>
+        <v>6998603</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4849,7 +4841,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4859,7 +4851,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4874,17 +4866,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4902,48 +4894,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133383831</v>
+        <v>133381477</v>
       </c>
       <c r="B38" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635587</v>
+        <v>635611</v>
       </c>
       <c r="R38" t="n">
-        <v>6998661</v>
+        <v>6998529</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4997,22 +4997,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,37 +5020,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R39" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5089,7 +5092,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5098,28 +5101,44 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5127,40 +5146,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5208,34 +5224,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133383867</v>
+        <v>133381512</v>
       </c>
       <c r="B42" t="n">
         <v>57145</v>
@@ -5382,7 +5382,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635701</v>
+        <v>635708</v>
       </c>
       <c r="R42" t="n">
-        <v>6998483</v>
+        <v>6998578</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5457,49 +5457,54 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381489</v>
+        <v>133381478</v>
       </c>
       <c r="B43" t="n">
-        <v>92217</v>
+        <v>57145</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5507,10 +5512,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635687</v>
+        <v>635628</v>
       </c>
       <c r="R43" t="n">
-        <v>6998661</v>
+        <v>6998554</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5542,7 +5547,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5552,7 +5557,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5561,24 +5566,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5595,7 +5584,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381512</v>
+        <v>133383867</v>
       </c>
       <c r="B44" t="n">
         <v>57145</v>
@@ -5628,7 +5617,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5638,13 +5627,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635708</v>
+        <v>635701</v>
       </c>
       <c r="R44" t="n">
-        <v>6998578</v>
+        <v>6998483</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5673,7 +5662,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,12 +5672,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5703,54 +5692,49 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133381478</v>
+        <v>133381489</v>
       </c>
       <c r="B45" t="n">
-        <v>57145</v>
+        <v>92217</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5758,10 +5742,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635628</v>
+        <v>635687</v>
       </c>
       <c r="R45" t="n">
-        <v>6998554</v>
+        <v>6998661</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5793,7 +5777,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5803,7 +5787,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5812,8 +5796,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5830,10 +5830,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133381490</v>
+        <v>133383864</v>
       </c>
       <c r="B46" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5868,13 +5868,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>635685</v>
+        <v>635759</v>
       </c>
       <c r="R46" t="n">
-        <v>6998661</v>
+        <v>6998415</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5928,38 +5928,38 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133383864</v>
+        <v>133381490</v>
       </c>
       <c r="B47" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635759</v>
+        <v>635685</v>
       </c>
       <c r="R47" t="n">
-        <v>6998415</v>
+        <v>6998661</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6054,70 +6054,74 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133381509</v>
+        <v>133383830</v>
       </c>
       <c r="B48" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6125,13 +6129,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635725</v>
+        <v>635569</v>
       </c>
       <c r="R48" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6160,7 +6164,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6179,64 +6183,61 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133383830</v>
+        <v>133381509</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6244,13 +6245,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635569</v>
+        <v>635725</v>
       </c>
       <c r="R49" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6279,7 +6280,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6289,7 +6290,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6298,19 +6299,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383824</v>
+        <v>133383844</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,26 +6443,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6470,13 +6475,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635647</v>
+        <v>635724</v>
       </c>
       <c r="R51" t="n">
-        <v>6998562</v>
+        <v>6998682</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6505,7 +6510,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6515,7 +6520,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6524,24 +6534,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6558,10 +6552,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383836</v>
+        <v>133383846</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,26 +6563,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6596,13 +6595,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635678</v>
+        <v>635727</v>
       </c>
       <c r="R52" t="n">
-        <v>6998668</v>
+        <v>6998685</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6631,7 +6630,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6641,7 +6640,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6650,24 +6654,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6684,10 +6672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383828</v>
+        <v>133383824</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6695,34 +6683,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635586</v>
+        <v>635647</v>
       </c>
       <c r="R53" t="n">
-        <v>6998633</v>
+        <v>6998562</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6754,7 +6745,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6764,7 +6755,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6773,8 +6764,24 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6791,7 +6798,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383852</v>
+        <v>133383828</v>
       </c>
       <c r="B54" t="n">
         <v>91918</v>
@@ -6826,10 +6833,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635765</v>
+        <v>635586</v>
       </c>
       <c r="R54" t="n">
-        <v>6998580</v>
+        <v>6998633</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6861,7 +6868,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6871,7 +6878,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6898,10 +6905,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383844</v>
+        <v>133383836</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6909,31 +6916,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6941,13 +6943,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635724</v>
+        <v>635678</v>
       </c>
       <c r="R55" t="n">
-        <v>6998682</v>
+        <v>6998668</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6976,7 +6978,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6986,12 +6988,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7000,8 +6997,24 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7018,10 +7031,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383846</v>
+        <v>133383852</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7029,45 +7042,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635727</v>
+        <v>635765</v>
       </c>
       <c r="R56" t="n">
-        <v>6998685</v>
+        <v>6998580</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7096,7 +7101,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7106,12 +7111,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383863</v>
+        <v>133383860</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,26 +7149,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7176,10 +7181,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635750</v>
+        <v>635875</v>
       </c>
       <c r="R57" t="n">
-        <v>6998423</v>
+        <v>6998347</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7211,7 +7216,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7221,7 +7226,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7230,24 +7240,8 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7264,42 +7258,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133383860</v>
+        <v>133381487</v>
       </c>
       <c r="B58" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7307,13 +7305,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635875</v>
+        <v>635566</v>
       </c>
       <c r="R58" t="n">
-        <v>6998347</v>
+        <v>6998671</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,7 +7340,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7352,12 +7350,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7366,64 +7359,61 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381487</v>
+        <v>133381508</v>
       </c>
       <c r="B59" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7431,10 +7421,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635566</v>
+        <v>635708</v>
       </c>
       <c r="R59" t="n">
-        <v>6998671</v>
+        <v>6998507</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7466,7 +7456,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7476,7 +7466,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7485,7 +7475,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7504,42 +7493,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381508</v>
+        <v>133383863</v>
       </c>
       <c r="B60" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7547,13 +7531,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635708</v>
+        <v>635750</v>
       </c>
       <c r="R60" t="n">
-        <v>6998507</v>
+        <v>6998423</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7582,7 +7566,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7592,7 +7576,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7601,18 +7585,34 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7734,10 +7734,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133381495</v>
+        <v>133383849</v>
       </c>
       <c r="B62" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7745,16 +7745,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635759</v>
+        <v>635737</v>
       </c>
       <c r="R62" t="n">
-        <v>6998610</v>
+        <v>6998616</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,7 +7822,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7837,44 +7842,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7882,7 +7887,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7897,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R63" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,12 +7942,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7957,54 +7957,58 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133381492</v>
+        <v>133383829</v>
       </c>
       <c r="B64" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8012,13 +8016,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635679</v>
+        <v>635584</v>
       </c>
       <c r="R64" t="n">
-        <v>6998680</v>
+        <v>6998640</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8047,7 +8051,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8057,7 +8061,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8066,64 +8070,61 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133383829</v>
+        <v>133381495</v>
       </c>
       <c r="B65" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8131,13 +8132,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635584</v>
+        <v>635759</v>
       </c>
       <c r="R65" t="n">
-        <v>6998640</v>
+        <v>6998610</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8166,7 +8167,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8176,7 +8177,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8185,29 +8186,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133381516</v>
+        <v>133383840</v>
       </c>
       <c r="B66" t="n">
-        <v>57145</v>
+        <v>91881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8215,45 +8215,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635613</v>
+        <v>635687</v>
       </c>
       <c r="R66" t="n">
-        <v>6998551</v>
+        <v>6998644</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8282,7 +8274,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8292,12 +8284,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre spillning med tarmtömning.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8312,12 +8299,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8450,10 +8437,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133383840</v>
+        <v>133381516</v>
       </c>
       <c r="B68" t="n">
-        <v>91881</v>
+        <v>57145</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8461,37 +8448,45 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635687</v>
+        <v>635613</v>
       </c>
       <c r="R68" t="n">
-        <v>6998644</v>
+        <v>6998551</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8520,7 +8515,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8530,7 +8525,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre spillning med tarmtömning.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8545,60 +8545,63 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133383843</v>
+        <v>133381513</v>
       </c>
       <c r="B69" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635701</v>
+        <v>635632</v>
       </c>
       <c r="R69" t="n">
-        <v>6998689</v>
+        <v>6998603</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8627,7 +8630,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8637,7 +8640,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8646,69 +8649,82 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133381513</v>
+        <v>133383843</v>
       </c>
       <c r="B70" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635632</v>
+        <v>635701</v>
       </c>
       <c r="R70" t="n">
-        <v>6998603</v>
+        <v>6998689</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8737,7 +8753,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8747,7 +8763,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8756,34 +8772,18 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133381498</v>
+        <v>133383871</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,45 +3837,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635811</v>
+        <v>635666</v>
       </c>
       <c r="R29" t="n">
-        <v>6998569</v>
+        <v>6998564</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3904,7 +3899,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3914,12 +3909,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3928,28 +3918,44 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383871</v>
+        <v>133383848</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,37 +3963,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635666</v>
+        <v>635765</v>
       </c>
       <c r="R30" t="n">
-        <v>6998564</v>
+        <v>6998624</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4019,7 +4022,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4029,7 +4032,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4038,24 +4041,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4072,10 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383848</v>
+        <v>133383835</v>
       </c>
       <c r="B31" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4083,34 +4070,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635765</v>
+        <v>635674</v>
       </c>
       <c r="R31" t="n">
-        <v>6998624</v>
+        <v>6998672</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4142,7 +4132,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4152,7 +4142,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4161,8 +4151,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4179,37 +4185,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133383835</v>
+        <v>133381479</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4217,13 +4228,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635674</v>
+        <v>635609</v>
       </c>
       <c r="R32" t="n">
-        <v>6998672</v>
+        <v>6998605</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4252,7 +4263,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4262,7 +4273,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4271,61 +4282,45 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133381479</v>
+        <v>133383869</v>
       </c>
       <c r="B33" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4338,7 +4333,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4348,13 +4343,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635609</v>
+        <v>635723</v>
       </c>
       <c r="R33" t="n">
-        <v>6998605</v>
+        <v>6998486</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4383,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4393,7 +4388,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,22 +4403,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133383869</v>
+        <v>133381498</v>
       </c>
       <c r="B34" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4431,21 +4426,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4453,23 +4448,23 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635723</v>
+        <v>635811</v>
       </c>
       <c r="R34" t="n">
-        <v>6998486</v>
+        <v>6998569</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4493,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4503,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,12 +4523,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383844</v>
+        <v>133383824</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,31 +6443,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6475,13 +6470,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635724</v>
+        <v>635647</v>
       </c>
       <c r="R51" t="n">
-        <v>6998682</v>
+        <v>6998562</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6510,7 +6505,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6520,12 +6515,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6534,8 +6524,24 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6552,10 +6558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383846</v>
+        <v>133383828</v>
       </c>
       <c r="B52" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6563,45 +6569,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635727</v>
+        <v>635586</v>
       </c>
       <c r="R52" t="n">
-        <v>6998685</v>
+        <v>6998633</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6630,7 +6628,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6640,12 +6638,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6672,7 +6665,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383824</v>
+        <v>133383836</v>
       </c>
       <c r="B53" t="n">
         <v>79333</v>
@@ -6710,10 +6703,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635647</v>
+        <v>635678</v>
       </c>
       <c r="R53" t="n">
-        <v>6998562</v>
+        <v>6998668</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6745,7 +6738,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6755,7 +6748,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6798,7 +6791,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383828</v>
+        <v>133383852</v>
       </c>
       <c r="B54" t="n">
         <v>91918</v>
@@ -6833,10 +6826,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635586</v>
+        <v>635765</v>
       </c>
       <c r="R54" t="n">
-        <v>6998633</v>
+        <v>6998580</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6868,7 +6861,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6878,7 +6871,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6905,10 +6898,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383836</v>
+        <v>133383844</v>
       </c>
       <c r="B55" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,26 +6909,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6943,13 +6941,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635678</v>
+        <v>635724</v>
       </c>
       <c r="R55" t="n">
-        <v>6998668</v>
+        <v>6998682</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6978,7 +6976,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6988,7 +6986,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6997,24 +7000,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7031,10 +7018,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383852</v>
+        <v>133383846</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7042,37 +7029,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635765</v>
+        <v>635727</v>
       </c>
       <c r="R56" t="n">
-        <v>6998580</v>
+        <v>6998685</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7101,7 +7096,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7111,7 +7106,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383860</v>
+        <v>133383863</v>
       </c>
       <c r="B57" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,31 +7149,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7181,10 +7176,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635875</v>
+        <v>635750</v>
       </c>
       <c r="R57" t="n">
-        <v>6998347</v>
+        <v>6998423</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7216,7 +7211,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7226,12 +7221,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7240,8 +7230,24 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7258,46 +7264,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381487</v>
+        <v>133381482</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7305,10 +7307,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635566</v>
+        <v>635585</v>
       </c>
       <c r="R58" t="n">
-        <v>6998671</v>
+        <v>6998647</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7340,7 +7342,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7350,7 +7352,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7359,7 +7361,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7493,10 +7494,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133383863</v>
+        <v>133383860</v>
       </c>
       <c r="B60" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7504,26 +7505,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7531,10 +7537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635750</v>
+        <v>635875</v>
       </c>
       <c r="R60" t="n">
-        <v>6998423</v>
+        <v>6998347</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7566,7 +7572,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7576,7 +7582,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7585,24 +7596,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7619,42 +7614,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381482</v>
+        <v>133381487</v>
       </c>
       <c r="B61" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7662,10 +7661,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635585</v>
+        <v>635566</v>
       </c>
       <c r="R61" t="n">
-        <v>6998647</v>
+        <v>6998671</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7697,7 +7696,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7707,7 +7706,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7716,6 +7715,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7734,10 +7734,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133383849</v>
+        <v>133381495</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7745,16 +7745,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635737</v>
+        <v>635759</v>
       </c>
       <c r="R62" t="n">
-        <v>6998616</v>
+        <v>6998610</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,12 +7822,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7842,12 +7837,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8089,10 +8084,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133381495</v>
+        <v>133383849</v>
       </c>
       <c r="B65" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8100,16 +8095,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8122,7 +8117,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -8132,13 +8127,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635759</v>
+        <v>635737</v>
       </c>
       <c r="R65" t="n">
-        <v>6998610</v>
+        <v>6998616</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8167,7 +8162,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8177,7 +8172,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8192,22 +8192,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133383840</v>
+        <v>133381516</v>
       </c>
       <c r="B66" t="n">
-        <v>91881</v>
+        <v>57145</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8215,37 +8215,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635687</v>
+        <v>635613</v>
       </c>
       <c r="R66" t="n">
-        <v>6998644</v>
+        <v>6998551</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8274,7 +8282,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8284,7 +8292,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre spillning med tarmtömning.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8299,63 +8312,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133381507</v>
+        <v>133383840</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>635729</v>
+        <v>635687</v>
       </c>
       <c r="R67" t="n">
-        <v>6998456</v>
+        <v>6998644</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8384,7 +8394,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8394,7 +8404,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8403,76 +8413,55 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133381516</v>
+        <v>133381507</v>
       </c>
       <c r="B68" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8480,10 +8469,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635613</v>
+        <v>635729</v>
       </c>
       <c r="R68" t="n">
-        <v>6998551</v>
+        <v>6998456</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8515,7 +8504,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8525,12 +8514,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre spillning med tarmtömning.</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8539,8 +8523,24 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -908,44 +908,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133383841</v>
+        <v>133381481</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -955,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635692</v>
+        <v>635587</v>
       </c>
       <c r="R4" t="n">
-        <v>6998659</v>
+        <v>6998640</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,50 +1008,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381481</v>
+        <v>133381485</v>
       </c>
       <c r="B5" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635587</v>
+        <v>635571</v>
       </c>
       <c r="R5" t="n">
-        <v>6998640</v>
+        <v>6998656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,6 +1115,21 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1140,32 +1146,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381485</v>
+        <v>133381486</v>
       </c>
       <c r="B6" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635571</v>
+        <v>635569</v>
       </c>
       <c r="R6" t="n">
-        <v>6998656</v>
+        <v>6998651</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,37 +1272,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133381486</v>
+        <v>133383841</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635569</v>
+        <v>635692</v>
       </c>
       <c r="R7" t="n">
-        <v>6998651</v>
+        <v>6998659</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,30 +1377,15 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381505</v>
+        <v>133381493</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,21 +2673,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635742</v>
+        <v>635756</v>
       </c>
       <c r="R19" t="n">
-        <v>6998412</v>
+        <v>6998647</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381493</v>
+        <v>133381505</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,21 +2799,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635756</v>
+        <v>635742</v>
       </c>
       <c r="R20" t="n">
-        <v>6998647</v>
+        <v>6998412</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133381506</v>
+        <v>133383837</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,40 +3155,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635731</v>
+        <v>635681</v>
       </c>
       <c r="R23" t="n">
-        <v>6998450</v>
+        <v>6998667</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3217,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,7 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,44 +3233,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383837</v>
+        <v>133381506</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,37 +3262,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635681</v>
+        <v>635731</v>
       </c>
       <c r="R24" t="n">
-        <v>6998667</v>
+        <v>6998450</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3340,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3350,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,18 +3343,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,16 +3602,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R27" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383845</v>
+        <v>133383854</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,16 +3722,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3749,13 +3754,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635723</v>
+        <v>635783</v>
       </c>
       <c r="R28" t="n">
-        <v>6998687</v>
+        <v>6998545</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3784,7 +3789,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3794,12 +3799,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3952,10 +3952,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383848</v>
+        <v>133383835</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3963,34 +3963,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635765</v>
+        <v>635674</v>
       </c>
       <c r="R30" t="n">
-        <v>6998624</v>
+        <v>6998672</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4022,7 +4025,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4032,7 +4035,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4041,8 +4044,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4059,10 +4078,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383835</v>
+        <v>133381498</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4070,40 +4089,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635674</v>
+        <v>635811</v>
       </c>
       <c r="R31" t="n">
-        <v>6998672</v>
+        <v>6998569</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4132,7 +4156,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4142,7 +4166,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4151,90 +4180,66 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133381479</v>
+        <v>133383848</v>
       </c>
       <c r="B32" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635609</v>
+        <v>635765</v>
       </c>
       <c r="R32" t="n">
-        <v>6998605</v>
+        <v>6998624</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4263,7 +4268,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4273,7 +4278,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4288,39 +4293,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383869</v>
+        <v>133381479</v>
       </c>
       <c r="B33" t="n">
-        <v>56522</v>
+        <v>57145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4333,7 +4338,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4343,13 +4348,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635723</v>
+        <v>635609</v>
       </c>
       <c r="R33" t="n">
-        <v>6998486</v>
+        <v>6998605</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4378,7 +4383,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,7 +4393,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,22 +4408,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133381498</v>
+        <v>133383869</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4426,21 +4431,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4448,23 +4453,23 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635811</v>
+        <v>635723</v>
       </c>
       <c r="R34" t="n">
-        <v>6998569</v>
+        <v>6998486</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4493,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4503,12 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,22 +4523,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381504</v>
+        <v>133383831</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,40 +4546,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635773</v>
+        <v>635587</v>
       </c>
       <c r="R35" t="n">
-        <v>6998405</v>
+        <v>6998661</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4608,7 +4605,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4618,7 +4615,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4627,44 +4624,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133383831</v>
+        <v>133381504</v>
       </c>
       <c r="B36" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4672,37 +4653,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635587</v>
+        <v>635773</v>
       </c>
       <c r="R36" t="n">
-        <v>6998661</v>
+        <v>6998405</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4731,7 +4715,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4741,7 +4725,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4750,18 +4734,34 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5009,51 +5009,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133381502</v>
+        <v>133383873</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635781</v>
+        <v>635593</v>
       </c>
       <c r="R39" t="n">
-        <v>6998384</v>
+        <v>6998584</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5082,7 +5079,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5092,7 +5089,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5101,44 +5098,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B40" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5146,37 +5127,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5189,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5199,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5224,50 +5208,66 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383873</v>
+        <v>133383832</v>
       </c>
       <c r="B41" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635593</v>
+        <v>635589</v>
       </c>
       <c r="R41" t="n">
-        <v>6998584</v>
+        <v>6998667</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5349,42 +5349,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381512</v>
+        <v>133381489</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>92217</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5392,10 +5387,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635708</v>
+        <v>635687</v>
       </c>
       <c r="R42" t="n">
-        <v>6998578</v>
+        <v>6998661</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5427,7 +5422,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,12 +5432,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5451,8 +5441,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5469,7 +5475,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381478</v>
+        <v>133381512</v>
       </c>
       <c r="B43" t="n">
         <v>57145</v>
@@ -5502,7 +5508,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5512,10 +5518,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635628</v>
+        <v>635708</v>
       </c>
       <c r="R43" t="n">
-        <v>6998554</v>
+        <v>6998578</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5547,7 +5553,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5557,7 +5563,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5704,37 +5715,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133381489</v>
+        <v>133381478</v>
       </c>
       <c r="B45" t="n">
-        <v>92217</v>
+        <v>57145</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5742,10 +5758,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635687</v>
+        <v>635628</v>
       </c>
       <c r="R45" t="n">
-        <v>6998661</v>
+        <v>6998554</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5777,7 +5793,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5787,7 +5803,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5796,24 +5812,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5830,10 +5830,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133383864</v>
+        <v>133381490</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5868,13 +5868,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>635759</v>
+        <v>635685</v>
       </c>
       <c r="R46" t="n">
-        <v>6998415</v>
+        <v>6998661</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5928,38 +5928,38 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133381490</v>
+        <v>133383864</v>
       </c>
       <c r="B47" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635685</v>
+        <v>635759</v>
       </c>
       <c r="R47" t="n">
-        <v>6998661</v>
+        <v>6998415</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6054,74 +6054,70 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133383830</v>
+        <v>133381509</v>
       </c>
       <c r="B48" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6129,13 +6125,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635569</v>
+        <v>635725</v>
       </c>
       <c r="R48" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6164,7 +6160,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6183,26 +6179,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381509</v>
+        <v>133381491</v>
       </c>
       <c r="B49" t="n">
         <v>57145</v>
@@ -6235,7 +6230,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6245,10 +6240,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635725</v>
+        <v>635695</v>
       </c>
       <c r="R49" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6280,7 +6275,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6290,7 +6285,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6317,42 +6312,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133381491</v>
+        <v>133383830</v>
       </c>
       <c r="B50" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6360,13 +6359,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635695</v>
+        <v>635569</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6395,7 +6394,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6405,7 +6404,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6414,18 +6413,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383828</v>
+        <v>133383836</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,34 +6569,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635586</v>
+        <v>635678</v>
       </c>
       <c r="R52" t="n">
-        <v>6998633</v>
+        <v>6998668</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6628,7 +6631,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6638,7 +6641,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6647,8 +6650,24 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6665,10 +6684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383836</v>
+        <v>133383844</v>
       </c>
       <c r="B53" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6676,26 +6695,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6703,13 +6727,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635678</v>
+        <v>635724</v>
       </c>
       <c r="R53" t="n">
-        <v>6998668</v>
+        <v>6998682</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6738,7 +6762,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6748,7 +6772,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6757,24 +6786,8 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6791,10 +6804,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383852</v>
+        <v>133383846</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6802,37 +6815,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635765</v>
+        <v>635727</v>
       </c>
       <c r="R54" t="n">
-        <v>6998580</v>
+        <v>6998685</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6861,7 +6882,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6871,7 +6892,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6898,10 +6924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383844</v>
+        <v>133383828</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6909,45 +6935,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635724</v>
+        <v>635586</v>
       </c>
       <c r="R55" t="n">
-        <v>6998682</v>
+        <v>6998633</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6976,7 +6994,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6986,12 +7004,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,10 +7031,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383846</v>
+        <v>133383852</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7029,45 +7042,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635727</v>
+        <v>635765</v>
       </c>
       <c r="R56" t="n">
-        <v>6998685</v>
+        <v>6998580</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7096,7 +7101,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7106,12 +7111,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383863</v>
+        <v>133383860</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,26 +7149,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7176,10 +7181,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635750</v>
+        <v>635875</v>
       </c>
       <c r="R57" t="n">
-        <v>6998423</v>
+        <v>6998347</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7211,7 +7216,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7221,7 +7226,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7230,24 +7240,8 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7264,42 +7258,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381482</v>
+        <v>133381487</v>
       </c>
       <c r="B58" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7307,10 +7305,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635585</v>
+        <v>635566</v>
       </c>
       <c r="R58" t="n">
-        <v>6998647</v>
+        <v>6998671</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7342,7 +7340,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7352,7 +7350,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7361,6 +7359,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7379,42 +7378,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381508</v>
+        <v>133383863</v>
       </c>
       <c r="B59" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7422,13 +7416,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635708</v>
+        <v>635750</v>
       </c>
       <c r="R59" t="n">
-        <v>6998507</v>
+        <v>6998423</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7457,7 +7451,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7467,7 +7461,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7476,50 +7470,66 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133383860</v>
+        <v>133381508</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7527,7 +7537,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7537,13 +7547,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635875</v>
+        <v>635708</v>
       </c>
       <c r="R60" t="n">
-        <v>6998347</v>
+        <v>6998507</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7572,7 +7582,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7582,12 +7592,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7602,58 +7607,54 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381487</v>
+        <v>133381482</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7661,10 +7662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635566</v>
+        <v>635585</v>
       </c>
       <c r="R61" t="n">
-        <v>6998671</v>
+        <v>6998647</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7696,7 +7697,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7706,7 +7707,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7715,7 +7716,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7849,32 +7849,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133381492</v>
+        <v>133383849</v>
       </c>
       <c r="B63" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635679</v>
+        <v>635737</v>
       </c>
       <c r="R63" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,7 +7937,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7952,58 +7957,54 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133383829</v>
+        <v>133381492</v>
       </c>
       <c r="B64" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8011,13 +8012,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635584</v>
+        <v>635679</v>
       </c>
       <c r="R64" t="n">
-        <v>6998640</v>
+        <v>6998680</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8046,7 +8047,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8056,7 +8057,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8065,61 +8066,64 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133383849</v>
+        <v>133383829</v>
       </c>
       <c r="B65" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8127,10 +8131,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635737</v>
+        <v>635584</v>
       </c>
       <c r="R65" t="n">
-        <v>6998616</v>
+        <v>6998640</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -8162,7 +8166,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8172,12 +8176,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8186,6 +8185,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8204,10 +8204,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133381516</v>
+        <v>133383840</v>
       </c>
       <c r="B66" t="n">
-        <v>57145</v>
+        <v>91881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8215,45 +8215,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635613</v>
+        <v>635687</v>
       </c>
       <c r="R66" t="n">
-        <v>6998551</v>
+        <v>6998644</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8282,7 +8274,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8292,12 +8284,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre spillning med tarmtömning.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8312,60 +8299,63 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133383840</v>
+        <v>133381507</v>
       </c>
       <c r="B67" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>635687</v>
+        <v>635729</v>
       </c>
       <c r="R67" t="n">
-        <v>6998644</v>
+        <v>6998456</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8394,7 +8384,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8404,7 +8394,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8413,55 +8403,76 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133381507</v>
+        <v>133381516</v>
       </c>
       <c r="B68" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8469,10 +8480,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635729</v>
+        <v>635613</v>
       </c>
       <c r="R68" t="n">
-        <v>6998456</v>
+        <v>6998551</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8504,7 +8515,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8514,7 +8525,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre spillning med tarmtömning.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8523,24 +8539,8 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -2309,60 +2309,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133383825</v>
+        <v>133381484</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635595</v>
+        <v>635574</v>
       </c>
       <c r="R16" t="n">
-        <v>6998619</v>
+        <v>6998638</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2391,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2401,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,67 +2398,78 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133381484</v>
+        <v>133383825</v>
       </c>
       <c r="B17" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635574</v>
+        <v>635595</v>
       </c>
       <c r="R17" t="n">
-        <v>6998638</v>
+        <v>6998619</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,18 +2517,19 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383845</v>
+        <v>133383854</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,16 +3602,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635723</v>
+        <v>635783</v>
       </c>
       <c r="R27" t="n">
-        <v>6998687</v>
+        <v>6998545</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,12 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3711,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,16 +3717,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3754,13 +3749,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R28" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3794,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383871</v>
+        <v>133383848</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,37 +3837,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635666</v>
+        <v>635765</v>
       </c>
       <c r="R29" t="n">
-        <v>6998564</v>
+        <v>6998624</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3899,7 +3896,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3909,7 +3906,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3918,24 +3915,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3952,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383835</v>
+        <v>133383871</v>
       </c>
       <c r="B30" t="n">
         <v>79333</v>
@@ -3990,10 +3971,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635674</v>
+        <v>635666</v>
       </c>
       <c r="R30" t="n">
-        <v>6998672</v>
+        <v>6998564</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4025,7 +4006,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4035,7 +4016,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4050,17 +4031,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4078,10 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133381498</v>
+        <v>133383835</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4089,45 +4070,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635811</v>
+        <v>635674</v>
       </c>
       <c r="R31" t="n">
-        <v>6998569</v>
+        <v>6998672</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4156,7 +4132,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4166,12 +4142,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4180,28 +4151,44 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133383848</v>
+        <v>133381498</v>
       </c>
       <c r="B32" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4209,37 +4196,45 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635765</v>
+        <v>635811</v>
       </c>
       <c r="R32" t="n">
-        <v>6998624</v>
+        <v>6998569</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4268,7 +4263,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4278,7 +4273,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4293,12 +4293,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -6082,42 +6082,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133381509</v>
+        <v>133383830</v>
       </c>
       <c r="B48" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6125,13 +6129,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635725</v>
+        <v>635569</v>
       </c>
       <c r="R48" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6160,7 +6164,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6179,25 +6183,26 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381491</v>
+        <v>133381509</v>
       </c>
       <c r="B49" t="n">
         <v>57145</v>
@@ -6230,7 +6235,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6240,10 +6245,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635695</v>
+        <v>635725</v>
       </c>
       <c r="R49" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6275,7 +6280,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6285,7 +6290,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6312,46 +6317,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133383830</v>
+        <v>133381491</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6359,13 +6360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635569</v>
+        <v>635695</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6394,7 +6395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6404,7 +6405,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6413,29 +6414,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383824</v>
+        <v>133383828</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,37 +6443,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635647</v>
+        <v>635586</v>
       </c>
       <c r="R51" t="n">
-        <v>6998562</v>
+        <v>6998633</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6505,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6515,7 +6512,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6524,24 +6521,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6558,10 +6539,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383836</v>
+        <v>133383852</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,37 +6550,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635678</v>
+        <v>635765</v>
       </c>
       <c r="R52" t="n">
-        <v>6998668</v>
+        <v>6998580</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6631,7 +6609,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6641,7 +6619,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6650,24 +6628,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6684,10 +6646,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383844</v>
+        <v>133383824</v>
       </c>
       <c r="B53" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6695,31 +6657,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6727,13 +6684,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635724</v>
+        <v>635647</v>
       </c>
       <c r="R53" t="n">
-        <v>6998682</v>
+        <v>6998562</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6762,7 +6719,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6772,12 +6729,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6786,8 +6738,24 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6804,10 +6772,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383846</v>
+        <v>133383836</v>
       </c>
       <c r="B54" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6815,31 +6783,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6847,13 +6810,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635727</v>
+        <v>635678</v>
       </c>
       <c r="R54" t="n">
-        <v>6998685</v>
+        <v>6998668</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6882,7 +6845,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6892,12 +6855,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6906,8 +6864,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6924,10 +6898,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383828</v>
+        <v>133383844</v>
       </c>
       <c r="B55" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6935,37 +6909,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635586</v>
+        <v>635724</v>
       </c>
       <c r="R55" t="n">
-        <v>6998633</v>
+        <v>6998682</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6994,7 +6976,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7004,7 +6986,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7031,10 +7018,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383852</v>
+        <v>133383846</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7042,37 +7029,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635765</v>
+        <v>635727</v>
       </c>
       <c r="R56" t="n">
-        <v>6998580</v>
+        <v>6998685</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7101,7 +7096,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7111,7 +7106,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383860</v>
+        <v>133383863</v>
       </c>
       <c r="B57" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,31 +7149,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7181,10 +7176,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635875</v>
+        <v>635750</v>
       </c>
       <c r="R57" t="n">
-        <v>6998347</v>
+        <v>6998423</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7216,7 +7211,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7226,12 +7221,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7240,8 +7230,24 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7258,46 +7264,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381487</v>
+        <v>133383860</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7305,13 +7307,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635566</v>
+        <v>635875</v>
       </c>
       <c r="R58" t="n">
-        <v>6998671</v>
+        <v>6998347</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7340,7 +7342,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7350,7 +7352,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7359,56 +7366,60 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133383863</v>
+        <v>133381508</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7416,13 +7427,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635750</v>
+        <v>635708</v>
       </c>
       <c r="R59" t="n">
-        <v>6998423</v>
+        <v>6998507</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7451,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7461,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7470,61 +7481,45 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381508</v>
+        <v>133381482</v>
       </c>
       <c r="B60" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7547,10 +7542,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635708</v>
+        <v>635585</v>
       </c>
       <c r="R60" t="n">
-        <v>6998507</v>
+        <v>6998647</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7582,7 +7577,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7592,7 +7587,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7619,42 +7614,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381482</v>
+        <v>133381487</v>
       </c>
       <c r="B61" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7662,10 +7661,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635585</v>
+        <v>635566</v>
       </c>
       <c r="R61" t="n">
-        <v>6998647</v>
+        <v>6998671</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7697,7 +7696,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7707,7 +7706,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7716,6 +7715,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133381495</v>
+        <v>133381492</v>
       </c>
       <c r="B62" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7767,7 +7767,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635759</v>
+        <v>635679</v>
       </c>
       <c r="R62" t="n">
-        <v>6998610</v>
+        <v>6998680</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7849,10 +7849,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133383849</v>
+        <v>133381495</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7860,16 +7860,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635737</v>
+        <v>635759</v>
       </c>
       <c r="R63" t="n">
-        <v>6998616</v>
+        <v>6998610</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,12 +7937,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7957,44 +7952,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133381492</v>
+        <v>133383849</v>
       </c>
       <c r="B64" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8002,7 +7997,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8012,13 +8007,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635679</v>
+        <v>635737</v>
       </c>
       <c r="R64" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8047,7 +8042,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8057,7 +8052,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8072,12 +8072,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R2" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,82 +764,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R3" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,56 +874,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381481</v>
+        <v>133381485</v>
       </c>
       <c r="B4" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635587</v>
+        <v>635571</v>
       </c>
       <c r="R4" t="n">
-        <v>6998640</v>
+        <v>6998656</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +1003,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1020,32 +1034,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381485</v>
+        <v>133381486</v>
       </c>
       <c r="B5" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635571</v>
+        <v>635569</v>
       </c>
       <c r="R5" t="n">
-        <v>6998656</v>
+        <v>6998651</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,37 +1160,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381486</v>
+        <v>133383841</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635569</v>
+        <v>635692</v>
       </c>
       <c r="R6" t="n">
-        <v>6998651</v>
+        <v>6998659</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,74 +1265,51 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133383841</v>
+        <v>133381481</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635692</v>
+        <v>635587</v>
       </c>
       <c r="R7" t="n">
-        <v>6998659</v>
+        <v>6998640</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,12 +1380,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2309,48 +2309,60 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133381484</v>
+        <v>133383825</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635574</v>
+        <v>635595</v>
       </c>
       <c r="R16" t="n">
-        <v>6998638</v>
+        <v>6998619</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2391,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2401,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,78 +2410,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383825</v>
+        <v>133381484</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635595</v>
+        <v>635574</v>
       </c>
       <c r="R17" t="n">
-        <v>6998619</v>
+        <v>6998638</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2498,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,19 +2518,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,16 +3602,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R27" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383845</v>
+        <v>133383854</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,16 +3722,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3749,13 +3754,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635723</v>
+        <v>635783</v>
       </c>
       <c r="R28" t="n">
-        <v>6998687</v>
+        <v>6998545</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3784,7 +3789,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3794,12 +3799,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383848</v>
+        <v>133383869</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,34 +3837,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635765</v>
+        <v>635723</v>
       </c>
       <c r="R29" t="n">
-        <v>6998624</v>
+        <v>6998486</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3896,7 +3904,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3906,7 +3914,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3933,10 +3941,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383871</v>
+        <v>133383848</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3944,37 +3952,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635666</v>
+        <v>635765</v>
       </c>
       <c r="R30" t="n">
-        <v>6998564</v>
+        <v>6998624</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4006,7 +4011,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4016,7 +4021,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4025,24 +4030,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4059,7 +4048,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383835</v>
+        <v>133383871</v>
       </c>
       <c r="B31" t="n">
         <v>79333</v>
@@ -4097,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635674</v>
+        <v>635666</v>
       </c>
       <c r="R31" t="n">
-        <v>6998672</v>
+        <v>6998564</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4132,7 +4121,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4142,7 +4131,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4157,17 +4146,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4185,10 +4174,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133381498</v>
+        <v>133383835</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4196,45 +4185,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635811</v>
+        <v>635674</v>
       </c>
       <c r="R32" t="n">
-        <v>6998569</v>
+        <v>6998672</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4263,7 +4247,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4273,12 +4257,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4287,50 +4266,66 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133381479</v>
+        <v>133381498</v>
       </c>
       <c r="B33" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4338,20 +4333,20 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635609</v>
+        <v>635811</v>
       </c>
       <c r="R33" t="n">
-        <v>6998605</v>
+        <v>6998569</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4383,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4393,7 +4388,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4420,27 +4420,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133383869</v>
+        <v>133381479</v>
       </c>
       <c r="B34" t="n">
-        <v>56522</v>
+        <v>57145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635723</v>
+        <v>635609</v>
       </c>
       <c r="R34" t="n">
-        <v>6998486</v>
+        <v>6998605</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,12 +4523,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383863</v>
+        <v>133383860</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,26 +7149,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7176,10 +7181,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635750</v>
+        <v>635875</v>
       </c>
       <c r="R57" t="n">
-        <v>6998423</v>
+        <v>6998347</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7211,7 +7216,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7221,7 +7226,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7230,24 +7240,8 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7264,42 +7258,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133383860</v>
+        <v>133381487</v>
       </c>
       <c r="B58" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7307,13 +7305,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635875</v>
+        <v>635566</v>
       </c>
       <c r="R58" t="n">
-        <v>6998347</v>
+        <v>6998671</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,7 +7340,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7352,12 +7350,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7366,60 +7359,56 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381508</v>
+        <v>133383863</v>
       </c>
       <c r="B59" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7427,13 +7416,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635708</v>
+        <v>635750</v>
       </c>
       <c r="R59" t="n">
-        <v>6998507</v>
+        <v>6998423</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7462,7 +7451,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7461,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7481,45 +7470,61 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381482</v>
+        <v>133381508</v>
       </c>
       <c r="B60" t="n">
-        <v>56522</v>
+        <v>57145</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7542,10 +7547,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635585</v>
+        <v>635708</v>
       </c>
       <c r="R60" t="n">
-        <v>6998647</v>
+        <v>6998507</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7577,7 +7582,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7587,7 +7592,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7614,46 +7619,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381487</v>
+        <v>133381482</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7661,10 +7662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635566</v>
+        <v>635585</v>
       </c>
       <c r="R61" t="n">
-        <v>6998671</v>
+        <v>6998647</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7696,7 +7697,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7706,7 +7707,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7715,7 +7716,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133381492</v>
+        <v>133381495</v>
       </c>
       <c r="B62" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7767,7 +7767,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635679</v>
+        <v>635759</v>
       </c>
       <c r="R62" t="n">
-        <v>6998680</v>
+        <v>6998610</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7849,10 +7849,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133381495</v>
+        <v>133383849</v>
       </c>
       <c r="B63" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7860,16 +7860,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635759</v>
+        <v>635737</v>
       </c>
       <c r="R63" t="n">
-        <v>6998610</v>
+        <v>6998616</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,7 +7937,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7952,44 +7957,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B64" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7997,7 +8002,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8007,13 +8012,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R64" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8042,7 +8047,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8052,12 +8057,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8072,12 +8072,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R2" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,69 +767,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R3" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,71 +890,56 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381485</v>
+        <v>133381481</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635571</v>
+        <v>635587</v>
       </c>
       <c r="R4" t="n">
-        <v>6998656</v>
+        <v>6998640</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,21 +1004,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1034,32 +1020,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381486</v>
+        <v>133381485</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635569</v>
+        <v>635571</v>
       </c>
       <c r="R5" t="n">
-        <v>6998651</v>
+        <v>6998656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,46 +1146,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133383841</v>
+        <v>133381486</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,13 +1184,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635692</v>
+        <v>635569</v>
       </c>
       <c r="R6" t="n">
-        <v>6998659</v>
+        <v>6998651</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,51 +1242,74 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133381481</v>
+        <v>133383841</v>
       </c>
       <c r="B7" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635587</v>
+        <v>635692</v>
       </c>
       <c r="R7" t="n">
-        <v>6998640</v>
+        <v>6998659</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,12 +1380,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133381480</v>
+        <v>133383823</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,26 +2547,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2574,13 +2579,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635598</v>
+        <v>635652</v>
       </c>
       <c r="R18" t="n">
-        <v>6998614</v>
+        <v>6998555</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2609,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,44 +2633,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381493</v>
+        <v>133381501</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,37 +2662,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635756</v>
+        <v>635890</v>
       </c>
       <c r="R19" t="n">
-        <v>6998647</v>
+        <v>6998459</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,24 +2748,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2788,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381505</v>
+        <v>133381480</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,21 +2777,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2826,10 +2804,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635742</v>
+        <v>635598</v>
       </c>
       <c r="R20" t="n">
-        <v>6998412</v>
+        <v>6998614</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2861,7 +2839,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2871,7 +2849,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,17 +2864,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2914,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133383823</v>
+        <v>133381493</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,31 +2903,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2957,13 +2930,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635652</v>
+        <v>635756</v>
       </c>
       <c r="R21" t="n">
-        <v>6998555</v>
+        <v>6998647</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2992,7 +2965,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3002,7 +2975,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,28 +2984,44 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381501</v>
+        <v>133381505</v>
       </c>
       <c r="B22" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,42 +3029,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635890</v>
+        <v>635742</v>
       </c>
       <c r="R22" t="n">
-        <v>6998459</v>
+        <v>6998412</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3107,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,7 +3101,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,8 +3110,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3591,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383845</v>
+        <v>133383854</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,16 +3602,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635723</v>
+        <v>635783</v>
       </c>
       <c r="R27" t="n">
-        <v>6998687</v>
+        <v>6998545</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,12 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3711,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,16 +3717,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3754,13 +3749,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R28" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3794,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5009,48 +5009,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133383873</v>
+        <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635593</v>
+        <v>635781</v>
       </c>
       <c r="R39" t="n">
-        <v>6998584</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5089,7 +5092,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5098,28 +5101,44 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5127,40 +5146,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5208,66 +5224,50 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383832</v>
+        <v>133383873</v>
       </c>
       <c r="B41" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635589</v>
+        <v>635593</v>
       </c>
       <c r="R41" t="n">
-        <v>6998667</v>
+        <v>6998584</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383860</v>
+        <v>133383863</v>
       </c>
       <c r="B57" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,31 +7149,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7181,10 +7176,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635875</v>
+        <v>635750</v>
       </c>
       <c r="R57" t="n">
-        <v>6998347</v>
+        <v>6998423</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7216,7 +7211,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7226,12 +7221,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7240,8 +7230,24 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7258,46 +7264,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381487</v>
+        <v>133383860</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7305,13 +7307,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635566</v>
+        <v>635875</v>
       </c>
       <c r="R58" t="n">
-        <v>6998671</v>
+        <v>6998347</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7340,7 +7342,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7350,7 +7352,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7359,56 +7366,60 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133383863</v>
+        <v>133381508</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7416,13 +7427,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635750</v>
+        <v>635708</v>
       </c>
       <c r="R59" t="n">
-        <v>6998423</v>
+        <v>6998507</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7451,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7461,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7470,61 +7481,45 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381508</v>
+        <v>133381482</v>
       </c>
       <c r="B60" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7547,10 +7542,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635708</v>
+        <v>635585</v>
       </c>
       <c r="R60" t="n">
-        <v>6998507</v>
+        <v>6998647</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7582,7 +7577,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7592,7 +7587,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7619,42 +7614,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381482</v>
+        <v>133381487</v>
       </c>
       <c r="B61" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7662,10 +7661,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635585</v>
+        <v>635566</v>
       </c>
       <c r="R61" t="n">
-        <v>6998647</v>
+        <v>6998671</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7697,7 +7696,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7707,7 +7706,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7716,6 +7715,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -2309,60 +2309,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133383825</v>
+        <v>133381484</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635595</v>
+        <v>635574</v>
       </c>
       <c r="R16" t="n">
-        <v>6998619</v>
+        <v>6998638</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2391,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2401,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,67 +2398,78 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133381484</v>
+        <v>133383825</v>
       </c>
       <c r="B17" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635574</v>
+        <v>635595</v>
       </c>
       <c r="R17" t="n">
-        <v>6998638</v>
+        <v>6998619</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,28 +2517,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133383823</v>
+        <v>133381480</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,31 +2547,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2579,13 +2574,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635652</v>
+        <v>635598</v>
       </c>
       <c r="R18" t="n">
-        <v>6998555</v>
+        <v>6998614</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,28 +2628,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381501</v>
+        <v>133381493</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,42 +2673,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635890</v>
+        <v>635756</v>
       </c>
       <c r="R19" t="n">
-        <v>6998459</v>
+        <v>6998647</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2729,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,8 +2754,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2766,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381480</v>
+        <v>133381505</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,21 +2799,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2804,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635598</v>
+        <v>635742</v>
       </c>
       <c r="R20" t="n">
-        <v>6998614</v>
+        <v>6998412</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2839,7 +2861,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2849,7 +2871,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,17 +2886,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2892,10 +2914,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133381493</v>
+        <v>133383823</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,26 +2925,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2930,13 +2957,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635756</v>
+        <v>635652</v>
       </c>
       <c r="R21" t="n">
-        <v>6998647</v>
+        <v>6998555</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2965,7 +2992,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2975,7 +3002,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,44 +3011,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381505</v>
+        <v>133381501</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,37 +3040,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635742</v>
+        <v>635890</v>
       </c>
       <c r="R22" t="n">
-        <v>6998412</v>
+        <v>6998459</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3091,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,24 +3126,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3591,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,16 +3602,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R27" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383845</v>
+        <v>133383854</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,16 +3722,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3749,13 +3754,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635723</v>
+        <v>635783</v>
       </c>
       <c r="R28" t="n">
-        <v>6998687</v>
+        <v>6998545</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3784,7 +3789,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3794,12 +3799,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383869</v>
+        <v>133383848</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>91918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,42 +3837,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635723</v>
+        <v>635765</v>
       </c>
       <c r="R29" t="n">
-        <v>6998486</v>
+        <v>6998624</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3904,7 +3896,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3914,7 +3906,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3941,48 +3933,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383848</v>
+        <v>133381479</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635765</v>
+        <v>635609</v>
       </c>
       <c r="R30" t="n">
-        <v>6998624</v>
+        <v>6998605</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4036,22 +4036,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383871</v>
+        <v>133383869</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4059,26 +4059,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4086,10 +4091,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635666</v>
+        <v>635723</v>
       </c>
       <c r="R31" t="n">
-        <v>6998564</v>
+        <v>6998486</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4121,7 +4126,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4131,7 +4136,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4140,24 +4145,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4174,7 +4163,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133383835</v>
+        <v>133383871</v>
       </c>
       <c r="B32" t="n">
         <v>79333</v>
@@ -4212,10 +4201,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635674</v>
+        <v>635666</v>
       </c>
       <c r="R32" t="n">
-        <v>6998672</v>
+        <v>6998564</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4247,7 +4236,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4257,7 +4246,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4272,17 +4261,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4300,10 +4289,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133381498</v>
+        <v>133383835</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,45 +4300,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635811</v>
+        <v>635674</v>
       </c>
       <c r="R33" t="n">
-        <v>6998569</v>
+        <v>6998672</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4378,7 +4362,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,12 +4372,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4402,50 +4381,66 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133381479</v>
+        <v>133381498</v>
       </c>
       <c r="B34" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4453,20 +4448,20 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635609</v>
+        <v>635811</v>
       </c>
       <c r="R34" t="n">
-        <v>6998605</v>
+        <v>6998569</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4498,7 +4493,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4503,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5009,51 +5009,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133381502</v>
+        <v>133383873</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635781</v>
+        <v>635593</v>
       </c>
       <c r="R39" t="n">
-        <v>6998384</v>
+        <v>6998584</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5082,7 +5079,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5092,7 +5089,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5101,44 +5098,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B40" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5146,37 +5127,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5189,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5199,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5224,50 +5208,66 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383873</v>
+        <v>133383832</v>
       </c>
       <c r="B41" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635593</v>
+        <v>635589</v>
       </c>
       <c r="R41" t="n">
-        <v>6998584</v>
+        <v>6998667</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6082,46 +6082,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133383830</v>
+        <v>133381509</v>
       </c>
       <c r="B48" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6129,13 +6125,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635569</v>
+        <v>635725</v>
       </c>
       <c r="R48" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6164,7 +6160,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6183,26 +6179,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381509</v>
+        <v>133381491</v>
       </c>
       <c r="B49" t="n">
         <v>57145</v>
@@ -6235,7 +6230,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6245,10 +6240,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635725</v>
+        <v>635695</v>
       </c>
       <c r="R49" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6280,7 +6275,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6290,7 +6285,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6317,42 +6312,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133381491</v>
+        <v>133383830</v>
       </c>
       <c r="B50" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6360,13 +6359,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635695</v>
+        <v>635569</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6395,7 +6394,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6405,7 +6404,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6414,18 +6413,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383863</v>
+        <v>133383860</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,26 +7149,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7176,10 +7181,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635750</v>
+        <v>635875</v>
       </c>
       <c r="R57" t="n">
-        <v>6998423</v>
+        <v>6998347</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7211,7 +7216,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7221,7 +7226,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7230,24 +7240,8 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7264,42 +7258,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133383860</v>
+        <v>133381487</v>
       </c>
       <c r="B58" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7307,13 +7305,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635875</v>
+        <v>635566</v>
       </c>
       <c r="R58" t="n">
-        <v>6998347</v>
+        <v>6998671</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,7 +7340,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7352,12 +7350,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7366,60 +7359,56 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381508</v>
+        <v>133383863</v>
       </c>
       <c r="B59" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7427,13 +7416,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635708</v>
+        <v>635750</v>
       </c>
       <c r="R59" t="n">
-        <v>6998507</v>
+        <v>6998423</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7462,7 +7451,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7461,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7481,45 +7470,61 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381482</v>
+        <v>133381508</v>
       </c>
       <c r="B60" t="n">
-        <v>56522</v>
+        <v>57145</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7542,10 +7547,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635585</v>
+        <v>635708</v>
       </c>
       <c r="R60" t="n">
-        <v>6998647</v>
+        <v>6998507</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7577,7 +7582,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7587,7 +7592,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7614,46 +7619,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381487</v>
+        <v>133381482</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7661,10 +7662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635566</v>
+        <v>635585</v>
       </c>
       <c r="R61" t="n">
-        <v>6998671</v>
+        <v>6998647</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7696,7 +7697,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7706,7 +7707,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7715,7 +7716,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>92219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R2" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,82 +764,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>91883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R3" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,54 +874,78 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381481</v>
+        <v>133383841</v>
       </c>
       <c r="B4" t="n">
-        <v>97995</v>
+        <v>99132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635587</v>
+        <v>635692</v>
       </c>
       <c r="R4" t="n">
-        <v>6998640</v>
+        <v>6998659</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,49 +1016,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381485</v>
+        <v>133381481</v>
       </c>
       <c r="B5" t="n">
-        <v>91918</v>
+        <v>97997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635571</v>
+        <v>635587</v>
       </c>
       <c r="R5" t="n">
-        <v>6998656</v>
+        <v>6998640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,21 +1124,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1146,32 +1140,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381486</v>
+        <v>133381485</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635569</v>
+        <v>635571</v>
       </c>
       <c r="R6" t="n">
-        <v>6998651</v>
+        <v>6998656</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,46 +1266,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133383841</v>
+        <v>133381486</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>91883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635692</v>
+        <v>635569</v>
       </c>
       <c r="R7" t="n">
-        <v>6998659</v>
+        <v>6998651</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1362,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>133383833</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>133383858</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2095,32 +2095,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133383870</v>
+        <v>133381484</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>97997</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635705</v>
+        <v>635574</v>
       </c>
       <c r="R14" t="n">
-        <v>6998524</v>
+        <v>6998638</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,57 +2190,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133383839</v>
+        <v>133383825</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>99132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635722</v>
+        <v>635595</v>
       </c>
       <c r="R15" t="n">
-        <v>6998645</v>
+        <v>6998619</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2272,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,6 +2303,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2309,32 +2322,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133381484</v>
+        <v>133383870</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2344,13 +2357,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635574</v>
+        <v>635705</v>
       </c>
       <c r="R16" t="n">
-        <v>6998638</v>
+        <v>6998524</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2402,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,69 +2417,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383825</v>
+        <v>133383839</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635595</v>
+        <v>635722</v>
       </c>
       <c r="R17" t="n">
-        <v>6998619</v>
+        <v>6998645</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2498,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,7 +2518,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133381480</v>
+        <v>133383823</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,26 +2547,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2574,13 +2579,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635598</v>
+        <v>635652</v>
       </c>
       <c r="R18" t="n">
-        <v>6998614</v>
+        <v>6998555</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2609,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,44 +2633,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381493</v>
+        <v>133381501</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,37 +2662,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635756</v>
+        <v>635890</v>
       </c>
       <c r="R19" t="n">
-        <v>6998647</v>
+        <v>6998459</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,24 +2748,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2791,7 +2769,7 @@
         <v>133381505</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2914,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133383823</v>
+        <v>133381480</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,31 +2903,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2957,13 +2930,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635652</v>
+        <v>635598</v>
       </c>
       <c r="R21" t="n">
-        <v>6998555</v>
+        <v>6998614</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2992,7 +2965,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3002,7 +2975,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,28 +2984,44 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381501</v>
+        <v>133381493</v>
       </c>
       <c r="B22" t="n">
-        <v>57955</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,42 +3029,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635890</v>
+        <v>635756</v>
       </c>
       <c r="R22" t="n">
-        <v>6998459</v>
+        <v>6998647</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3107,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,7 +3101,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,8 +3110,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383837</v>
+        <v>133381506</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,37 +3155,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635681</v>
+        <v>635731</v>
       </c>
       <c r="R23" t="n">
-        <v>6998667</v>
+        <v>6998450</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3214,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3227,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,69 +3236,82 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133381506</v>
+        <v>133383859</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>91883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635731</v>
+        <v>635892</v>
       </c>
       <c r="R24" t="n">
-        <v>6998450</v>
+        <v>6998470</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3324,7 +3340,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3350,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3343,44 +3359,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383859</v>
+        <v>133383862</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635892</v>
+        <v>635771</v>
       </c>
       <c r="R25" t="n">
-        <v>6998470</v>
+        <v>6998407</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,45 +3484,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383862</v>
+        <v>133383854</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635771</v>
+        <v>635783</v>
       </c>
       <c r="R26" t="n">
-        <v>6998407</v>
+        <v>6998545</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3554,7 +3562,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3564,7 +3572,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3591,10 +3599,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383845</v>
+        <v>133383837</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,45 +3610,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635723</v>
+        <v>635681</v>
       </c>
       <c r="R27" t="n">
-        <v>6998687</v>
+        <v>6998667</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,12 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3711,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,16 +3717,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3754,13 +3749,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R28" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3794,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383848</v>
+        <v>133383869</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,34 +3837,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635765</v>
+        <v>635723</v>
       </c>
       <c r="R29" t="n">
-        <v>6998624</v>
+        <v>6998486</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3896,7 +3904,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3906,7 +3914,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3933,56 +3941,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133381479</v>
+        <v>133383848</v>
       </c>
       <c r="B30" t="n">
-        <v>57145</v>
+        <v>91920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635609</v>
+        <v>635765</v>
       </c>
       <c r="R30" t="n">
-        <v>6998605</v>
+        <v>6998624</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4036,22 +4036,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383869</v>
+        <v>133381498</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4081,23 +4081,23 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635723</v>
+        <v>635811</v>
       </c>
       <c r="R31" t="n">
-        <v>6998486</v>
+        <v>6998569</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4136,7 +4136,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4151,49 +4156,54 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133383871</v>
+        <v>133381479</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4201,13 +4211,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635666</v>
+        <v>635609</v>
       </c>
       <c r="R32" t="n">
-        <v>6998564</v>
+        <v>6998605</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4236,7 +4246,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4246,7 +4256,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,44 +4265,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383835</v>
+        <v>133383871</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4327,10 +4321,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635674</v>
+        <v>635666</v>
       </c>
       <c r="R33" t="n">
-        <v>6998672</v>
+        <v>6998564</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4362,7 +4356,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4372,7 +4366,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4387,17 +4381,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4415,10 +4409,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133381498</v>
+        <v>133383835</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4426,45 +4420,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635811</v>
+        <v>635674</v>
       </c>
       <c r="R34" t="n">
-        <v>6998569</v>
+        <v>6998672</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4493,7 +4482,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4503,12 +4492,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,28 +4501,44 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133383831</v>
+        <v>133381504</v>
       </c>
       <c r="B35" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,37 +4546,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635587</v>
+        <v>635773</v>
       </c>
       <c r="R35" t="n">
-        <v>6998661</v>
+        <v>6998405</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4605,7 +4608,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4618,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4624,28 +4627,44 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381504</v>
+        <v>133381496</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4680,10 +4699,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635773</v>
+        <v>635761</v>
       </c>
       <c r="R36" t="n">
-        <v>6998405</v>
+        <v>6998603</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4715,7 +4734,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4725,7 +4744,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4740,17 +4759,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4768,10 +4787,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381496</v>
+        <v>133383831</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4779,40 +4798,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635761</v>
+        <v>635587</v>
       </c>
       <c r="R37" t="n">
-        <v>6998603</v>
+        <v>6998661</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4841,7 +4857,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4851,7 +4867,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4860,34 +4876,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5012,7 +5012,7 @@
         <v>133383873</v>
       </c>
       <c r="B39" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91918</v>
+        <v>92219</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5127,40 +5127,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,7 +5186,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5196,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5208,44 +5205,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B41" t="n">
-        <v>92217</v>
+        <v>91920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5253,37 +5234,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R41" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5296,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5306,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,55 +5315,76 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381489</v>
+        <v>133381512</v>
       </c>
       <c r="B42" t="n">
-        <v>92217</v>
+        <v>57145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5387,10 +5392,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635687</v>
+        <v>635708</v>
       </c>
       <c r="R42" t="n">
-        <v>6998661</v>
+        <v>6998578</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5422,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5432,7 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5441,24 +5451,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5475,7 +5469,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381512</v>
+        <v>133381478</v>
       </c>
       <c r="B43" t="n">
         <v>57145</v>
@@ -5508,7 +5502,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5518,10 +5512,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635708</v>
+        <v>635628</v>
       </c>
       <c r="R43" t="n">
-        <v>6998578</v>
+        <v>6998554</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5553,7 +5547,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5563,12 +5557,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5715,42 +5704,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133381478</v>
+        <v>133381489</v>
       </c>
       <c r="B45" t="n">
-        <v>57145</v>
+        <v>92219</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5758,10 +5742,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635628</v>
+        <v>635687</v>
       </c>
       <c r="R45" t="n">
-        <v>6998554</v>
+        <v>6998661</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5793,7 +5777,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5803,7 +5787,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5812,8 +5796,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5830,10 +5830,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133381490</v>
+        <v>133383864</v>
       </c>
       <c r="B46" t="n">
-        <v>92217</v>
+        <v>79334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5868,13 +5868,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>635685</v>
+        <v>635759</v>
       </c>
       <c r="R46" t="n">
-        <v>6998661</v>
+        <v>6998415</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5928,38 +5928,38 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133383864</v>
+        <v>133381490</v>
       </c>
       <c r="B47" t="n">
-        <v>79333</v>
+        <v>92219</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635759</v>
+        <v>635685</v>
       </c>
       <c r="R47" t="n">
-        <v>6998415</v>
+        <v>6998661</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6054,70 +6054,74 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133381509</v>
+        <v>133383830</v>
       </c>
       <c r="B48" t="n">
-        <v>57145</v>
+        <v>99132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6125,13 +6129,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635725</v>
+        <v>635569</v>
       </c>
       <c r="R48" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6160,7 +6164,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6179,25 +6183,26 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381491</v>
+        <v>133381509</v>
       </c>
       <c r="B49" t="n">
         <v>57145</v>
@@ -6230,7 +6235,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6240,10 +6245,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635695</v>
+        <v>635725</v>
       </c>
       <c r="R49" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6275,7 +6280,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6285,7 +6290,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6312,46 +6317,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133383830</v>
+        <v>133381491</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6359,13 +6360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635569</v>
+        <v>635695</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6394,7 +6395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6404,7 +6405,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6413,29 +6414,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383828</v>
+        <v>133383824</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,34 +6443,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635586</v>
+        <v>635647</v>
       </c>
       <c r="R51" t="n">
-        <v>6998633</v>
+        <v>6998562</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6502,7 +6505,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,7 +6515,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6521,8 +6524,24 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6539,10 +6558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383852</v>
+        <v>133383836</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6550,34 +6569,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635765</v>
+        <v>635678</v>
       </c>
       <c r="R52" t="n">
-        <v>6998580</v>
+        <v>6998668</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6609,7 +6631,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6619,7 +6641,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6628,8 +6650,24 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6646,10 +6684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383824</v>
+        <v>133383828</v>
       </c>
       <c r="B53" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6657,37 +6695,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635647</v>
+        <v>635586</v>
       </c>
       <c r="R53" t="n">
-        <v>6998562</v>
+        <v>6998633</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6719,7 +6754,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6729,7 +6764,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6738,24 +6773,8 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6772,10 +6791,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383836</v>
+        <v>133383852</v>
       </c>
       <c r="B54" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6783,37 +6802,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635678</v>
+        <v>635765</v>
       </c>
       <c r="R54" t="n">
-        <v>6998668</v>
+        <v>6998580</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6845,7 +6861,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6855,7 +6871,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6864,24 +6880,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7138,42 +7138,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383860</v>
+        <v>133381487</v>
       </c>
       <c r="B57" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7181,13 +7185,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635875</v>
+        <v>635566</v>
       </c>
       <c r="R57" t="n">
-        <v>6998347</v>
+        <v>6998671</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7216,7 +7220,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7226,12 +7230,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7240,64 +7239,56 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381487</v>
+        <v>133383863</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>79334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7305,13 +7296,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635566</v>
+        <v>635750</v>
       </c>
       <c r="R58" t="n">
-        <v>6998671</v>
+        <v>6998423</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7340,7 +7331,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7350,7 +7341,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7363,25 +7354,40 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133383863</v>
+        <v>133383860</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7389,26 +7395,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7416,10 +7427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635750</v>
+        <v>635875</v>
       </c>
       <c r="R59" t="n">
-        <v>6998423</v>
+        <v>6998347</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -7451,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7461,7 +7472,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7470,24 +7486,8 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7734,10 +7734,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133381495</v>
+        <v>133383849</v>
       </c>
       <c r="B62" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7745,16 +7745,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635759</v>
+        <v>635737</v>
       </c>
       <c r="R62" t="n">
-        <v>6998610</v>
+        <v>6998616</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,7 +7822,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7837,44 +7842,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7882,7 +7887,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7897,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R63" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,12 +7942,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7957,44 +7957,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133381492</v>
+        <v>133381495</v>
       </c>
       <c r="B64" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8002,7 +8002,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635679</v>
+        <v>635759</v>
       </c>
       <c r="R64" t="n">
-        <v>6998680</v>
+        <v>6998610</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8087,7 +8087,7 @@
         <v>133383829</v>
       </c>
       <c r="B65" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>133383840</v>
       </c>
       <c r="B66" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>133381507</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8557,10 +8557,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381513</v>
+        <v>133381515</v>
       </c>
       <c r="B69" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8568,26 +8568,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8595,13 +8600,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635632</v>
+        <v>635614</v>
       </c>
       <c r="R69" t="n">
-        <v>6998603</v>
+        <v>6998564</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8630,7 +8635,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8640,7 +8645,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8649,24 +8654,8 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8683,48 +8672,51 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133383843</v>
+        <v>133381513</v>
       </c>
       <c r="B70" t="n">
-        <v>91881</v>
+        <v>79334</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635701</v>
+        <v>635632</v>
       </c>
       <c r="R70" t="n">
-        <v>6998689</v>
+        <v>6998603</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8753,7 +8745,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8763,7 +8755,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8772,74 +8764,82 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133381515</v>
+        <v>133383843</v>
       </c>
       <c r="B71" t="n">
-        <v>57136</v>
+        <v>91883</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635614</v>
+        <v>635701</v>
       </c>
       <c r="R71" t="n">
-        <v>6998564</v>
+        <v>6998689</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8893,12 +8893,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B2" t="n">
-        <v>92219</v>
+        <v>91883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R2" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,69 +767,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B3" t="n">
-        <v>91883</v>
+        <v>92219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R3" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,80 +890,55 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133383841</v>
+        <v>133381486</v>
       </c>
       <c r="B4" t="n">
-        <v>99132</v>
+        <v>91883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635692</v>
+        <v>635569</v>
       </c>
       <c r="R4" t="n">
-        <v>6998659</v>
+        <v>6998651</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,53 +1004,67 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381481</v>
+        <v>133381485</v>
       </c>
       <c r="B5" t="n">
-        <v>97997</v>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635587</v>
+        <v>635571</v>
       </c>
       <c r="R5" t="n">
-        <v>6998640</v>
+        <v>6998656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,6 +1129,21 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1140,37 +1160,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381485</v>
+        <v>133383841</v>
       </c>
       <c r="B6" t="n">
-        <v>91920</v>
+        <v>99132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635571</v>
+        <v>635692</v>
       </c>
       <c r="R6" t="n">
-        <v>6998656</v>
+        <v>6998659</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,40 +1265,25 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133381486</v>
+        <v>133381481</v>
       </c>
       <c r="B7" t="n">
-        <v>91883</v>
+        <v>97997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,26 +1291,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635569</v>
+        <v>635587</v>
       </c>
       <c r="R7" t="n">
-        <v>6998651</v>
+        <v>6998640</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,21 +1376,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -5349,42 +5349,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381512</v>
+        <v>133381489</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>92219</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5392,10 +5387,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635708</v>
+        <v>635687</v>
       </c>
       <c r="R42" t="n">
-        <v>6998578</v>
+        <v>6998661</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5427,7 +5422,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,12 +5432,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5451,8 +5441,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5469,7 +5475,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381478</v>
+        <v>133381512</v>
       </c>
       <c r="B43" t="n">
         <v>57145</v>
@@ -5502,7 +5508,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5512,10 +5518,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635628</v>
+        <v>635708</v>
       </c>
       <c r="R43" t="n">
-        <v>6998554</v>
+        <v>6998578</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5547,7 +5553,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5557,7 +5563,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5584,7 +5595,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133383867</v>
+        <v>133381478</v>
       </c>
       <c r="B44" t="n">
         <v>57145</v>
@@ -5617,7 +5628,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5627,13 +5638,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635701</v>
+        <v>635628</v>
       </c>
       <c r="R44" t="n">
-        <v>6998483</v>
+        <v>6998554</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5662,7 +5673,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5672,12 +5683,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5692,49 +5698,54 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133381489</v>
+        <v>133383867</v>
       </c>
       <c r="B45" t="n">
-        <v>92219</v>
+        <v>57145</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5742,13 +5753,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635687</v>
+        <v>635701</v>
       </c>
       <c r="R45" t="n">
-        <v>6998661</v>
+        <v>6998483</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5777,7 +5788,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5787,7 +5798,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5796,34 +5812,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6082,46 +6082,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133383830</v>
+        <v>133381509</v>
       </c>
       <c r="B48" t="n">
-        <v>99132</v>
+        <v>57145</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6129,13 +6125,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635569</v>
+        <v>635725</v>
       </c>
       <c r="R48" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6164,7 +6160,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6183,26 +6179,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381509</v>
+        <v>133381491</v>
       </c>
       <c r="B49" t="n">
         <v>57145</v>
@@ -6235,7 +6230,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6245,10 +6240,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635725</v>
+        <v>635695</v>
       </c>
       <c r="R49" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6280,7 +6275,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6290,7 +6285,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6317,42 +6312,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133381491</v>
+        <v>133383830</v>
       </c>
       <c r="B50" t="n">
-        <v>57145</v>
+        <v>99132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6360,13 +6359,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635695</v>
+        <v>635569</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6395,7 +6394,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6405,7 +6404,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6414,28 +6413,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383824</v>
+        <v>133383844</v>
       </c>
       <c r="B51" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,26 +6443,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6470,13 +6475,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635647</v>
+        <v>635724</v>
       </c>
       <c r="R51" t="n">
-        <v>6998562</v>
+        <v>6998682</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6505,7 +6510,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6515,7 +6520,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6524,24 +6534,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6558,10 +6552,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383836</v>
+        <v>133383846</v>
       </c>
       <c r="B52" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,26 +6563,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6596,13 +6595,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635678</v>
+        <v>635727</v>
       </c>
       <c r="R52" t="n">
-        <v>6998668</v>
+        <v>6998685</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6631,7 +6630,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6641,7 +6640,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6650,24 +6654,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6684,10 +6672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383828</v>
+        <v>133383824</v>
       </c>
       <c r="B53" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6695,34 +6683,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635586</v>
+        <v>635647</v>
       </c>
       <c r="R53" t="n">
-        <v>6998633</v>
+        <v>6998562</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6754,7 +6745,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6764,7 +6755,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6773,8 +6764,24 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6791,10 +6798,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383852</v>
+        <v>133383836</v>
       </c>
       <c r="B54" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6802,34 +6809,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635765</v>
+        <v>635678</v>
       </c>
       <c r="R54" t="n">
-        <v>6998580</v>
+        <v>6998668</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6861,7 +6871,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6871,7 +6881,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6880,8 +6890,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6898,10 +6924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383844</v>
+        <v>133383828</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6909,45 +6935,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635724</v>
+        <v>635586</v>
       </c>
       <c r="R55" t="n">
-        <v>6998682</v>
+        <v>6998633</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6976,7 +6994,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6986,12 +7004,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,10 +7031,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383846</v>
+        <v>133383852</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7029,45 +7042,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635727</v>
+        <v>635765</v>
       </c>
       <c r="R56" t="n">
-        <v>6998685</v>
+        <v>6998580</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7096,7 +7101,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7106,12 +7111,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7734,10 +7734,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133383849</v>
+        <v>133381495</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7745,16 +7745,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635737</v>
+        <v>635759</v>
       </c>
       <c r="R62" t="n">
-        <v>6998616</v>
+        <v>6998610</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,12 +7822,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7842,44 +7837,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133381492</v>
+        <v>133383849</v>
       </c>
       <c r="B63" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7887,7 +7882,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7897,13 +7892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635679</v>
+        <v>635737</v>
       </c>
       <c r="R63" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7932,7 +7927,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7942,7 +7937,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7957,44 +7957,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133381495</v>
+        <v>133381492</v>
       </c>
       <c r="B64" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8002,7 +8002,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635759</v>
+        <v>635679</v>
       </c>
       <c r="R64" t="n">
-        <v>6998610</v>
+        <v>6998680</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8557,10 +8557,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381515</v>
+        <v>133381513</v>
       </c>
       <c r="B69" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8568,31 +8568,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8600,13 +8595,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635614</v>
+        <v>635632</v>
       </c>
       <c r="R69" t="n">
-        <v>6998564</v>
+        <v>6998603</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8635,7 +8630,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8645,7 +8640,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8654,8 +8649,24 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8672,51 +8683,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133381513</v>
+        <v>133383843</v>
       </c>
       <c r="B70" t="n">
-        <v>79334</v>
+        <v>91883</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635632</v>
+        <v>635701</v>
       </c>
       <c r="R70" t="n">
-        <v>6998603</v>
+        <v>6998689</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8745,7 +8753,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8755,7 +8763,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8764,82 +8772,74 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133383843</v>
+        <v>133381515</v>
       </c>
       <c r="B71" t="n">
-        <v>91883</v>
+        <v>57136</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635701</v>
+        <v>635614</v>
       </c>
       <c r="R71" t="n">
-        <v>6998689</v>
+        <v>6998564</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8893,12 +8893,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>92219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R2" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,82 +764,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B3" t="n">
-        <v>92219</v>
+        <v>91883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R3" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,18 +874,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1392,48 +1392,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133383833</v>
+        <v>133383855</v>
       </c>
       <c r="B8" t="n">
-        <v>91883</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635598</v>
+        <v>635821</v>
       </c>
       <c r="R8" t="n">
-        <v>6998686</v>
+        <v>6998575</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1480,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133383858</v>
+        <v>133383838</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,26 +1523,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1537,10 +1555,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635878</v>
+        <v>635697</v>
       </c>
       <c r="R9" t="n">
-        <v>6998469</v>
+        <v>6998678</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1572,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1600,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,24 +1614,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1625,56 +1632,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133383855</v>
+        <v>133383833</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>91883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635821</v>
+        <v>635598</v>
       </c>
       <c r="R10" t="n">
-        <v>6998575</v>
+        <v>6998686</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,7 +1702,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1712,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1739,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133383838</v>
+        <v>133383858</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,31 +1750,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1788,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635697</v>
+        <v>635878</v>
       </c>
       <c r="R11" t="n">
-        <v>6998678</v>
+        <v>6998469</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1823,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,8 +1831,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -6082,42 +6082,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133381509</v>
+        <v>133383830</v>
       </c>
       <c r="B48" t="n">
-        <v>57145</v>
+        <v>99132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6125,13 +6129,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635725</v>
+        <v>635569</v>
       </c>
       <c r="R48" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6160,7 +6164,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6179,25 +6183,26 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381491</v>
+        <v>133381509</v>
       </c>
       <c r="B49" t="n">
         <v>57145</v>
@@ -6230,7 +6235,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6240,10 +6245,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635695</v>
+        <v>635725</v>
       </c>
       <c r="R49" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6275,7 +6280,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6285,7 +6290,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6312,46 +6317,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133383830</v>
+        <v>133381491</v>
       </c>
       <c r="B50" t="n">
-        <v>99132</v>
+        <v>57145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6359,13 +6360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635569</v>
+        <v>635695</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6394,7 +6395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6404,7 +6405,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6413,19 +6414,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -7258,10 +7258,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133383863</v>
+        <v>133381482</v>
       </c>
       <c r="B58" t="n">
-        <v>79334</v>
+        <v>56522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7269,26 +7269,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7296,13 +7301,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635750</v>
+        <v>635585</v>
       </c>
       <c r="R58" t="n">
-        <v>6998423</v>
+        <v>6998647</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7331,7 +7336,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7341,7 +7346,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7350,44 +7355,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133383860</v>
+        <v>133383863</v>
       </c>
       <c r="B59" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7395,31 +7384,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7427,10 +7411,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635875</v>
+        <v>635750</v>
       </c>
       <c r="R59" t="n">
-        <v>6998347</v>
+        <v>6998423</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -7462,7 +7446,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,12 +7456,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7486,8 +7465,24 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7504,32 +7499,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381508</v>
+        <v>133383860</v>
       </c>
       <c r="B60" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7537,7 +7532,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7547,13 +7542,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635708</v>
+        <v>635875</v>
       </c>
       <c r="R60" t="n">
-        <v>6998507</v>
+        <v>6998347</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7582,7 +7577,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7592,7 +7587,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7607,39 +7607,39 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381482</v>
+        <v>133381508</v>
       </c>
       <c r="B61" t="n">
-        <v>56522</v>
+        <v>57145</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635585</v>
+        <v>635708</v>
       </c>
       <c r="R61" t="n">
-        <v>6998647</v>
+        <v>6998507</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8557,10 +8557,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381513</v>
+        <v>133381515</v>
       </c>
       <c r="B69" t="n">
-        <v>79334</v>
+        <v>57136</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8568,26 +8568,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8595,13 +8600,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635632</v>
+        <v>635614</v>
       </c>
       <c r="R69" t="n">
-        <v>6998603</v>
+        <v>6998564</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8630,7 +8635,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8640,7 +8645,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8649,24 +8654,8 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8683,48 +8672,51 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133383843</v>
+        <v>133381513</v>
       </c>
       <c r="B70" t="n">
-        <v>91883</v>
+        <v>79334</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635701</v>
+        <v>635632</v>
       </c>
       <c r="R70" t="n">
-        <v>6998689</v>
+        <v>6998603</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8753,7 +8745,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8763,7 +8755,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8772,74 +8764,82 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133381515</v>
+        <v>133383843</v>
       </c>
       <c r="B71" t="n">
-        <v>57136</v>
+        <v>91883</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635614</v>
+        <v>635701</v>
       </c>
       <c r="R71" t="n">
-        <v>6998564</v>
+        <v>6998689</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8893,12 +8893,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133383847</v>
       </c>
       <c r="B2" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133381488</v>
       </c>
       <c r="B3" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,32 +908,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381486</v>
+        <v>133381485</v>
       </c>
       <c r="B4" t="n">
-        <v>91883</v>
+        <v>91928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635569</v>
+        <v>635571</v>
       </c>
       <c r="R4" t="n">
-        <v>6998651</v>
+        <v>6998656</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,32 +1034,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381485</v>
+        <v>133381486</v>
       </c>
       <c r="B5" t="n">
-        <v>91920</v>
+        <v>91891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635571</v>
+        <v>635569</v>
       </c>
       <c r="R5" t="n">
-        <v>6998656</v>
+        <v>6998651</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,44 +1160,36 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133383841</v>
+        <v>133381481</v>
       </c>
       <c r="B6" t="n">
-        <v>99132</v>
+        <v>98005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1207,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635692</v>
+        <v>635587</v>
       </c>
       <c r="R6" t="n">
-        <v>6998659</v>
+        <v>6998640</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,48 +1260,56 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133381481</v>
+        <v>133383841</v>
       </c>
       <c r="B7" t="n">
-        <v>97997</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635587</v>
+        <v>635692</v>
       </c>
       <c r="R7" t="n">
-        <v>6998640</v>
+        <v>6998659</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,12 +1380,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
         <v>133383833</v>
       </c>
       <c r="B10" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1865,32 +1865,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133383857</v>
+        <v>133381503</v>
       </c>
       <c r="B12" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635848</v>
+        <v>635782</v>
       </c>
       <c r="R12" t="n">
-        <v>6998513</v>
+        <v>6998397</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,44 +1968,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133381503</v>
+        <v>133383857</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635782</v>
+        <v>635848</v>
       </c>
       <c r="R13" t="n">
-        <v>6998397</v>
+        <v>6998513</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,44 +2083,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133381484</v>
+        <v>133383870</v>
       </c>
       <c r="B14" t="n">
-        <v>97997</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635574</v>
+        <v>635705</v>
       </c>
       <c r="R14" t="n">
-        <v>6998638</v>
+        <v>6998524</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,69 +2190,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133383825</v>
+        <v>133383839</v>
       </c>
       <c r="B15" t="n">
-        <v>99132</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635595</v>
+        <v>635722</v>
       </c>
       <c r="R15" t="n">
-        <v>6998619</v>
+        <v>6998645</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2284,7 +2272,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2282,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2291,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2322,32 +2309,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133383870</v>
+        <v>133381484</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>98005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2357,13 +2344,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635705</v>
+        <v>635574</v>
       </c>
       <c r="R16" t="n">
-        <v>6998524</v>
+        <v>6998638</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,57 +2404,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383839</v>
+        <v>133383825</v>
       </c>
       <c r="B17" t="n">
-        <v>91920</v>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635722</v>
+        <v>635595</v>
       </c>
       <c r="R17" t="n">
-        <v>6998645</v>
+        <v>6998619</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2499,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,6 +2517,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133383823</v>
+        <v>133381480</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,31 +2547,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2579,13 +2574,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635652</v>
+        <v>635598</v>
       </c>
       <c r="R18" t="n">
-        <v>6998555</v>
+        <v>6998614</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,28 +2628,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381501</v>
+        <v>133381493</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>91928</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,42 +2673,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635890</v>
+        <v>635756</v>
       </c>
       <c r="R19" t="n">
-        <v>6998459</v>
+        <v>6998647</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2729,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,8 +2754,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2766,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381505</v>
+        <v>133383823</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,26 +2799,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2804,13 +2831,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635742</v>
+        <v>635652</v>
       </c>
       <c r="R20" t="n">
-        <v>6998412</v>
+        <v>6998555</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2839,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2849,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,44 +2885,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133381480</v>
+        <v>133381501</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,37 +2914,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635598</v>
+        <v>635890</v>
       </c>
       <c r="R21" t="n">
-        <v>6998614</v>
+        <v>6998459</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2965,7 +2981,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2975,7 +2991,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,24 +3000,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3018,10 +3018,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381493</v>
+        <v>133381505</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635756</v>
+        <v>635742</v>
       </c>
       <c r="R22" t="n">
-        <v>6998647</v>
+        <v>6998412</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133381506</v>
+        <v>133383837</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,40 +3155,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635731</v>
+        <v>635681</v>
       </c>
       <c r="R23" t="n">
-        <v>6998450</v>
+        <v>6998667</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3217,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,7 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,82 +3233,69 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383859</v>
+        <v>133381506</v>
       </c>
       <c r="B24" t="n">
-        <v>91883</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635892</v>
+        <v>635731</v>
       </c>
       <c r="R24" t="n">
-        <v>6998470</v>
+        <v>6998450</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3340,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3350,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3359,28 +3343,44 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383862</v>
+        <v>133383859</v>
       </c>
       <c r="B25" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635771</v>
+        <v>635892</v>
       </c>
       <c r="R25" t="n">
-        <v>6998407</v>
+        <v>6998470</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,53 +3484,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383854</v>
+        <v>133383862</v>
       </c>
       <c r="B26" t="n">
-        <v>57955</v>
+        <v>91891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635783</v>
+        <v>635771</v>
       </c>
       <c r="R26" t="n">
-        <v>6998545</v>
+        <v>6998407</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3562,7 +3554,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3572,7 +3564,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383837</v>
+        <v>133383854</v>
       </c>
       <c r="B27" t="n">
-        <v>91920</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,34 +3602,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635681</v>
+        <v>635783</v>
       </c>
       <c r="R27" t="n">
-        <v>6998667</v>
+        <v>6998545</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383869</v>
+        <v>133383871</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,31 +3837,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3869,10 +3864,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635723</v>
+        <v>635666</v>
       </c>
       <c r="R29" t="n">
-        <v>6998486</v>
+        <v>6998564</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3904,7 +3899,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3914,7 +3909,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3923,8 +3918,24 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3941,10 +3952,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383848</v>
+        <v>133383835</v>
       </c>
       <c r="B30" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,34 +3963,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635765</v>
+        <v>635674</v>
       </c>
       <c r="R30" t="n">
-        <v>6998624</v>
+        <v>6998672</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4011,7 +4025,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4021,7 +4035,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4030,8 +4044,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4048,10 +4078,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133381498</v>
+        <v>133383848</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4059,45 +4089,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635811</v>
+        <v>635765</v>
       </c>
       <c r="R31" t="n">
-        <v>6998569</v>
+        <v>6998624</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4126,7 +4148,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4136,12 +4158,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4156,12 +4173,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4283,10 +4300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383871</v>
+        <v>133381498</v>
       </c>
       <c r="B33" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,40 +4311,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635666</v>
+        <v>635811</v>
       </c>
       <c r="R33" t="n">
-        <v>6998564</v>
+        <v>6998569</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4356,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4366,7 +4388,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4375,44 +4402,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133383835</v>
+        <v>133383869</v>
       </c>
       <c r="B34" t="n">
-        <v>79334</v>
+        <v>56522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4420,26 +4431,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4447,10 +4463,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635674</v>
+        <v>635723</v>
       </c>
       <c r="R34" t="n">
-        <v>6998672</v>
+        <v>6998486</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4482,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4492,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4501,24 +4517,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4535,37 +4535,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381504</v>
+        <v>133381477</v>
       </c>
       <c r="B35" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4573,10 +4578,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635773</v>
+        <v>635611</v>
       </c>
       <c r="R35" t="n">
-        <v>6998405</v>
+        <v>6998529</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4608,7 +4613,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4618,7 +4623,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4627,24 +4632,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4661,10 +4650,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381496</v>
+        <v>133383831</v>
       </c>
       <c r="B36" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4672,40 +4661,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635761</v>
+        <v>635587</v>
       </c>
       <c r="R36" t="n">
-        <v>6998603</v>
+        <v>6998661</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4734,7 +4720,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4744,7 +4730,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4753,44 +4739,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133383831</v>
+        <v>133381504</v>
       </c>
       <c r="B37" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,37 +4768,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635587</v>
+        <v>635773</v>
       </c>
       <c r="R37" t="n">
-        <v>6998661</v>
+        <v>6998405</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4857,7 +4830,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4867,7 +4840,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4876,60 +4849,71 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381477</v>
+        <v>133381496</v>
       </c>
       <c r="B38" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4937,10 +4921,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635611</v>
+        <v>635761</v>
       </c>
       <c r="R38" t="n">
-        <v>6998529</v>
+        <v>6998603</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4972,7 +4956,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4966,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4991,8 +4975,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5012,7 +5012,7 @@
         <v>133383873</v>
       </c>
       <c r="B39" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B40" t="n">
-        <v>92219</v>
+        <v>91928</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5127,37 +5127,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5186,7 +5189,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5196,7 +5199,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5205,28 +5208,44 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B41" t="n">
-        <v>91920</v>
+        <v>92227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5234,40 +5253,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R41" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5296,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5306,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,34 +5331,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5352,7 +5352,7 @@
         <v>133381489</v>
       </c>
       <c r="B42" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381478</v>
+        <v>133383867</v>
       </c>
       <c r="B44" t="n">
         <v>57145</v>
@@ -5628,7 +5628,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5638,13 +5638,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635628</v>
+        <v>635701</v>
       </c>
       <c r="R44" t="n">
-        <v>6998554</v>
+        <v>6998483</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,7 +5683,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5698,19 +5703,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133383867</v>
+        <v>133381478</v>
       </c>
       <c r="B45" t="n">
         <v>57145</v>
@@ -5743,7 +5748,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5753,13 +5758,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635701</v>
+        <v>635628</v>
       </c>
       <c r="R45" t="n">
-        <v>6998483</v>
+        <v>6998554</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5798,12 +5803,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,22 +5818,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133383864</v>
+        <v>133381490</v>
       </c>
       <c r="B46" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5868,13 +5868,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>635759</v>
+        <v>635685</v>
       </c>
       <c r="R46" t="n">
-        <v>6998415</v>
+        <v>6998661</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5928,38 +5928,38 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133381490</v>
+        <v>133383864</v>
       </c>
       <c r="B47" t="n">
-        <v>92219</v>
+        <v>79334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635685</v>
+        <v>635759</v>
       </c>
       <c r="R47" t="n">
-        <v>6998661</v>
+        <v>6998415</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6054,74 +6054,70 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133383830</v>
+        <v>133381509</v>
       </c>
       <c r="B48" t="n">
-        <v>99132</v>
+        <v>57145</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6129,13 +6125,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635569</v>
+        <v>635725</v>
       </c>
       <c r="R48" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6164,7 +6160,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6183,26 +6179,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381509</v>
+        <v>133381491</v>
       </c>
       <c r="B49" t="n">
         <v>57145</v>
@@ -6235,7 +6230,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6245,10 +6240,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635725</v>
+        <v>635695</v>
       </c>
       <c r="R49" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6280,7 +6275,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6290,7 +6285,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6317,42 +6312,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133381491</v>
+        <v>133383830</v>
       </c>
       <c r="B50" t="n">
-        <v>57145</v>
+        <v>99140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6360,13 +6359,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635695</v>
+        <v>635569</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6395,7 +6394,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6405,7 +6404,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6414,28 +6413,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383844</v>
+        <v>133383852</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,45 +6443,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635724</v>
+        <v>635765</v>
       </c>
       <c r="R51" t="n">
-        <v>6998682</v>
+        <v>6998580</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6510,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6520,12 +6512,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6552,10 +6539,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383846</v>
+        <v>133383828</v>
       </c>
       <c r="B52" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6563,45 +6550,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635727</v>
+        <v>635586</v>
       </c>
       <c r="R52" t="n">
-        <v>6998685</v>
+        <v>6998633</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6630,7 +6609,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6640,12 +6619,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6924,10 +6898,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383828</v>
+        <v>133383844</v>
       </c>
       <c r="B55" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6935,37 +6909,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635586</v>
+        <v>635724</v>
       </c>
       <c r="R55" t="n">
-        <v>6998633</v>
+        <v>6998682</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6994,7 +6976,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7004,7 +6986,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7031,10 +7018,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383852</v>
+        <v>133383846</v>
       </c>
       <c r="B56" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7042,37 +7029,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635765</v>
+        <v>635727</v>
       </c>
       <c r="R56" t="n">
-        <v>6998580</v>
+        <v>6998685</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7101,7 +7096,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7111,7 +7106,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,46 +7138,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133381487</v>
+        <v>133381482</v>
       </c>
       <c r="B57" t="n">
-        <v>99132</v>
+        <v>56522</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7185,10 +7181,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635566</v>
+        <v>635585</v>
       </c>
       <c r="R57" t="n">
-        <v>6998671</v>
+        <v>6998647</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7220,7 +7216,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7230,7 +7226,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7239,7 +7235,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7258,42 +7253,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381482</v>
+        <v>133381487</v>
       </c>
       <c r="B58" t="n">
-        <v>56522</v>
+        <v>99140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7301,10 +7300,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635585</v>
+        <v>635566</v>
       </c>
       <c r="R58" t="n">
-        <v>6998647</v>
+        <v>6998671</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7336,7 +7335,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7346,7 +7345,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7355,6 +7354,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133383860</v>
+        <v>133381508</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7532,7 +7532,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7542,13 +7542,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635875</v>
+        <v>635708</v>
       </c>
       <c r="R60" t="n">
-        <v>6998347</v>
+        <v>6998507</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7587,12 +7587,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7607,44 +7602,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381508</v>
+        <v>133383860</v>
       </c>
       <c r="B61" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7652,7 +7647,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7662,13 +7657,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635708</v>
+        <v>635875</v>
       </c>
       <c r="R61" t="n">
-        <v>6998507</v>
+        <v>6998347</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7697,7 +7692,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7707,7 +7702,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7722,22 +7722,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133381495</v>
+        <v>133383849</v>
       </c>
       <c r="B62" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7745,16 +7745,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635759</v>
+        <v>635737</v>
       </c>
       <c r="R62" t="n">
-        <v>6998610</v>
+        <v>6998616</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,7 +7822,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7837,54 +7842,58 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133383849</v>
+        <v>133383829</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7892,10 +7901,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635737</v>
+        <v>635584</v>
       </c>
       <c r="R63" t="n">
-        <v>6998616</v>
+        <v>6998640</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7927,7 +7936,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,12 +7946,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7951,6 +7955,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7969,32 +7974,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133381492</v>
+        <v>133381495</v>
       </c>
       <c r="B64" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8002,7 +8007,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8012,10 +8017,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635679</v>
+        <v>635759</v>
       </c>
       <c r="R64" t="n">
-        <v>6998680</v>
+        <v>6998610</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8047,7 +8052,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8057,7 +8062,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8084,46 +8089,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133383829</v>
+        <v>133381492</v>
       </c>
       <c r="B65" t="n">
-        <v>99132</v>
+        <v>57145</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8131,13 +8132,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635584</v>
+        <v>635679</v>
       </c>
       <c r="R65" t="n">
-        <v>6998640</v>
+        <v>6998680</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8166,7 +8167,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8176,7 +8177,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8185,19 +8186,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8207,7 +8207,7 @@
         <v>133383840</v>
       </c>
       <c r="B66" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8557,10 +8557,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381515</v>
+        <v>133381513</v>
       </c>
       <c r="B69" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8568,31 +8568,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8600,13 +8595,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635614</v>
+        <v>635632</v>
       </c>
       <c r="R69" t="n">
-        <v>6998564</v>
+        <v>6998603</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8635,7 +8630,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8645,7 +8640,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8654,8 +8649,24 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8672,51 +8683,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133381513</v>
+        <v>133383843</v>
       </c>
       <c r="B70" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635632</v>
+        <v>635701</v>
       </c>
       <c r="R70" t="n">
-        <v>6998603</v>
+        <v>6998689</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8745,7 +8753,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8755,7 +8763,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8764,82 +8772,74 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133383843</v>
+        <v>133381515</v>
       </c>
       <c r="B71" t="n">
-        <v>91883</v>
+        <v>57136</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635701</v>
+        <v>635614</v>
       </c>
       <c r="R71" t="n">
-        <v>6998689</v>
+        <v>6998564</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8893,12 +8893,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -1392,56 +1392,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133383855</v>
+        <v>133383833</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>91891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635821</v>
+        <v>635598</v>
       </c>
       <c r="R8" t="n">
-        <v>6998575</v>
+        <v>6998686</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,12 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133383838</v>
+        <v>133383858</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,31 +1510,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1555,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635697</v>
+        <v>635878</v>
       </c>
       <c r="R9" t="n">
-        <v>6998678</v>
+        <v>6998469</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1590,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,12 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,8 +1591,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1632,48 +1625,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133383833</v>
+        <v>133383855</v>
       </c>
       <c r="B10" t="n">
-        <v>91891</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635598</v>
+        <v>635821</v>
       </c>
       <c r="R10" t="n">
-        <v>6998686</v>
+        <v>6998575</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1713,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133383858</v>
+        <v>133383838</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,26 +1756,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1777,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635878</v>
+        <v>635697</v>
       </c>
       <c r="R11" t="n">
-        <v>6998469</v>
+        <v>6998678</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1812,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,24 +1847,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2536,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133381480</v>
+        <v>133383823</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,26 +2547,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2574,13 +2579,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635598</v>
+        <v>635652</v>
       </c>
       <c r="R18" t="n">
-        <v>6998614</v>
+        <v>6998555</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2609,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,44 +2633,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381493</v>
+        <v>133381501</v>
       </c>
       <c r="B19" t="n">
-        <v>91928</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,37 +2662,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635756</v>
+        <v>635890</v>
       </c>
       <c r="R19" t="n">
-        <v>6998647</v>
+        <v>6998459</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,24 +2748,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2788,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133383823</v>
+        <v>133381480</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>91928</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,31 +2777,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2831,13 +2804,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635652</v>
+        <v>635598</v>
       </c>
       <c r="R20" t="n">
-        <v>6998555</v>
+        <v>6998614</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2866,7 +2839,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2849,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,28 +2858,44 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133381501</v>
+        <v>133381493</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>91928</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,42 +2903,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635890</v>
+        <v>635756</v>
       </c>
       <c r="R21" t="n">
-        <v>6998459</v>
+        <v>6998647</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2981,7 +2965,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2991,7 +2975,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,8 +2984,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383837</v>
+        <v>133383845</v>
       </c>
       <c r="B23" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,37 +3155,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635681</v>
+        <v>635723</v>
       </c>
       <c r="R23" t="n">
-        <v>6998667</v>
+        <v>6998687</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3214,7 +3222,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3232,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,10 +3264,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133381506</v>
+        <v>133383837</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,40 +3275,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635731</v>
+        <v>635681</v>
       </c>
       <c r="R24" t="n">
-        <v>6998450</v>
+        <v>6998667</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3324,7 +3334,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3344,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3343,82 +3353,69 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383859</v>
+        <v>133381506</v>
       </c>
       <c r="B25" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635892</v>
+        <v>635731</v>
       </c>
       <c r="R25" t="n">
-        <v>6998470</v>
+        <v>6998450</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3454,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3466,25 +3463,41 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383862</v>
+        <v>133383859</v>
       </c>
       <c r="B26" t="n">
         <v>91891</v>
@@ -3519,10 +3532,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635771</v>
+        <v>635892</v>
       </c>
       <c r="R26" t="n">
-        <v>6998407</v>
+        <v>6998470</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3554,7 +3567,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3564,7 +3577,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3591,53 +3604,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383854</v>
+        <v>133383862</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>91891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635783</v>
+        <v>635771</v>
       </c>
       <c r="R27" t="n">
-        <v>6998545</v>
+        <v>6998407</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3684,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383845</v>
+        <v>133383854</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,16 +3722,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3749,13 +3754,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635723</v>
+        <v>635783</v>
       </c>
       <c r="R28" t="n">
-        <v>6998687</v>
+        <v>6998545</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3784,7 +3789,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3794,12 +3799,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4535,56 +4535,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381477</v>
+        <v>133383831</v>
       </c>
       <c r="B35" t="n">
-        <v>57145</v>
+        <v>91928</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635611</v>
+        <v>635587</v>
       </c>
       <c r="R35" t="n">
-        <v>6998529</v>
+        <v>6998661</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4613,7 +4605,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4623,7 +4615,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,22 +4630,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133383831</v>
+        <v>133381504</v>
       </c>
       <c r="B36" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,37 +4653,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635587</v>
+        <v>635773</v>
       </c>
       <c r="R36" t="n">
-        <v>6998661</v>
+        <v>6998405</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4720,7 +4715,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4730,7 +4725,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4739,25 +4734,41 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381504</v>
+        <v>133381496</v>
       </c>
       <c r="B37" t="n">
         <v>79334</v>
@@ -4795,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635773</v>
+        <v>635761</v>
       </c>
       <c r="R37" t="n">
-        <v>6998405</v>
+        <v>6998603</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4830,7 +4841,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4840,7 +4851,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,17 +4866,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4883,37 +4894,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381496</v>
+        <v>133381477</v>
       </c>
       <c r="B38" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4921,10 +4937,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635761</v>
+        <v>635611</v>
       </c>
       <c r="R38" t="n">
-        <v>6998603</v>
+        <v>6998529</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4956,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4966,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4975,24 +4991,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5009,48 +5009,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133383873</v>
+        <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>91891</v>
+        <v>91928</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635593</v>
+        <v>635781</v>
       </c>
       <c r="R39" t="n">
-        <v>6998584</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5089,7 +5092,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5098,28 +5101,44 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91928</v>
+        <v>92227</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5127,40 +5146,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5208,66 +5224,50 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383832</v>
+        <v>133383873</v>
       </c>
       <c r="B41" t="n">
-        <v>92227</v>
+        <v>91891</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635589</v>
+        <v>635593</v>
       </c>
       <c r="R41" t="n">
-        <v>6998667</v>
+        <v>6998584</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5349,37 +5349,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381489</v>
+        <v>133381478</v>
       </c>
       <c r="B42" t="n">
-        <v>92227</v>
+        <v>57145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5387,10 +5392,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635687</v>
+        <v>635628</v>
       </c>
       <c r="R42" t="n">
-        <v>6998661</v>
+        <v>6998554</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5422,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5432,7 +5437,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5441,24 +5446,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5475,42 +5464,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381512</v>
+        <v>133381489</v>
       </c>
       <c r="B43" t="n">
-        <v>57145</v>
+        <v>92227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5518,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635708</v>
+        <v>635687</v>
       </c>
       <c r="R43" t="n">
-        <v>6998578</v>
+        <v>6998661</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5553,7 +5537,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5563,12 +5547,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5577,8 +5556,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5595,7 +5590,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133383867</v>
+        <v>133381512</v>
       </c>
       <c r="B44" t="n">
         <v>57145</v>
@@ -5628,7 +5623,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5638,13 +5633,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635701</v>
+        <v>635708</v>
       </c>
       <c r="R44" t="n">
-        <v>6998483</v>
+        <v>6998578</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5673,7 +5668,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,12 +5678,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5703,19 +5698,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133381478</v>
+        <v>133383867</v>
       </c>
       <c r="B45" t="n">
         <v>57145</v>
@@ -5748,7 +5743,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5758,13 +5753,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635628</v>
+        <v>635701</v>
       </c>
       <c r="R45" t="n">
-        <v>6998554</v>
+        <v>6998483</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5803,7 +5798,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,12 +5818,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383852</v>
+        <v>133383828</v>
       </c>
       <c r="B51" t="n">
         <v>91928</v>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635765</v>
+        <v>635586</v>
       </c>
       <c r="R51" t="n">
-        <v>6998580</v>
+        <v>6998633</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6539,7 +6539,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383828</v>
+        <v>133383852</v>
       </c>
       <c r="B52" t="n">
         <v>91928</v>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635586</v>
+        <v>635765</v>
       </c>
       <c r="R52" t="n">
-        <v>6998633</v>
+        <v>6998580</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -8204,10 +8204,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133383840</v>
+        <v>133381516</v>
       </c>
       <c r="B66" t="n">
-        <v>91891</v>
+        <v>57145</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8215,37 +8215,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635687</v>
+        <v>635613</v>
       </c>
       <c r="R66" t="n">
-        <v>6998644</v>
+        <v>6998551</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8274,7 +8282,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8284,7 +8292,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre spillning med tarmtömning.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8299,63 +8312,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133381507</v>
+        <v>133383840</v>
       </c>
       <c r="B67" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>635729</v>
+        <v>635687</v>
       </c>
       <c r="R67" t="n">
-        <v>6998456</v>
+        <v>6998644</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8384,7 +8394,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8394,7 +8404,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8403,76 +8413,55 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133381516</v>
+        <v>133381507</v>
       </c>
       <c r="B68" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8480,10 +8469,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635613</v>
+        <v>635729</v>
       </c>
       <c r="R68" t="n">
-        <v>6998551</v>
+        <v>6998456</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8515,7 +8504,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8525,12 +8514,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre spillning med tarmtömning.</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8539,8 +8523,24 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383845</v>
+        <v>133383837</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,45 +3155,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635723</v>
+        <v>635681</v>
       </c>
       <c r="R23" t="n">
-        <v>6998687</v>
+        <v>6998667</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3222,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3232,12 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3264,10 +3251,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383837</v>
+        <v>133381506</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,37 +3262,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635681</v>
+        <v>635731</v>
       </c>
       <c r="R24" t="n">
-        <v>6998667</v>
+        <v>6998450</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3334,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3344,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3353,69 +3343,82 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133381506</v>
+        <v>133383859</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635731</v>
+        <v>635892</v>
       </c>
       <c r="R25" t="n">
-        <v>6998450</v>
+        <v>6998470</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3444,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,7 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3463,41 +3466,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383859</v>
+        <v>133383862</v>
       </c>
       <c r="B26" t="n">
         <v>91891</v>
@@ -3532,10 +3519,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635892</v>
+        <v>635771</v>
       </c>
       <c r="R26" t="n">
-        <v>6998470</v>
+        <v>6998407</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3567,7 +3554,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3577,7 +3564,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3604,45 +3591,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383862</v>
+        <v>133383854</v>
       </c>
       <c r="B27" t="n">
-        <v>91891</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635771</v>
+        <v>635783</v>
       </c>
       <c r="R27" t="n">
-        <v>6998407</v>
+        <v>6998545</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3711,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,16 +3717,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3754,13 +3749,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R28" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3794,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383871</v>
+        <v>133383848</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,37 +3837,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635666</v>
+        <v>635765</v>
       </c>
       <c r="R29" t="n">
-        <v>6998564</v>
+        <v>6998624</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3899,7 +3896,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3909,7 +3906,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3918,24 +3915,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3952,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383835</v>
+        <v>133383871</v>
       </c>
       <c r="B30" t="n">
         <v>79334</v>
@@ -3990,10 +3971,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635674</v>
+        <v>635666</v>
       </c>
       <c r="R30" t="n">
-        <v>6998672</v>
+        <v>6998564</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4025,7 +4006,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4035,7 +4016,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4050,17 +4031,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4078,10 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383848</v>
+        <v>133383835</v>
       </c>
       <c r="B31" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4089,34 +4070,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635765</v>
+        <v>635674</v>
       </c>
       <c r="R31" t="n">
-        <v>6998624</v>
+        <v>6998672</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4148,7 +4132,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4158,7 +4142,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4167,8 +4151,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4300,10 +4300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133381498</v>
+        <v>133383869</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,21 +4311,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4333,23 +4333,23 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635811</v>
+        <v>635723</v>
       </c>
       <c r="R33" t="n">
-        <v>6998569</v>
+        <v>6998486</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,12 +4388,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,22 +4403,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133383869</v>
+        <v>133381498</v>
       </c>
       <c r="B34" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4431,21 +4426,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4453,23 +4448,23 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635723</v>
+        <v>635811</v>
       </c>
       <c r="R34" t="n">
-        <v>6998486</v>
+        <v>6998569</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4493,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4503,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,60 +4523,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133383831</v>
+        <v>133381477</v>
       </c>
       <c r="B35" t="n">
-        <v>91928</v>
+        <v>57145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635587</v>
+        <v>635611</v>
       </c>
       <c r="R35" t="n">
-        <v>6998661</v>
+        <v>6998529</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4605,7 +4613,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4623,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,22 +4638,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381504</v>
+        <v>133383831</v>
       </c>
       <c r="B36" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4653,40 +4661,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635773</v>
+        <v>635587</v>
       </c>
       <c r="R36" t="n">
-        <v>6998405</v>
+        <v>6998661</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4715,7 +4720,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4725,7 +4730,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4734,41 +4739,25 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381496</v>
+        <v>133381504</v>
       </c>
       <c r="B37" t="n">
         <v>79334</v>
@@ -4806,10 +4795,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635761</v>
+        <v>635773</v>
       </c>
       <c r="R37" t="n">
-        <v>6998603</v>
+        <v>6998405</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4841,7 +4830,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4851,7 +4840,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4866,17 +4855,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4894,42 +4883,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381477</v>
+        <v>133381496</v>
       </c>
       <c r="B38" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4937,10 +4921,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635611</v>
+        <v>635761</v>
       </c>
       <c r="R38" t="n">
-        <v>6998529</v>
+        <v>6998603</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4972,7 +4956,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4966,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4991,8 +4975,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5009,51 +5009,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133381502</v>
+        <v>133383873</v>
       </c>
       <c r="B39" t="n">
-        <v>91928</v>
+        <v>91891</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635781</v>
+        <v>635593</v>
       </c>
       <c r="R39" t="n">
-        <v>6998384</v>
+        <v>6998584</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5082,7 +5079,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5092,7 +5089,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5101,44 +5098,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B40" t="n">
-        <v>92227</v>
+        <v>91928</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5146,37 +5127,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5189,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5199,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5224,50 +5208,66 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383873</v>
+        <v>133383832</v>
       </c>
       <c r="B41" t="n">
-        <v>91891</v>
+        <v>92227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635593</v>
+        <v>635589</v>
       </c>
       <c r="R41" t="n">
-        <v>6998584</v>
+        <v>6998667</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -2095,32 +2095,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133383870</v>
+        <v>133381484</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>98005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635705</v>
+        <v>635574</v>
       </c>
       <c r="R14" t="n">
-        <v>6998524</v>
+        <v>6998638</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,57 +2190,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133383839</v>
+        <v>133383825</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635722</v>
+        <v>635595</v>
       </c>
       <c r="R15" t="n">
-        <v>6998645</v>
+        <v>6998619</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2272,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,6 +2303,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2309,32 +2322,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133381484</v>
+        <v>133383870</v>
       </c>
       <c r="B16" t="n">
-        <v>98005</v>
+        <v>91928</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2344,13 +2357,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635574</v>
+        <v>635705</v>
       </c>
       <c r="R16" t="n">
-        <v>6998638</v>
+        <v>6998524</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2402,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,69 +2417,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383825</v>
+        <v>133383839</v>
       </c>
       <c r="B17" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635595</v>
+        <v>635722</v>
       </c>
       <c r="R17" t="n">
-        <v>6998619</v>
+        <v>6998645</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2498,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,7 +2518,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383837</v>
+        <v>133383845</v>
       </c>
       <c r="B23" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,37 +3155,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635681</v>
+        <v>635723</v>
       </c>
       <c r="R23" t="n">
-        <v>6998667</v>
+        <v>6998687</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3214,7 +3222,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3232,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,10 +3264,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133381506</v>
+        <v>133383837</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,40 +3275,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635731</v>
+        <v>635681</v>
       </c>
       <c r="R24" t="n">
-        <v>6998450</v>
+        <v>6998667</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3324,7 +3334,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3344,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3343,82 +3353,69 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383859</v>
+        <v>133381506</v>
       </c>
       <c r="B25" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635892</v>
+        <v>635731</v>
       </c>
       <c r="R25" t="n">
-        <v>6998470</v>
+        <v>6998450</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3447,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3454,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3466,25 +3463,41 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383862</v>
+        <v>133383859</v>
       </c>
       <c r="B26" t="n">
         <v>91891</v>
@@ -3519,10 +3532,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635771</v>
+        <v>635892</v>
       </c>
       <c r="R26" t="n">
-        <v>6998407</v>
+        <v>6998470</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3554,7 +3567,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3564,7 +3577,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3591,53 +3604,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383854</v>
+        <v>133383862</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>91891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635783</v>
+        <v>635771</v>
       </c>
       <c r="R27" t="n">
-        <v>6998545</v>
+        <v>6998407</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3684,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383845</v>
+        <v>133383854</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,16 +3722,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3749,13 +3754,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635723</v>
+        <v>635783</v>
       </c>
       <c r="R28" t="n">
-        <v>6998687</v>
+        <v>6998545</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3784,7 +3789,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3794,12 +3799,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383848</v>
+        <v>133383871</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,34 +3837,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635765</v>
+        <v>635666</v>
       </c>
       <c r="R29" t="n">
-        <v>6998624</v>
+        <v>6998564</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3896,7 +3899,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3906,7 +3909,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3915,8 +3918,24 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3933,7 +3952,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383871</v>
+        <v>133383835</v>
       </c>
       <c r="B30" t="n">
         <v>79334</v>
@@ -3971,10 +3990,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635666</v>
+        <v>635674</v>
       </c>
       <c r="R30" t="n">
-        <v>6998564</v>
+        <v>6998672</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4006,7 +4025,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4016,7 +4035,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4031,17 +4050,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4059,10 +4078,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383835</v>
+        <v>133383848</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4070,37 +4089,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635674</v>
+        <v>635765</v>
       </c>
       <c r="R31" t="n">
-        <v>6998672</v>
+        <v>6998624</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4132,7 +4148,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4142,7 +4158,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4151,24 +4167,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4300,10 +4300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383869</v>
+        <v>133381498</v>
       </c>
       <c r="B33" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,21 +4311,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4333,23 +4333,23 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635723</v>
+        <v>635811</v>
       </c>
       <c r="R33" t="n">
-        <v>6998486</v>
+        <v>6998569</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,7 +4388,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,22 +4408,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133381498</v>
+        <v>133383869</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4426,21 +4431,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4448,23 +4453,23 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635811</v>
+        <v>635723</v>
       </c>
       <c r="R34" t="n">
-        <v>6998569</v>
+        <v>6998486</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4493,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4503,12 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,68 +4523,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381477</v>
+        <v>133383831</v>
       </c>
       <c r="B35" t="n">
-        <v>57145</v>
+        <v>91928</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635611</v>
+        <v>635587</v>
       </c>
       <c r="R35" t="n">
-        <v>6998529</v>
+        <v>6998661</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4613,7 +4605,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4623,7 +4615,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,22 +4630,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133383831</v>
+        <v>133381504</v>
       </c>
       <c r="B36" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,37 +4653,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635587</v>
+        <v>635773</v>
       </c>
       <c r="R36" t="n">
-        <v>6998661</v>
+        <v>6998405</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4720,7 +4715,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4730,7 +4725,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4739,25 +4734,41 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381504</v>
+        <v>133381496</v>
       </c>
       <c r="B37" t="n">
         <v>79334</v>
@@ -4795,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635773</v>
+        <v>635761</v>
       </c>
       <c r="R37" t="n">
-        <v>6998405</v>
+        <v>6998603</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4830,7 +4841,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4840,7 +4851,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,17 +4866,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4883,37 +4894,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381496</v>
+        <v>133381477</v>
       </c>
       <c r="B38" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4921,10 +4937,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635761</v>
+        <v>635611</v>
       </c>
       <c r="R38" t="n">
-        <v>6998603</v>
+        <v>6998529</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4956,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4966,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4975,24 +4991,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5349,42 +5349,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381478</v>
+        <v>133381489</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>92227</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5392,10 +5387,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635628</v>
+        <v>635687</v>
       </c>
       <c r="R42" t="n">
-        <v>6998554</v>
+        <v>6998661</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5427,7 +5422,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,7 +5432,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5446,8 +5441,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5464,37 +5475,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381489</v>
+        <v>133381512</v>
       </c>
       <c r="B43" t="n">
-        <v>92227</v>
+        <v>57145</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5502,10 +5518,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635687</v>
+        <v>635708</v>
       </c>
       <c r="R43" t="n">
-        <v>6998661</v>
+        <v>6998578</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5537,7 +5553,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5547,7 +5563,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5556,24 +5577,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5590,7 +5595,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381512</v>
+        <v>133383867</v>
       </c>
       <c r="B44" t="n">
         <v>57145</v>
@@ -5623,7 +5628,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5633,13 +5638,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635708</v>
+        <v>635701</v>
       </c>
       <c r="R44" t="n">
-        <v>6998578</v>
+        <v>6998483</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5668,7 +5673,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5678,12 +5683,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5698,19 +5703,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133383867</v>
+        <v>133381478</v>
       </c>
       <c r="B45" t="n">
         <v>57145</v>
@@ -5743,7 +5748,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5753,13 +5758,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635701</v>
+        <v>635628</v>
       </c>
       <c r="R45" t="n">
-        <v>6998483</v>
+        <v>6998554</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5798,12 +5803,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,12 +5818,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133381482</v>
+        <v>133383860</v>
       </c>
       <c r="B57" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,21 +7149,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7171,7 +7171,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7181,13 +7181,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635585</v>
+        <v>635875</v>
       </c>
       <c r="R57" t="n">
-        <v>6998647</v>
+        <v>6998347</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7226,7 +7226,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7241,58 +7246,49 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381487</v>
+        <v>133383863</v>
       </c>
       <c r="B58" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7300,13 +7296,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635566</v>
+        <v>635750</v>
       </c>
       <c r="R58" t="n">
-        <v>6998671</v>
+        <v>6998423</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7335,7 +7331,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7345,7 +7341,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7358,52 +7354,72 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133383863</v>
+        <v>133381508</v>
       </c>
       <c r="B59" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7411,13 +7427,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635750</v>
+        <v>635708</v>
       </c>
       <c r="R59" t="n">
-        <v>6998423</v>
+        <v>6998507</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7446,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7456,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7465,61 +7481,45 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381508</v>
+        <v>133381482</v>
       </c>
       <c r="B60" t="n">
-        <v>57145</v>
+        <v>56522</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635708</v>
+        <v>635585</v>
       </c>
       <c r="R60" t="n">
-        <v>6998507</v>
+        <v>6998647</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7614,42 +7614,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133383860</v>
+        <v>133381487</v>
       </c>
       <c r="B61" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7657,13 +7661,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635875</v>
+        <v>635566</v>
       </c>
       <c r="R61" t="n">
-        <v>6998347</v>
+        <v>6998671</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7692,7 +7696,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7702,12 +7706,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7716,18 +7715,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383845</v>
+        <v>133383837</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,45 +3155,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635723</v>
+        <v>635681</v>
       </c>
       <c r="R23" t="n">
-        <v>6998687</v>
+        <v>6998667</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3222,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3232,12 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3264,10 +3251,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383837</v>
+        <v>133381506</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,37 +3262,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635681</v>
+        <v>635731</v>
       </c>
       <c r="R24" t="n">
-        <v>6998667</v>
+        <v>6998450</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3334,7 +3324,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3344,7 +3334,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3353,69 +3343,82 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133381506</v>
+        <v>133383859</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635731</v>
+        <v>635892</v>
       </c>
       <c r="R25" t="n">
-        <v>6998450</v>
+        <v>6998470</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3444,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,7 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3463,41 +3466,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383859</v>
+        <v>133383862</v>
       </c>
       <c r="B26" t="n">
         <v>91891</v>
@@ -3532,10 +3519,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635892</v>
+        <v>635771</v>
       </c>
       <c r="R26" t="n">
-        <v>6998470</v>
+        <v>6998407</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3567,7 +3554,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3577,7 +3564,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3604,45 +3591,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383862</v>
+        <v>133383854</v>
       </c>
       <c r="B27" t="n">
-        <v>91891</v>
+        <v>57955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635771</v>
+        <v>635783</v>
       </c>
       <c r="R27" t="n">
-        <v>6998407</v>
+        <v>6998545</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3711,10 +3706,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383854</v>
+        <v>133383845</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3722,16 +3717,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3754,13 +3749,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635783</v>
+        <v>635723</v>
       </c>
       <c r="R28" t="n">
-        <v>6998545</v>
+        <v>6998687</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3794,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383871</v>
+        <v>133383848</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,37 +3837,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635666</v>
+        <v>635765</v>
       </c>
       <c r="R29" t="n">
-        <v>6998564</v>
+        <v>6998624</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3899,7 +3896,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3909,7 +3906,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3918,24 +3915,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3952,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383835</v>
+        <v>133383871</v>
       </c>
       <c r="B30" t="n">
         <v>79334</v>
@@ -3990,10 +3971,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635674</v>
+        <v>635666</v>
       </c>
       <c r="R30" t="n">
-        <v>6998672</v>
+        <v>6998564</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4025,7 +4006,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4035,7 +4016,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4050,17 +4031,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4078,10 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383848</v>
+        <v>133383835</v>
       </c>
       <c r="B31" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4089,34 +4070,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635765</v>
+        <v>635674</v>
       </c>
       <c r="R31" t="n">
-        <v>6998624</v>
+        <v>6998672</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4148,7 +4132,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4158,7 +4142,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4167,8 +4151,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4300,10 +4300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133381498</v>
+        <v>133383869</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,21 +4311,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4333,23 +4333,23 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635811</v>
+        <v>635723</v>
       </c>
       <c r="R33" t="n">
-        <v>6998569</v>
+        <v>6998486</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,12 +4388,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,22 +4403,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133383869</v>
+        <v>133381498</v>
       </c>
       <c r="B34" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4431,21 +4426,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4453,23 +4448,23 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635723</v>
+        <v>635811</v>
       </c>
       <c r="R34" t="n">
-        <v>6998486</v>
+        <v>6998569</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4493,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4503,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,12 +4523,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5349,37 +5349,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381489</v>
+        <v>133381478</v>
       </c>
       <c r="B42" t="n">
-        <v>92227</v>
+        <v>57145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5387,10 +5392,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635687</v>
+        <v>635628</v>
       </c>
       <c r="R42" t="n">
-        <v>6998661</v>
+        <v>6998554</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5422,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5432,7 +5437,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5441,24 +5446,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5475,42 +5464,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381512</v>
+        <v>133381489</v>
       </c>
       <c r="B43" t="n">
-        <v>57145</v>
+        <v>92227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5518,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635708</v>
+        <v>635687</v>
       </c>
       <c r="R43" t="n">
-        <v>6998578</v>
+        <v>6998661</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5553,7 +5537,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5563,12 +5547,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5577,8 +5556,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5595,7 +5590,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133383867</v>
+        <v>133381512</v>
       </c>
       <c r="B44" t="n">
         <v>57145</v>
@@ -5628,7 +5623,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5638,13 +5633,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635701</v>
+        <v>635708</v>
       </c>
       <c r="R44" t="n">
-        <v>6998483</v>
+        <v>6998578</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5673,7 +5668,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,12 +5678,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5703,19 +5698,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133381478</v>
+        <v>133383867</v>
       </c>
       <c r="B45" t="n">
         <v>57145</v>
@@ -5748,7 +5743,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5758,13 +5753,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635628</v>
+        <v>635701</v>
       </c>
       <c r="R45" t="n">
-        <v>6998554</v>
+        <v>6998483</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5803,7 +5798,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,12 +5818,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -2095,32 +2095,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133381484</v>
+        <v>133383870</v>
       </c>
       <c r="B14" t="n">
-        <v>98005</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635574</v>
+        <v>635705</v>
       </c>
       <c r="R14" t="n">
-        <v>6998638</v>
+        <v>6998524</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,69 +2190,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133383825</v>
+        <v>133383839</v>
       </c>
       <c r="B15" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635595</v>
+        <v>635722</v>
       </c>
       <c r="R15" t="n">
-        <v>6998619</v>
+        <v>6998645</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2284,7 +2272,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2282,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2291,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2322,32 +2309,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133383870</v>
+        <v>133381484</v>
       </c>
       <c r="B16" t="n">
-        <v>91928</v>
+        <v>98005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2357,13 +2344,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635705</v>
+        <v>635574</v>
       </c>
       <c r="R16" t="n">
-        <v>6998524</v>
+        <v>6998638</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,57 +2404,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383839</v>
+        <v>133383825</v>
       </c>
       <c r="B17" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635722</v>
+        <v>635595</v>
       </c>
       <c r="R17" t="n">
-        <v>6998645</v>
+        <v>6998619</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2499,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,6 +2517,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -5009,48 +5009,51 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133383873</v>
+        <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>91891</v>
+        <v>91928</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635593</v>
+        <v>635781</v>
       </c>
       <c r="R39" t="n">
-        <v>6998584</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5089,7 +5092,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5098,28 +5101,44 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91928</v>
+        <v>92227</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5127,40 +5146,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5208,66 +5224,50 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383832</v>
+        <v>133383873</v>
       </c>
       <c r="B41" t="n">
-        <v>92227</v>
+        <v>91891</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635589</v>
+        <v>635593</v>
       </c>
       <c r="R41" t="n">
-        <v>6998667</v>
+        <v>6998584</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133383847</v>
       </c>
       <c r="B2" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133381488</v>
       </c>
       <c r="B3" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,37 +908,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381485</v>
+        <v>133381481</v>
       </c>
       <c r="B4" t="n">
-        <v>91928</v>
+        <v>98033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635571</v>
+        <v>635587</v>
       </c>
       <c r="R4" t="n">
-        <v>6998656</v>
+        <v>6998640</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,21 +1004,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1034,32 +1020,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381486</v>
+        <v>133381485</v>
       </c>
       <c r="B5" t="n">
-        <v>91891</v>
+        <v>91947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635569</v>
+        <v>635571</v>
       </c>
       <c r="R5" t="n">
-        <v>6998651</v>
+        <v>6998656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381481</v>
+        <v>133381486</v>
       </c>
       <c r="B6" t="n">
-        <v>98005</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,27 +1157,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1199,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635587</v>
+        <v>635569</v>
       </c>
       <c r="R6" t="n">
-        <v>6998640</v>
+        <v>6998651</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,6 +1241,21 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1275,7 +1275,7 @@
         <v>133383841</v>
       </c>
       <c r="B7" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>133383833</v>
       </c>
       <c r="B8" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133383858</v>
+        <v>133383855</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>57965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,26 +1510,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1537,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635878</v>
+        <v>635821</v>
       </c>
       <c r="R9" t="n">
-        <v>6998469</v>
+        <v>6998575</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1572,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1587,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,24 +1601,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1625,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133383855</v>
+        <v>133383858</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>79348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,31 +1630,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1668,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635821</v>
+        <v>635878</v>
       </c>
       <c r="R10" t="n">
-        <v>6998575</v>
+        <v>6998469</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1703,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,8 +1711,24 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1748,7 +1748,7 @@
         <v>133383838</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>133381503</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>133383857</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,32 +2095,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133383870</v>
+        <v>133381484</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>98033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635705</v>
+        <v>635574</v>
       </c>
       <c r="R14" t="n">
-        <v>6998524</v>
+        <v>6998638</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,22 +2190,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133383839</v>
+        <v>133383870</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635722</v>
+        <v>635705</v>
       </c>
       <c r="R15" t="n">
-        <v>6998645</v>
+        <v>6998524</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,48 +2309,60 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133381484</v>
+        <v>133383825</v>
       </c>
       <c r="B16" t="n">
-        <v>98005</v>
+        <v>99168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635574</v>
+        <v>635595</v>
       </c>
       <c r="R16" t="n">
-        <v>6998638</v>
+        <v>6998619</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,7 +2391,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2401,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,75 +2410,64 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383825</v>
+        <v>133383839</v>
       </c>
       <c r="B17" t="n">
-        <v>99140</v>
+        <v>91947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635595</v>
+        <v>635722</v>
       </c>
       <c r="R17" t="n">
-        <v>6998619</v>
+        <v>6998645</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2498,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2508,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,7 +2518,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>133383823</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381501</v>
+        <v>133381480</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>91947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,42 +2662,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635890</v>
+        <v>635598</v>
       </c>
       <c r="R19" t="n">
-        <v>6998459</v>
+        <v>6998614</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2729,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,8 +2743,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2766,10 +2777,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381480</v>
+        <v>133381505</v>
       </c>
       <c r="B20" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,21 +2788,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2804,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635598</v>
+        <v>635742</v>
       </c>
       <c r="R20" t="n">
-        <v>6998614</v>
+        <v>6998412</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2839,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2849,7 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,17 +2875,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2895,7 +2906,7 @@
         <v>133381493</v>
       </c>
       <c r="B21" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,10 +3029,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381505</v>
+        <v>133381501</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>57962</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,37 +3040,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635742</v>
+        <v>635890</v>
       </c>
       <c r="R22" t="n">
-        <v>6998412</v>
+        <v>6998459</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3091,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,24 +3126,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383837</v>
+        <v>133381506</v>
       </c>
       <c r="B23" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,37 +3155,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635681</v>
+        <v>635731</v>
       </c>
       <c r="R23" t="n">
-        <v>6998667</v>
+        <v>6998450</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3214,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3227,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,28 +3236,44 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133381506</v>
+        <v>133383854</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>57962</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,26 +3281,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3289,13 +3313,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635731</v>
+        <v>635783</v>
       </c>
       <c r="R24" t="n">
-        <v>6998450</v>
+        <v>6998545</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3324,7 +3348,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3334,7 +3358,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3343,66 +3367,50 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383859</v>
+        <v>133383837</v>
       </c>
       <c r="B25" t="n">
-        <v>91891</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3412,10 +3420,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635892</v>
+        <v>635681</v>
       </c>
       <c r="R25" t="n">
-        <v>6998470</v>
+        <v>6998667</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3447,7 +3455,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3457,7 +3465,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,48 +3492,56 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383862</v>
+        <v>133383845</v>
       </c>
       <c r="B26" t="n">
-        <v>91891</v>
+        <v>57965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635771</v>
+        <v>635723</v>
       </c>
       <c r="R26" t="n">
-        <v>6998407</v>
+        <v>6998687</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3554,7 +3570,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3564,7 +3580,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3591,53 +3612,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383854</v>
+        <v>133383859</v>
       </c>
       <c r="B27" t="n">
-        <v>57955</v>
+        <v>91910</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635783</v>
+        <v>635892</v>
       </c>
       <c r="R27" t="n">
-        <v>6998545</v>
+        <v>6998470</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3669,7 +3682,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3692,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,56 +3719,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383845</v>
+        <v>133383862</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>91910</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635723</v>
+        <v>635771</v>
       </c>
       <c r="R28" t="n">
-        <v>6998687</v>
+        <v>6998407</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3784,7 +3789,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3794,12 +3799,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383848</v>
+        <v>133381498</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>57965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,37 +3837,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635765</v>
+        <v>635811</v>
       </c>
       <c r="R29" t="n">
-        <v>6998624</v>
+        <v>6998569</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3896,7 +3904,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3906,7 +3914,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,49 +3934,54 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383871</v>
+        <v>133381479</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>57152</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3971,13 +3989,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635666</v>
+        <v>635609</v>
       </c>
       <c r="R30" t="n">
-        <v>6998564</v>
+        <v>6998605</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4006,7 +4024,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4016,7 +4034,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4025,44 +4043,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383835</v>
+        <v>133383871</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4097,10 +4099,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635674</v>
+        <v>635666</v>
       </c>
       <c r="R31" t="n">
-        <v>6998672</v>
+        <v>6998564</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4132,7 +4134,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4142,7 +4144,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4157,17 +4159,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4185,56 +4187,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133381479</v>
+        <v>133383848</v>
       </c>
       <c r="B32" t="n">
-        <v>57145</v>
+        <v>91947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635609</v>
+        <v>635765</v>
       </c>
       <c r="R32" t="n">
-        <v>6998605</v>
+        <v>6998624</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4263,7 +4257,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4273,7 +4267,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4288,22 +4282,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383869</v>
+        <v>133383835</v>
       </c>
       <c r="B33" t="n">
-        <v>56522</v>
+        <v>79348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,31 +4305,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4343,10 +4332,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635723</v>
+        <v>635674</v>
       </c>
       <c r="R33" t="n">
-        <v>6998486</v>
+        <v>6998672</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4378,7 +4367,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,7 +4377,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4397,8 +4386,24 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4415,10 +4420,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133381498</v>
+        <v>133383869</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>56529</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4426,21 +4431,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4448,23 +4453,23 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635811</v>
+        <v>635723</v>
       </c>
       <c r="R34" t="n">
-        <v>6998569</v>
+        <v>6998486</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4493,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4503,12 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,60 +4523,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133383831</v>
+        <v>133381477</v>
       </c>
       <c r="B35" t="n">
-        <v>91928</v>
+        <v>57152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635587</v>
+        <v>635611</v>
       </c>
       <c r="R35" t="n">
-        <v>6998661</v>
+        <v>6998529</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4605,7 +4613,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4623,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,12 +4638,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4645,7 +4653,7 @@
         <v>133381504</v>
       </c>
       <c r="B36" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4771,7 +4779,7 @@
         <v>133381496</v>
       </c>
       <c r="B37" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4894,56 +4902,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381477</v>
+        <v>133383831</v>
       </c>
       <c r="B38" t="n">
-        <v>57145</v>
+        <v>91947</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635611</v>
+        <v>635587</v>
       </c>
       <c r="R38" t="n">
-        <v>6998529</v>
+        <v>6998661</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4997,22 +4997,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B39" t="n">
-        <v>91928</v>
+        <v>92218</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,40 +5020,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R39" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5082,7 +5079,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5092,7 +5089,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5101,66 +5098,50 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383832</v>
+        <v>133383873</v>
       </c>
       <c r="B40" t="n">
-        <v>92227</v>
+        <v>91910</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5170,13 +5151,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635589</v>
+        <v>635593</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998584</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5186,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5196,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5242,48 +5223,51 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383873</v>
+        <v>133381502</v>
       </c>
       <c r="B41" t="n">
-        <v>91891</v>
+        <v>91947</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635593</v>
+        <v>635781</v>
       </c>
       <c r="R41" t="n">
-        <v>6998584</v>
+        <v>6998384</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5296,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5306,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,28 +5315,44 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381478</v>
+        <v>133381512</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635628</v>
+        <v>635708</v>
       </c>
       <c r="R42" t="n">
-        <v>6998554</v>
+        <v>6998578</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,7 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5467,7 +5472,7 @@
         <v>133381489</v>
       </c>
       <c r="B43" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5590,10 +5595,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381512</v>
+        <v>133381478</v>
       </c>
       <c r="B44" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5623,7 +5628,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635708</v>
+        <v>635628</v>
       </c>
       <c r="R44" t="n">
-        <v>6998578</v>
+        <v>6998554</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5668,7 +5673,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5678,12 +5683,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5713,7 +5713,7 @@
         <v>133383867</v>
       </c>
       <c r="B45" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>133381490</v>
       </c>
       <c r="B46" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>133383864</v>
       </c>
       <c r="B47" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>133381509</v>
       </c>
       <c r="B48" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>133381491</v>
       </c>
       <c r="B49" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>133383830</v>
       </c>
       <c r="B50" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6432,10 +6432,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133383828</v>
+        <v>133383844</v>
       </c>
       <c r="B51" t="n">
-        <v>91928</v>
+        <v>57965</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,37 +6443,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635586</v>
+        <v>635724</v>
       </c>
       <c r="R51" t="n">
-        <v>6998633</v>
+        <v>6998682</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6502,7 +6510,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,7 +6520,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6539,10 +6552,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383852</v>
+        <v>133383824</v>
       </c>
       <c r="B52" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6550,34 +6563,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635765</v>
+        <v>635647</v>
       </c>
       <c r="R52" t="n">
-        <v>6998580</v>
+        <v>6998562</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6609,7 +6625,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6619,7 +6635,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6628,8 +6644,24 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6646,10 +6678,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383824</v>
+        <v>133383828</v>
       </c>
       <c r="B53" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6657,37 +6689,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635647</v>
+        <v>635586</v>
       </c>
       <c r="R53" t="n">
-        <v>6998562</v>
+        <v>6998633</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6719,7 +6748,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6729,7 +6758,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6738,24 +6767,8 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6775,7 +6788,7 @@
         <v>133383836</v>
       </c>
       <c r="B54" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6898,10 +6911,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383844</v>
+        <v>133383846</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6931,7 +6944,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6941,13 +6954,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635724</v>
+        <v>635727</v>
       </c>
       <c r="R55" t="n">
-        <v>6998682</v>
+        <v>6998685</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6976,7 +6989,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6986,12 +6999,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,10 +7031,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383846</v>
+        <v>133383852</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>91947</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7029,45 +7042,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635727</v>
+        <v>635765</v>
       </c>
       <c r="R56" t="n">
-        <v>6998685</v>
+        <v>6998580</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7096,7 +7101,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7106,12 +7111,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7138,42 +7138,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383860</v>
+        <v>133381487</v>
       </c>
       <c r="B57" t="n">
-        <v>57958</v>
+        <v>99168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7181,13 +7185,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635875</v>
+        <v>635566</v>
       </c>
       <c r="R57" t="n">
-        <v>6998347</v>
+        <v>6998671</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7216,7 +7220,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7226,12 +7230,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7240,55 +7239,61 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133383863</v>
+        <v>133381508</v>
       </c>
       <c r="B58" t="n">
-        <v>79334</v>
+        <v>57152</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7296,13 +7301,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635750</v>
+        <v>635708</v>
       </c>
       <c r="R58" t="n">
-        <v>6998423</v>
+        <v>6998507</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7331,7 +7336,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7341,7 +7346,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7350,61 +7355,45 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381508</v>
+        <v>133381482</v>
       </c>
       <c r="B59" t="n">
-        <v>57145</v>
+        <v>56529</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7427,10 +7416,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635708</v>
+        <v>635585</v>
       </c>
       <c r="R59" t="n">
-        <v>6998507</v>
+        <v>6998647</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7462,7 +7451,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7461,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7499,10 +7488,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381482</v>
+        <v>133383863</v>
       </c>
       <c r="B60" t="n">
-        <v>56522</v>
+        <v>79348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,31 +7499,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7542,13 +7526,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635585</v>
+        <v>635750</v>
       </c>
       <c r="R60" t="n">
-        <v>6998647</v>
+        <v>6998423</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7577,7 +7561,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7587,7 +7571,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7596,64 +7580,76 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381487</v>
+        <v>133383860</v>
       </c>
       <c r="B61" t="n">
-        <v>99140</v>
+        <v>57965</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7661,13 +7657,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635566</v>
+        <v>635875</v>
       </c>
       <c r="R61" t="n">
-        <v>6998671</v>
+        <v>6998347</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7696,7 +7692,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7706,7 +7702,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7715,61 +7716,64 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133383849</v>
+        <v>133383829</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>99168</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7777,10 +7781,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635737</v>
+        <v>635584</v>
       </c>
       <c r="R62" t="n">
-        <v>6998616</v>
+        <v>6998640</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -7812,7 +7816,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,12 +7826,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7836,6 +7835,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7854,46 +7854,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133383829</v>
+        <v>133383849</v>
       </c>
       <c r="B63" t="n">
-        <v>99140</v>
+        <v>57965</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7901,10 +7897,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635584</v>
+        <v>635737</v>
       </c>
       <c r="R63" t="n">
-        <v>6998640</v>
+        <v>6998616</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7936,7 +7932,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7946,7 +7942,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7955,7 +7956,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>133381495</v>
       </c>
       <c r="B64" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>133381492</v>
       </c>
       <c r="B65" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>133381516</v>
       </c>
       <c r="B66" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8324,48 +8324,51 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133383840</v>
+        <v>133381507</v>
       </c>
       <c r="B67" t="n">
-        <v>91891</v>
+        <v>79348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>635687</v>
+        <v>635729</v>
       </c>
       <c r="R67" t="n">
-        <v>6998644</v>
+        <v>6998456</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8394,7 +8397,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8404,7 +8407,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8413,69 +8416,82 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133381507</v>
+        <v>133383840</v>
       </c>
       <c r="B68" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635729</v>
+        <v>635687</v>
       </c>
       <c r="R68" t="n">
-        <v>6998456</v>
+        <v>6998644</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8504,7 +8520,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8514,7 +8530,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8523,85 +8539,66 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381513</v>
+        <v>133383843</v>
       </c>
       <c r="B69" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635632</v>
+        <v>635701</v>
       </c>
       <c r="R69" t="n">
-        <v>6998603</v>
+        <v>6998689</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8630,7 +8627,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8640,7 +8637,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8649,82 +8646,74 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133383843</v>
+        <v>133381515</v>
       </c>
       <c r="B70" t="n">
-        <v>91891</v>
+        <v>57143</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635701</v>
+        <v>635614</v>
       </c>
       <c r="R70" t="n">
-        <v>6998689</v>
+        <v>6998564</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8753,7 +8742,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8763,7 +8752,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8778,22 +8767,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133381515</v>
+        <v>133381513</v>
       </c>
       <c r="B71" t="n">
-        <v>57136</v>
+        <v>79348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8801,31 +8790,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8833,13 +8817,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635614</v>
+        <v>635632</v>
       </c>
       <c r="R71" t="n">
-        <v>6998564</v>
+        <v>6998603</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8868,7 +8852,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8878,7 +8862,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8887,8 +8871,24 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B2" t="n">
-        <v>92218</v>
+        <v>91910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R2" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,69 +767,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B3" t="n">
-        <v>91910</v>
+        <v>92218</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R3" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,72 +890,55 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381481</v>
+        <v>133381485</v>
       </c>
       <c r="B4" t="n">
-        <v>98033</v>
+        <v>91947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635587</v>
+        <v>635571</v>
       </c>
       <c r="R4" t="n">
-        <v>6998640</v>
+        <v>6998656</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +1003,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1020,37 +1034,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381485</v>
+        <v>133381481</v>
       </c>
       <c r="B5" t="n">
-        <v>91947</v>
+        <v>98033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635571</v>
+        <v>635587</v>
       </c>
       <c r="R5" t="n">
-        <v>6998656</v>
+        <v>6998640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,21 +1130,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -2536,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133383823</v>
+        <v>133381480</v>
       </c>
       <c r="B18" t="n">
-        <v>57962</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,31 +2547,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2579,13 +2574,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635652</v>
+        <v>635598</v>
       </c>
       <c r="R18" t="n">
-        <v>6998555</v>
+        <v>6998614</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,25 +2628,41 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381480</v>
+        <v>133381493</v>
       </c>
       <c r="B19" t="n">
         <v>91947</v>
@@ -2689,10 +2700,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635598</v>
+        <v>635756</v>
       </c>
       <c r="R19" t="n">
-        <v>6998614</v>
+        <v>6998647</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,10 +2914,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133381493</v>
+        <v>133383823</v>
       </c>
       <c r="B21" t="n">
-        <v>91947</v>
+        <v>57962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,26 +2925,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2941,13 +2957,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635756</v>
+        <v>635652</v>
       </c>
       <c r="R21" t="n">
-        <v>6998647</v>
+        <v>6998555</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2976,7 +2992,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2986,7 +3002,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,34 +3011,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4535,56 +4535,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381477</v>
+        <v>133383831</v>
       </c>
       <c r="B35" t="n">
-        <v>57152</v>
+        <v>91947</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635611</v>
+        <v>635587</v>
       </c>
       <c r="R35" t="n">
-        <v>6998529</v>
+        <v>6998661</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4613,7 +4605,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4623,7 +4615,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,49 +4630,54 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381504</v>
+        <v>133381477</v>
       </c>
       <c r="B36" t="n">
-        <v>79348</v>
+        <v>57152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4688,10 +4685,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635773</v>
+        <v>635611</v>
       </c>
       <c r="R36" t="n">
-        <v>6998405</v>
+        <v>6998529</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4723,7 +4720,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4733,7 +4730,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4742,24 +4739,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4776,7 +4757,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381496</v>
+        <v>133381504</v>
       </c>
       <c r="B37" t="n">
         <v>79348</v>
@@ -4814,10 +4795,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635761</v>
+        <v>635773</v>
       </c>
       <c r="R37" t="n">
-        <v>6998603</v>
+        <v>6998405</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4849,7 +4830,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4859,7 +4840,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4874,17 +4855,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4902,10 +4883,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133383831</v>
+        <v>133381496</v>
       </c>
       <c r="B38" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4913,37 +4894,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635587</v>
+        <v>635761</v>
       </c>
       <c r="R38" t="n">
-        <v>6998661</v>
+        <v>6998603</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4972,7 +4956,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4966,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4991,28 +4975,44 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>92218</v>
+        <v>91947</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,37 +5020,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R39" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5089,7 +5092,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5098,50 +5101,66 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383873</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91910</v>
+        <v>92218</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5151,13 +5170,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635593</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998584</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5186,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5196,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5223,51 +5242,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133381502</v>
+        <v>133383873</v>
       </c>
       <c r="B41" t="n">
-        <v>91947</v>
+        <v>91910</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635781</v>
+        <v>635593</v>
       </c>
       <c r="R41" t="n">
-        <v>6998384</v>
+        <v>6998584</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5296,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5306,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,34 +5331,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383836</v>
+        <v>133383846</v>
       </c>
       <c r="B54" t="n">
-        <v>79348</v>
+        <v>57965</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6796,26 +6796,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6823,13 +6828,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635678</v>
+        <v>635727</v>
       </c>
       <c r="R54" t="n">
-        <v>6998668</v>
+        <v>6998685</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6858,7 +6863,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6868,7 +6873,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6877,24 +6887,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6911,10 +6905,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383846</v>
+        <v>133383852</v>
       </c>
       <c r="B55" t="n">
-        <v>57965</v>
+        <v>91947</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6922,45 +6916,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635727</v>
+        <v>635765</v>
       </c>
       <c r="R55" t="n">
-        <v>6998685</v>
+        <v>6998580</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6989,7 +6975,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6999,12 +6985,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7031,10 +7012,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383852</v>
+        <v>133383836</v>
       </c>
       <c r="B56" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7042,34 +7023,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635765</v>
+        <v>635678</v>
       </c>
       <c r="R56" t="n">
-        <v>6998580</v>
+        <v>6998668</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -7101,7 +7085,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7111,7 +7095,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7120,8 +7104,24 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7138,46 +7138,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133381487</v>
+        <v>133383863</v>
       </c>
       <c r="B57" t="n">
-        <v>99168</v>
+        <v>79348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7185,13 +7176,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635566</v>
+        <v>635750</v>
       </c>
       <c r="R57" t="n">
-        <v>6998671</v>
+        <v>6998423</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7220,7 +7211,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7230,7 +7221,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7243,47 +7234,62 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381508</v>
+        <v>133383860</v>
       </c>
       <c r="B58" t="n">
-        <v>57152</v>
+        <v>57965</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7291,7 +7297,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7301,13 +7307,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635708</v>
+        <v>635875</v>
       </c>
       <c r="R58" t="n">
-        <v>6998507</v>
+        <v>6998347</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7336,7 +7342,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7346,7 +7352,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7361,54 +7372,58 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381482</v>
+        <v>133381487</v>
       </c>
       <c r="B59" t="n">
-        <v>56529</v>
+        <v>99168</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7416,10 +7431,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635585</v>
+        <v>635566</v>
       </c>
       <c r="R59" t="n">
-        <v>6998647</v>
+        <v>6998671</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7451,7 +7466,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7461,7 +7476,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7470,6 +7485,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7488,37 +7504,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133383863</v>
+        <v>133381508</v>
       </c>
       <c r="B60" t="n">
-        <v>79348</v>
+        <v>57152</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7526,13 +7547,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635750</v>
+        <v>635708</v>
       </c>
       <c r="R60" t="n">
-        <v>6998423</v>
+        <v>6998507</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7561,7 +7582,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7571,7 +7592,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7580,44 +7601,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133383860</v>
+        <v>133381482</v>
       </c>
       <c r="B61" t="n">
-        <v>57965</v>
+        <v>56529</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7625,21 +7630,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7647,7 +7652,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7657,13 +7662,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635875</v>
+        <v>635585</v>
       </c>
       <c r="R61" t="n">
-        <v>6998347</v>
+        <v>6998647</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7692,7 +7697,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7702,12 +7707,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7722,58 +7722,54 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133383829</v>
+        <v>133381492</v>
       </c>
       <c r="B62" t="n">
-        <v>99168</v>
+        <v>57152</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7781,13 +7777,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635584</v>
+        <v>635679</v>
       </c>
       <c r="R62" t="n">
-        <v>6998640</v>
+        <v>6998680</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7816,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7826,7 +7822,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7835,29 +7831,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133383849</v>
+        <v>133381495</v>
       </c>
       <c r="B63" t="n">
-        <v>57965</v>
+        <v>57962</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7865,16 +7860,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7887,7 +7882,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7897,13 +7892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635737</v>
+        <v>635759</v>
       </c>
       <c r="R63" t="n">
-        <v>6998616</v>
+        <v>6998610</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7932,7 +7927,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7942,12 +7937,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7962,54 +7952,58 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133381495</v>
+        <v>133383829</v>
       </c>
       <c r="B64" t="n">
-        <v>57962</v>
+        <v>99168</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8017,13 +8011,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635759</v>
+        <v>635584</v>
       </c>
       <c r="R64" t="n">
-        <v>6998610</v>
+        <v>6998640</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8052,7 +8046,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8062,7 +8056,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8071,50 +8065,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133381492</v>
+        <v>133383849</v>
       </c>
       <c r="B65" t="n">
-        <v>57152</v>
+        <v>57965</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8122,7 +8117,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -8132,13 +8127,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635679</v>
+        <v>635737</v>
       </c>
       <c r="R65" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8167,7 +8162,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8177,7 +8172,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8192,22 +8192,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133381516</v>
+        <v>133383840</v>
       </c>
       <c r="B66" t="n">
-        <v>57152</v>
+        <v>91910</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8215,45 +8215,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635613</v>
+        <v>635687</v>
       </c>
       <c r="R66" t="n">
-        <v>6998551</v>
+        <v>6998644</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8282,7 +8274,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8292,12 +8284,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre spillning med tarmtömning.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8312,49 +8299,54 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133381507</v>
+        <v>133381516</v>
       </c>
       <c r="B67" t="n">
-        <v>79348</v>
+        <v>57152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8362,10 +8354,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>635729</v>
+        <v>635613</v>
       </c>
       <c r="R67" t="n">
-        <v>6998456</v>
+        <v>6998551</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8397,7 +8389,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8407,7 +8399,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre spillning med tarmtömning.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8416,24 +8413,8 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8450,48 +8431,51 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133383840</v>
+        <v>133381507</v>
       </c>
       <c r="B68" t="n">
-        <v>91910</v>
+        <v>79348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635687</v>
+        <v>635729</v>
       </c>
       <c r="R68" t="n">
-        <v>6998644</v>
+        <v>6998456</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8520,7 +8504,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8530,7 +8514,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8539,66 +8523,90 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133383843</v>
+        <v>133381515</v>
       </c>
       <c r="B69" t="n">
-        <v>91910</v>
+        <v>57143</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635701</v>
+        <v>635614</v>
       </c>
       <c r="R69" t="n">
-        <v>6998689</v>
+        <v>6998564</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8627,7 +8635,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8637,7 +8645,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8652,22 +8660,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133381515</v>
+        <v>133381513</v>
       </c>
       <c r="B70" t="n">
-        <v>57143</v>
+        <v>79348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8675,31 +8683,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8707,13 +8710,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635614</v>
+        <v>635632</v>
       </c>
       <c r="R70" t="n">
-        <v>6998564</v>
+        <v>6998603</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8742,7 +8745,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8752,7 +8755,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8761,8 +8764,24 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8779,51 +8798,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133381513</v>
+        <v>133383843</v>
       </c>
       <c r="B71" t="n">
-        <v>79348</v>
+        <v>91910</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635632</v>
+        <v>635701</v>
       </c>
       <c r="R71" t="n">
-        <v>6998603</v>
+        <v>6998689</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8852,7 +8868,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8862,7 +8878,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8871,34 +8887,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>92228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R2" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,82 +764,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B3" t="n">
-        <v>92218</v>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R3" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,55 +874,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381485</v>
+        <v>133381481</v>
       </c>
       <c r="B4" t="n">
-        <v>91947</v>
+        <v>98043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635571</v>
+        <v>635587</v>
       </c>
       <c r="R4" t="n">
-        <v>6998656</v>
+        <v>6998640</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,21 +1004,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1034,38 +1020,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381481</v>
+        <v>133381485</v>
       </c>
       <c r="B5" t="n">
-        <v>98033</v>
+        <v>91957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635587</v>
+        <v>635571</v>
       </c>
       <c r="R5" t="n">
-        <v>6998640</v>
+        <v>6998656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,6 +1115,21 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,7 +1149,7 @@
         <v>133381486</v>
       </c>
       <c r="B6" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>133383841</v>
       </c>
       <c r="B7" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>133383833</v>
       </c>
       <c r="B8" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>133383855</v>
       </c>
       <c r="B9" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>133383858</v>
       </c>
       <c r="B10" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>133383838</v>
       </c>
       <c r="B11" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,32 +1865,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133381503</v>
+        <v>133383857</v>
       </c>
       <c r="B12" t="n">
-        <v>57152</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635782</v>
+        <v>635848</v>
       </c>
       <c r="R12" t="n">
-        <v>6998397</v>
+        <v>6998513</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,44 +1968,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133383857</v>
+        <v>133381503</v>
       </c>
       <c r="B13" t="n">
-        <v>57962</v>
+        <v>57162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635848</v>
+        <v>635782</v>
       </c>
       <c r="R13" t="n">
-        <v>6998513</v>
+        <v>6998397</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,44 +2083,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133381484</v>
+        <v>133383870</v>
       </c>
       <c r="B14" t="n">
-        <v>98033</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635574</v>
+        <v>635705</v>
       </c>
       <c r="R14" t="n">
-        <v>6998638</v>
+        <v>6998524</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,57 +2190,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133383870</v>
+        <v>133383825</v>
       </c>
       <c r="B15" t="n">
-        <v>91947</v>
+        <v>99178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635705</v>
+        <v>635595</v>
       </c>
       <c r="R15" t="n">
-        <v>6998524</v>
+        <v>6998619</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2272,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,6 +2303,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2309,57 +2322,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133383825</v>
+        <v>133383839</v>
       </c>
       <c r="B16" t="n">
-        <v>99168</v>
+        <v>91957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635595</v>
+        <v>635722</v>
       </c>
       <c r="R16" t="n">
-        <v>6998619</v>
+        <v>6998645</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2391,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2401,7 +2402,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,7 +2411,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2429,32 +2429,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133383839</v>
+        <v>133381484</v>
       </c>
       <c r="B17" t="n">
-        <v>91947</v>
+        <v>98043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635722</v>
+        <v>635574</v>
       </c>
       <c r="R17" t="n">
-        <v>6998645</v>
+        <v>6998638</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,22 +2524,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133381480</v>
+        <v>133383823</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,26 +2547,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2574,13 +2579,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635598</v>
+        <v>635652</v>
       </c>
       <c r="R18" t="n">
-        <v>6998614</v>
+        <v>6998555</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2609,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,34 +2633,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2665,7 +2654,7 @@
         <v>133381493</v>
       </c>
       <c r="B19" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2788,10 +2777,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381505</v>
+        <v>133381480</v>
       </c>
       <c r="B20" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,21 +2788,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2826,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635742</v>
+        <v>635598</v>
       </c>
       <c r="R20" t="n">
-        <v>6998412</v>
+        <v>6998614</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2861,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2871,7 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,17 +2875,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2914,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133383823</v>
+        <v>133381501</v>
       </c>
       <c r="B21" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2947,23 +2936,23 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635652</v>
+        <v>635890</v>
       </c>
       <c r="R21" t="n">
-        <v>6998555</v>
+        <v>6998459</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2992,7 +2981,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3002,7 +2991,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3017,22 +3006,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381501</v>
+        <v>133381505</v>
       </c>
       <c r="B22" t="n">
-        <v>57962</v>
+        <v>79358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,42 +3029,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635890</v>
+        <v>635742</v>
       </c>
       <c r="R22" t="n">
-        <v>6998459</v>
+        <v>6998412</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3107,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,7 +3101,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,8 +3110,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133381506</v>
+        <v>133383854</v>
       </c>
       <c r="B23" t="n">
-        <v>79348</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,26 +3155,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3182,13 +3187,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635731</v>
+        <v>635783</v>
       </c>
       <c r="R23" t="n">
-        <v>6998450</v>
+        <v>6998545</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3217,7 +3222,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,7 +3232,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,44 +3241,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383854</v>
+        <v>133383837</v>
       </c>
       <c r="B24" t="n">
-        <v>57962</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,42 +3270,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635783</v>
+        <v>635681</v>
       </c>
       <c r="R24" t="n">
-        <v>6998545</v>
+        <v>6998667</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3348,7 +3329,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3358,7 +3339,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3385,10 +3366,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383837</v>
+        <v>133383845</v>
       </c>
       <c r="B25" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,37 +3377,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635681</v>
+        <v>635723</v>
       </c>
       <c r="R25" t="n">
-        <v>6998667</v>
+        <v>6998687</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3455,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3465,7 +3454,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3492,56 +3486,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383845</v>
+        <v>133383859</v>
       </c>
       <c r="B26" t="n">
-        <v>57965</v>
+        <v>91920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635723</v>
+        <v>635892</v>
       </c>
       <c r="R26" t="n">
-        <v>6998687</v>
+        <v>6998470</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3570,7 +3556,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3580,12 +3566,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3612,10 +3593,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383859</v>
+        <v>133383862</v>
       </c>
       <c r="B27" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3647,10 +3628,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635892</v>
+        <v>635771</v>
       </c>
       <c r="R27" t="n">
-        <v>6998470</v>
+        <v>6998407</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3682,7 +3663,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3692,7 +3673,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3719,48 +3700,51 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383862</v>
+        <v>133381506</v>
       </c>
       <c r="B28" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635771</v>
+        <v>635731</v>
       </c>
       <c r="R28" t="n">
-        <v>6998407</v>
+        <v>6998450</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3773,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3783,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3808,28 +3792,44 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133381498</v>
+        <v>133383871</v>
       </c>
       <c r="B29" t="n">
-        <v>57965</v>
+        <v>79358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,45 +3837,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635811</v>
+        <v>635666</v>
       </c>
       <c r="R29" t="n">
-        <v>6998569</v>
+        <v>6998564</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3904,7 +3899,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3914,12 +3909,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3928,74 +3918,82 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133381479</v>
+        <v>133383848</v>
       </c>
       <c r="B30" t="n">
-        <v>57152</v>
+        <v>91957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635609</v>
+        <v>635765</v>
       </c>
       <c r="R30" t="n">
-        <v>6998605</v>
+        <v>6998624</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4024,7 +4022,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4034,7 +4032,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4049,22 +4047,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383871</v>
+        <v>133383835</v>
       </c>
       <c r="B31" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4099,10 +4097,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635666</v>
+        <v>635674</v>
       </c>
       <c r="R31" t="n">
-        <v>6998564</v>
+        <v>6998672</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4134,7 +4132,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4144,7 +4142,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4159,17 +4157,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4187,10 +4185,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133383848</v>
+        <v>133383869</v>
       </c>
       <c r="B32" t="n">
-        <v>91947</v>
+        <v>56539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,34 +4196,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635765</v>
+        <v>635723</v>
       </c>
       <c r="R32" t="n">
-        <v>6998624</v>
+        <v>6998486</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4257,7 +4263,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4267,7 +4273,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4294,10 +4300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133383835</v>
+        <v>133381498</v>
       </c>
       <c r="B33" t="n">
-        <v>79348</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,40 +4311,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635674</v>
+        <v>635811</v>
       </c>
       <c r="R33" t="n">
-        <v>6998672</v>
+        <v>6998569</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4367,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4377,7 +4388,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4386,61 +4402,45 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133383869</v>
+        <v>133381479</v>
       </c>
       <c r="B34" t="n">
-        <v>56529</v>
+        <v>57162</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635723</v>
+        <v>635609</v>
       </c>
       <c r="R34" t="n">
-        <v>6998486</v>
+        <v>6998605</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,60 +4523,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133383831</v>
+        <v>133381477</v>
       </c>
       <c r="B35" t="n">
-        <v>91947</v>
+        <v>57162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635587</v>
+        <v>635611</v>
       </c>
       <c r="R35" t="n">
-        <v>6998661</v>
+        <v>6998529</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4605,7 +4613,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4623,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,54 +4638,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381477</v>
+        <v>133381504</v>
       </c>
       <c r="B36" t="n">
-        <v>57152</v>
+        <v>79358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4685,10 +4688,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635611</v>
+        <v>635773</v>
       </c>
       <c r="R36" t="n">
-        <v>6998529</v>
+        <v>6998405</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4720,7 +4723,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4730,7 +4733,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4739,8 +4742,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4757,10 +4776,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381504</v>
+        <v>133381496</v>
       </c>
       <c r="B37" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4795,10 +4814,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635773</v>
+        <v>635761</v>
       </c>
       <c r="R37" t="n">
-        <v>6998405</v>
+        <v>6998603</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4830,7 +4849,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4840,7 +4859,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,17 +4874,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4883,10 +4902,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381496</v>
+        <v>133383831</v>
       </c>
       <c r="B38" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4894,40 +4913,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635761</v>
+        <v>635587</v>
       </c>
       <c r="R38" t="n">
-        <v>6998603</v>
+        <v>6998661</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4956,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4966,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4975,34 +4991,18 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5012,7 +5012,7 @@
         <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>133383873</v>
       </c>
       <c r="B41" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381512</v>
+        <v>133383867</v>
       </c>
       <c r="B42" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635708</v>
+        <v>635701</v>
       </c>
       <c r="R42" t="n">
-        <v>6998578</v>
+        <v>6998483</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5457,49 +5457,54 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381489</v>
+        <v>133381512</v>
       </c>
       <c r="B43" t="n">
-        <v>92218</v>
+        <v>57162</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5507,10 +5512,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635687</v>
+        <v>635708</v>
       </c>
       <c r="R43" t="n">
-        <v>6998661</v>
+        <v>6998578</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5542,7 +5547,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5552,7 +5557,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5561,24 +5571,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5595,42 +5589,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381478</v>
+        <v>133381489</v>
       </c>
       <c r="B44" t="n">
-        <v>57152</v>
+        <v>92228</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5638,10 +5627,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635628</v>
+        <v>635687</v>
       </c>
       <c r="R44" t="n">
-        <v>6998554</v>
+        <v>6998661</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5673,7 +5662,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,7 +5672,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5692,8 +5681,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5710,10 +5715,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133383867</v>
+        <v>133381478</v>
       </c>
       <c r="B45" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5743,7 +5748,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5753,13 +5758,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635701</v>
+        <v>635628</v>
       </c>
       <c r="R45" t="n">
-        <v>6998483</v>
+        <v>6998554</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5798,12 +5803,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,22 +5818,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133381490</v>
+        <v>133383864</v>
       </c>
       <c r="B46" t="n">
-        <v>92218</v>
+        <v>79358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5868,13 +5868,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>635685</v>
+        <v>635759</v>
       </c>
       <c r="R46" t="n">
-        <v>6998661</v>
+        <v>6998415</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5928,38 +5928,38 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133383864</v>
+        <v>133381490</v>
       </c>
       <c r="B47" t="n">
-        <v>79348</v>
+        <v>92228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635759</v>
+        <v>635685</v>
       </c>
       <c r="R47" t="n">
-        <v>6998415</v>
+        <v>6998661</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6054,70 +6054,74 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133381509</v>
+        <v>133383830</v>
       </c>
       <c r="B48" t="n">
-        <v>57152</v>
+        <v>99178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6125,13 +6129,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635725</v>
+        <v>635569</v>
       </c>
       <c r="R48" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6160,7 +6164,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6179,28 +6183,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381491</v>
+        <v>133381509</v>
       </c>
       <c r="B49" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6230,7 +6235,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6240,10 +6245,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635695</v>
+        <v>635725</v>
       </c>
       <c r="R49" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6275,7 +6280,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6285,7 +6290,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6312,46 +6317,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133383830</v>
+        <v>133381491</v>
       </c>
       <c r="B50" t="n">
-        <v>99168</v>
+        <v>57162</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6359,13 +6360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635569</v>
+        <v>635695</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6394,7 +6395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6404,7 +6405,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6413,19 +6414,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6435,7 +6435,7 @@
         <v>133383844</v>
       </c>
       <c r="B51" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>133383824</v>
       </c>
       <c r="B52" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>133383828</v>
       </c>
       <c r="B53" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383846</v>
+        <v>133383836</v>
       </c>
       <c r="B54" t="n">
-        <v>57965</v>
+        <v>79358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6796,31 +6796,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6828,13 +6823,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635727</v>
+        <v>635678</v>
       </c>
       <c r="R54" t="n">
-        <v>6998685</v>
+        <v>6998668</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6863,7 +6858,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6873,12 +6868,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6887,8 +6877,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6905,10 +6911,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383852</v>
+        <v>133383846</v>
       </c>
       <c r="B55" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,37 +6922,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635765</v>
+        <v>635727</v>
       </c>
       <c r="R55" t="n">
-        <v>6998580</v>
+        <v>6998685</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6975,7 +6989,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6985,7 +6999,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7012,10 +7031,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133383836</v>
+        <v>133383852</v>
       </c>
       <c r="B56" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7023,37 +7042,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635678</v>
+        <v>635765</v>
       </c>
       <c r="R56" t="n">
-        <v>6998668</v>
+        <v>6998580</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -7085,7 +7101,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7095,7 +7111,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7104,24 +7120,8 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7138,37 +7138,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383863</v>
+        <v>133381487</v>
       </c>
       <c r="B57" t="n">
-        <v>79348</v>
+        <v>99178</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7176,13 +7185,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635750</v>
+        <v>635566</v>
       </c>
       <c r="R57" t="n">
-        <v>6998423</v>
+        <v>6998671</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7211,7 +7220,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7221,7 +7230,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7234,62 +7243,47 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133383860</v>
+        <v>133381508</v>
       </c>
       <c r="B58" t="n">
-        <v>57965</v>
+        <v>57162</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7297,7 +7291,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7307,13 +7301,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635875</v>
+        <v>635708</v>
       </c>
       <c r="R58" t="n">
-        <v>6998347</v>
+        <v>6998507</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,7 +7336,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7352,12 +7346,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7372,58 +7361,54 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381487</v>
+        <v>133381482</v>
       </c>
       <c r="B59" t="n">
-        <v>99168</v>
+        <v>56539</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7431,10 +7416,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635566</v>
+        <v>635585</v>
       </c>
       <c r="R59" t="n">
-        <v>6998671</v>
+        <v>6998647</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7466,7 +7451,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7476,7 +7461,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7485,7 +7470,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7504,42 +7488,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381508</v>
+        <v>133383863</v>
       </c>
       <c r="B60" t="n">
-        <v>57152</v>
+        <v>79358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7547,13 +7526,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635708</v>
+        <v>635750</v>
       </c>
       <c r="R60" t="n">
-        <v>6998507</v>
+        <v>6998423</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7582,7 +7561,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7592,7 +7571,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7601,28 +7580,44 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381482</v>
+        <v>133383860</v>
       </c>
       <c r="B61" t="n">
-        <v>56529</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7630,21 +7625,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7652,7 +7647,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7662,13 +7657,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635585</v>
+        <v>635875</v>
       </c>
       <c r="R61" t="n">
-        <v>6998647</v>
+        <v>6998347</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7697,7 +7692,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7707,7 +7702,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7722,54 +7722,58 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133381492</v>
+        <v>133383829</v>
       </c>
       <c r="B62" t="n">
-        <v>57152</v>
+        <v>99178</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7777,13 +7781,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635679</v>
+        <v>635584</v>
       </c>
       <c r="R62" t="n">
-        <v>6998680</v>
+        <v>6998640</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7812,7 +7816,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,7 +7826,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7831,28 +7835,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133381495</v>
+        <v>133383849</v>
       </c>
       <c r="B63" t="n">
-        <v>57962</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7860,16 +7865,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7882,7 +7887,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7897,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635759</v>
+        <v>635737</v>
       </c>
       <c r="R63" t="n">
-        <v>6998610</v>
+        <v>6998616</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,7 +7942,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7952,58 +7962,54 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133383829</v>
+        <v>133381495</v>
       </c>
       <c r="B64" t="n">
-        <v>99168</v>
+        <v>57972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8011,13 +8017,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635584</v>
+        <v>635759</v>
       </c>
       <c r="R64" t="n">
-        <v>6998640</v>
+        <v>6998610</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8046,7 +8052,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8056,7 +8062,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8065,51 +8071,50 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B65" t="n">
-        <v>57965</v>
+        <v>57162</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8117,7 +8122,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -8127,13 +8132,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R65" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8162,7 +8167,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8172,12 +8177,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8192,22 +8192,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133383840</v>
+        <v>133381516</v>
       </c>
       <c r="B66" t="n">
-        <v>91910</v>
+        <v>57162</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8215,37 +8215,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>635687</v>
+        <v>635613</v>
       </c>
       <c r="R66" t="n">
-        <v>6998644</v>
+        <v>6998551</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8274,7 +8282,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8284,7 +8292,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre spillning med tarmtömning.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8299,54 +8312,49 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133381516</v>
+        <v>133381507</v>
       </c>
       <c r="B67" t="n">
-        <v>57152</v>
+        <v>79358</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>övernattning</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8354,10 +8362,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>635613</v>
+        <v>635729</v>
       </c>
       <c r="R67" t="n">
-        <v>6998551</v>
+        <v>6998456</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8389,7 +8397,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8399,12 +8407,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre spillning med tarmtömning.</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8413,8 +8416,24 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8431,51 +8450,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133381507</v>
+        <v>133383840</v>
       </c>
       <c r="B68" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>635729</v>
+        <v>635687</v>
       </c>
       <c r="R68" t="n">
-        <v>6998456</v>
+        <v>6998644</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8504,7 +8520,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8514,7 +8530,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8523,90 +8539,66 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381515</v>
+        <v>133383843</v>
       </c>
       <c r="B69" t="n">
-        <v>57143</v>
+        <v>91920</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635614</v>
+        <v>635701</v>
       </c>
       <c r="R69" t="n">
-        <v>6998564</v>
+        <v>6998689</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8635,7 +8627,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8645,7 +8637,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8660,22 +8652,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133381513</v>
+        <v>133381515</v>
       </c>
       <c r="B70" t="n">
-        <v>79348</v>
+        <v>57153</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8683,26 +8675,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8710,13 +8707,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635632</v>
+        <v>635614</v>
       </c>
       <c r="R70" t="n">
-        <v>6998603</v>
+        <v>6998564</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8745,7 +8742,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8755,7 +8752,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8764,24 +8761,8 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8798,48 +8779,51 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133383843</v>
+        <v>133381513</v>
       </c>
       <c r="B71" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635701</v>
+        <v>635632</v>
       </c>
       <c r="R71" t="n">
-        <v>6998689</v>
+        <v>6998603</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8868,7 +8852,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8878,7 +8862,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8887,18 +8871,34 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -2095,32 +2095,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133383870</v>
+        <v>133381484</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>98043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635705</v>
+        <v>635574</v>
       </c>
       <c r="R14" t="n">
-        <v>6998524</v>
+        <v>6998638</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,69 +2190,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133383825</v>
+        <v>133383870</v>
       </c>
       <c r="B15" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635595</v>
+        <v>635705</v>
       </c>
       <c r="R15" t="n">
-        <v>6998619</v>
+        <v>6998524</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2284,7 +2272,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2282,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2291,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2322,45 +2309,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133383839</v>
+        <v>133383825</v>
       </c>
       <c r="B16" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635722</v>
+        <v>635595</v>
       </c>
       <c r="R16" t="n">
-        <v>6998645</v>
+        <v>6998619</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2392,7 +2391,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,7 +2401,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,6 +2410,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2429,32 +2429,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133381484</v>
+        <v>133383839</v>
       </c>
       <c r="B17" t="n">
-        <v>98043</v>
+        <v>91957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635574</v>
+        <v>635722</v>
       </c>
       <c r="R17" t="n">
-        <v>6998638</v>
+        <v>6998645</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,12 +2524,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381493</v>
+        <v>133381480</v>
       </c>
       <c r="B19" t="n">
         <v>91957</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635756</v>
+        <v>635598</v>
       </c>
       <c r="R19" t="n">
-        <v>6998647</v>
+        <v>6998614</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2777,10 +2777,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381480</v>
+        <v>133381501</v>
       </c>
       <c r="B20" t="n">
-        <v>91957</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,37 +2788,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635598</v>
+        <v>635890</v>
       </c>
       <c r="R20" t="n">
-        <v>6998614</v>
+        <v>6998459</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2850,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,24 +2874,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2903,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133381501</v>
+        <v>133381505</v>
       </c>
       <c r="B21" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,42 +2903,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635890</v>
+        <v>635742</v>
       </c>
       <c r="R21" t="n">
-        <v>6998459</v>
+        <v>6998412</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2981,7 +2965,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2991,7 +2975,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,8 +2984,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3018,10 +3018,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381505</v>
+        <v>133381493</v>
       </c>
       <c r="B22" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635742</v>
+        <v>635756</v>
       </c>
       <c r="R22" t="n">
-        <v>6998412</v>
+        <v>6998647</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133383854</v>
+        <v>133381506</v>
       </c>
       <c r="B23" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,31 +3155,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3187,13 +3182,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635783</v>
+        <v>635731</v>
       </c>
       <c r="R23" t="n">
-        <v>6998545</v>
+        <v>6998450</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3222,7 +3217,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3232,7 +3227,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3241,28 +3236,44 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383837</v>
+        <v>133383854</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,34 +3281,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635681</v>
+        <v>635783</v>
       </c>
       <c r="R24" t="n">
-        <v>6998667</v>
+        <v>6998545</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3329,7 +3348,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3339,7 +3358,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383845</v>
+        <v>133383837</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,45 +3396,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635723</v>
+        <v>635681</v>
       </c>
       <c r="R25" t="n">
-        <v>6998687</v>
+        <v>6998667</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3444,7 +3455,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,12 +3465,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3486,48 +3492,56 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383859</v>
+        <v>133383845</v>
       </c>
       <c r="B26" t="n">
-        <v>91920</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635892</v>
+        <v>635723</v>
       </c>
       <c r="R26" t="n">
-        <v>6998470</v>
+        <v>6998687</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3556,7 +3570,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3566,7 +3580,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,7 +3612,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383862</v>
+        <v>133383859</v>
       </c>
       <c r="B27" t="n">
         <v>91920</v>
@@ -3628,10 +3647,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635771</v>
+        <v>635892</v>
       </c>
       <c r="R27" t="n">
-        <v>6998407</v>
+        <v>6998470</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3663,7 +3682,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3673,7 +3692,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3700,51 +3719,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133381506</v>
+        <v>133383862</v>
       </c>
       <c r="B28" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635731</v>
+        <v>635771</v>
       </c>
       <c r="R28" t="n">
-        <v>6998450</v>
+        <v>6998407</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3773,7 +3789,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3783,7 +3799,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3792,34 +3808,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4535,56 +4535,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133381477</v>
+        <v>133383831</v>
       </c>
       <c r="B35" t="n">
-        <v>57162</v>
+        <v>91957</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635611</v>
+        <v>635587</v>
       </c>
       <c r="R35" t="n">
-        <v>6998529</v>
+        <v>6998661</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4613,7 +4605,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4623,7 +4615,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,49 +4630,54 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381504</v>
+        <v>133381477</v>
       </c>
       <c r="B36" t="n">
-        <v>79358</v>
+        <v>57162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4688,10 +4685,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635773</v>
+        <v>635611</v>
       </c>
       <c r="R36" t="n">
-        <v>6998405</v>
+        <v>6998529</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4723,7 +4720,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4733,7 +4730,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4742,24 +4739,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4776,7 +4757,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381496</v>
+        <v>133381504</v>
       </c>
       <c r="B37" t="n">
         <v>79358</v>
@@ -4814,10 +4795,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635761</v>
+        <v>635773</v>
       </c>
       <c r="R37" t="n">
-        <v>6998603</v>
+        <v>6998405</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4849,7 +4830,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4859,7 +4840,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4874,17 +4855,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4902,10 +4883,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133383831</v>
+        <v>133381496</v>
       </c>
       <c r="B38" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4913,37 +4894,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635587</v>
+        <v>635761</v>
       </c>
       <c r="R38" t="n">
-        <v>6998661</v>
+        <v>6998603</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4972,7 +4956,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4982,7 +4966,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4991,28 +4975,44 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B39" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,40 +5020,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R39" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5082,7 +5079,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5092,7 +5089,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5101,66 +5098,50 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383832</v>
+        <v>133383873</v>
       </c>
       <c r="B40" t="n">
-        <v>92228</v>
+        <v>91920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5170,13 +5151,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635589</v>
+        <v>635593</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998584</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5186,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5196,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5242,48 +5223,51 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133383873</v>
+        <v>133381502</v>
       </c>
       <c r="B41" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635593</v>
+        <v>635781</v>
       </c>
       <c r="R41" t="n">
-        <v>6998584</v>
+        <v>6998384</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5312,7 +5296,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5306,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,25 +5315,41 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133383867</v>
+        <v>133381512</v>
       </c>
       <c r="B42" t="n">
         <v>57162</v>
@@ -5382,7 +5382,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635701</v>
+        <v>635708</v>
       </c>
       <c r="R42" t="n">
-        <v>6998483</v>
+        <v>6998578</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5457,54 +5457,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381512</v>
+        <v>133381489</v>
       </c>
       <c r="B43" t="n">
-        <v>57162</v>
+        <v>92228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5512,10 +5507,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635708</v>
+        <v>635687</v>
       </c>
       <c r="R43" t="n">
-        <v>6998578</v>
+        <v>6998661</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5547,7 +5542,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5557,12 +5552,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5571,8 +5561,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5589,37 +5595,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381489</v>
+        <v>133381478</v>
       </c>
       <c r="B44" t="n">
-        <v>92228</v>
+        <v>57162</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5627,10 +5638,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635687</v>
+        <v>635628</v>
       </c>
       <c r="R44" t="n">
-        <v>6998661</v>
+        <v>6998554</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5662,7 +5673,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5672,7 +5683,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5681,24 +5692,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5715,7 +5710,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133381478</v>
+        <v>133383867</v>
       </c>
       <c r="B45" t="n">
         <v>57162</v>
@@ -5748,7 +5743,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5758,13 +5753,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635628</v>
+        <v>635701</v>
       </c>
       <c r="R45" t="n">
-        <v>6998554</v>
+        <v>6998483</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5803,7 +5798,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,22 +5818,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133383864</v>
+        <v>133381490</v>
       </c>
       <c r="B46" t="n">
-        <v>79358</v>
+        <v>92228</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5868,13 +5868,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>635759</v>
+        <v>635685</v>
       </c>
       <c r="R46" t="n">
-        <v>6998415</v>
+        <v>6998661</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5928,38 +5928,38 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133381490</v>
+        <v>133383864</v>
       </c>
       <c r="B47" t="n">
-        <v>92228</v>
+        <v>79358</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635685</v>
+        <v>635759</v>
       </c>
       <c r="R47" t="n">
-        <v>6998661</v>
+        <v>6998415</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6054,74 +6054,70 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133383830</v>
+        <v>133381509</v>
       </c>
       <c r="B48" t="n">
-        <v>99178</v>
+        <v>57162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6129,13 +6125,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635569</v>
+        <v>635725</v>
       </c>
       <c r="R48" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6164,7 +6160,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6183,26 +6179,25 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381509</v>
+        <v>133381491</v>
       </c>
       <c r="B49" t="n">
         <v>57162</v>
@@ -6235,7 +6230,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6245,10 +6240,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635725</v>
+        <v>635695</v>
       </c>
       <c r="R49" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6280,7 +6275,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6290,7 +6285,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6317,42 +6312,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133381491</v>
+        <v>133383830</v>
       </c>
       <c r="B50" t="n">
-        <v>57162</v>
+        <v>99178</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6360,13 +6359,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635695</v>
+        <v>635569</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6395,7 +6394,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6405,7 +6404,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6414,18 +6413,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6552,7 +6552,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383824</v>
+        <v>133383836</v>
       </c>
       <c r="B52" t="n">
         <v>79358</v>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635647</v>
+        <v>635678</v>
       </c>
       <c r="R52" t="n">
-        <v>6998562</v>
+        <v>6998668</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6678,10 +6678,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383828</v>
+        <v>133383846</v>
       </c>
       <c r="B53" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6689,37 +6689,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635586</v>
+        <v>635727</v>
       </c>
       <c r="R53" t="n">
-        <v>6998633</v>
+        <v>6998685</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6748,7 +6756,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6758,7 +6766,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6785,7 +6798,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383836</v>
+        <v>133383824</v>
       </c>
       <c r="B54" t="n">
         <v>79358</v>
@@ -6823,10 +6836,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635678</v>
+        <v>635647</v>
       </c>
       <c r="R54" t="n">
-        <v>6998668</v>
+        <v>6998562</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6858,7 +6871,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6868,7 +6881,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6911,10 +6924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383846</v>
+        <v>133383828</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6922,45 +6935,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635727</v>
+        <v>635586</v>
       </c>
       <c r="R55" t="n">
-        <v>6998685</v>
+        <v>6998633</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6989,7 +6994,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6999,12 +7004,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7138,46 +7138,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133381487</v>
+        <v>133383863</v>
       </c>
       <c r="B57" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7185,13 +7176,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635566</v>
+        <v>635750</v>
       </c>
       <c r="R57" t="n">
-        <v>6998671</v>
+        <v>6998423</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7220,7 +7211,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7230,7 +7221,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7243,47 +7234,62 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133381508</v>
+        <v>133383860</v>
       </c>
       <c r="B58" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7291,7 +7297,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7301,13 +7307,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635708</v>
+        <v>635875</v>
       </c>
       <c r="R58" t="n">
-        <v>6998507</v>
+        <v>6998347</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7336,7 +7342,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7346,7 +7352,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7361,54 +7372,58 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381482</v>
+        <v>133381487</v>
       </c>
       <c r="B59" t="n">
-        <v>56539</v>
+        <v>99178</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7416,10 +7431,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635585</v>
+        <v>635566</v>
       </c>
       <c r="R59" t="n">
-        <v>6998647</v>
+        <v>6998671</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7451,7 +7466,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7461,7 +7476,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7470,6 +7485,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7488,37 +7504,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133383863</v>
+        <v>133381508</v>
       </c>
       <c r="B60" t="n">
-        <v>79358</v>
+        <v>57162</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7526,13 +7547,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635750</v>
+        <v>635708</v>
       </c>
       <c r="R60" t="n">
-        <v>6998423</v>
+        <v>6998507</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7561,7 +7582,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7571,7 +7592,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7580,44 +7601,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133383860</v>
+        <v>133381482</v>
       </c>
       <c r="B61" t="n">
-        <v>57975</v>
+        <v>56539</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7625,21 +7630,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7647,7 +7652,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7657,13 +7662,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635875</v>
+        <v>635585</v>
       </c>
       <c r="R61" t="n">
-        <v>6998347</v>
+        <v>6998647</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7692,7 +7697,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7702,12 +7707,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7722,58 +7722,54 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133383829</v>
+        <v>133381495</v>
       </c>
       <c r="B62" t="n">
-        <v>99178</v>
+        <v>57972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7781,13 +7777,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635584</v>
+        <v>635759</v>
       </c>
       <c r="R62" t="n">
-        <v>6998640</v>
+        <v>6998610</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7816,7 +7812,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7826,7 +7822,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7835,51 +7831,50 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B63" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7887,7 +7882,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7897,13 +7892,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R63" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7932,7 +7927,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7942,12 +7937,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7962,54 +7952,58 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133381495</v>
+        <v>133383829</v>
       </c>
       <c r="B64" t="n">
-        <v>57972</v>
+        <v>99178</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8017,13 +8011,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635759</v>
+        <v>635584</v>
       </c>
       <c r="R64" t="n">
-        <v>6998610</v>
+        <v>6998640</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8052,7 +8046,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8062,7 +8056,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8071,50 +8065,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133381492</v>
+        <v>133383849</v>
       </c>
       <c r="B65" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8122,7 +8117,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -8132,13 +8127,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635679</v>
+        <v>635737</v>
       </c>
       <c r="R65" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8167,7 +8162,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8177,7 +8172,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8192,12 +8192,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133383847</v>
+        <v>133381488</v>
       </c>
       <c r="B2" t="n">
-        <v>92228</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635762</v>
+        <v>635681</v>
       </c>
       <c r="R2" t="n">
-        <v>6998643</v>
+        <v>6998653</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,69 +767,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133381488</v>
+        <v>133383847</v>
       </c>
       <c r="B3" t="n">
-        <v>91920</v>
+        <v>92228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635681</v>
+        <v>635762</v>
       </c>
       <c r="R3" t="n">
-        <v>6998653</v>
+        <v>6998643</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,70 +890,62 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381481</v>
+        <v>133383841</v>
       </c>
       <c r="B4" t="n">
-        <v>98043</v>
+        <v>99178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635587</v>
+        <v>635692</v>
       </c>
       <c r="R4" t="n">
-        <v>6998640</v>
+        <v>6998659</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,49 +1016,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381485</v>
+        <v>133381481</v>
       </c>
       <c r="B5" t="n">
-        <v>91957</v>
+        <v>98043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635571</v>
+        <v>635587</v>
       </c>
       <c r="R5" t="n">
-        <v>6998656</v>
+        <v>6998640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,21 +1124,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1146,32 +1140,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381486</v>
+        <v>133381485</v>
       </c>
       <c r="B6" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635569</v>
+        <v>635571</v>
       </c>
       <c r="R6" t="n">
-        <v>6998651</v>
+        <v>6998656</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,46 +1266,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133383841</v>
+        <v>133381486</v>
       </c>
       <c r="B7" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635692</v>
+        <v>635569</v>
       </c>
       <c r="R7" t="n">
-        <v>6998659</v>
+        <v>6998651</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1362,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1865,32 +1865,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133383857</v>
+        <v>133381503</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>57162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635848</v>
+        <v>635782</v>
       </c>
       <c r="R12" t="n">
-        <v>6998513</v>
+        <v>6998397</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,44 +1968,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133381503</v>
+        <v>133383857</v>
       </c>
       <c r="B13" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635782</v>
+        <v>635848</v>
       </c>
       <c r="R13" t="n">
-        <v>6998397</v>
+        <v>6998513</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,12 +2083,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133383871</v>
+        <v>133381498</v>
       </c>
       <c r="B29" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3837,40 +3837,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635666</v>
+        <v>635811</v>
       </c>
       <c r="R29" t="n">
-        <v>6998564</v>
+        <v>6998569</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3899,7 +3904,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3909,7 +3914,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3918,82 +3928,74 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133383848</v>
+        <v>133381479</v>
       </c>
       <c r="B30" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635765</v>
+        <v>635609</v>
       </c>
       <c r="R30" t="n">
-        <v>6998624</v>
+        <v>6998605</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4022,7 +4024,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4032,7 +4034,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4047,19 +4049,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133383835</v>
+        <v>133383871</v>
       </c>
       <c r="B31" t="n">
         <v>79358</v>
@@ -4097,10 +4099,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635674</v>
+        <v>635666</v>
       </c>
       <c r="R31" t="n">
-        <v>6998672</v>
+        <v>6998564</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4132,7 +4134,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4142,7 +4144,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4157,17 +4159,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4185,10 +4187,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133383869</v>
+        <v>133383848</v>
       </c>
       <c r="B32" t="n">
-        <v>56539</v>
+        <v>91957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4196,42 +4198,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635723</v>
+        <v>635765</v>
       </c>
       <c r="R32" t="n">
-        <v>6998486</v>
+        <v>6998624</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4263,7 +4257,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4273,7 +4267,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4300,10 +4294,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133381498</v>
+        <v>133383835</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,45 +4305,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635811</v>
+        <v>635674</v>
       </c>
       <c r="R33" t="n">
-        <v>6998569</v>
+        <v>6998672</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4378,7 +4367,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,12 +4377,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4402,45 +4386,61 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133381479</v>
+        <v>133383869</v>
       </c>
       <c r="B34" t="n">
-        <v>57162</v>
+        <v>56539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635609</v>
+        <v>635723</v>
       </c>
       <c r="R34" t="n">
-        <v>6998605</v>
+        <v>6998486</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,60 +4523,68 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133383831</v>
+        <v>133381477</v>
       </c>
       <c r="B35" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635587</v>
+        <v>635611</v>
       </c>
       <c r="R35" t="n">
-        <v>6998661</v>
+        <v>6998529</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4605,7 +4613,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4623,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,54 +4638,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133381477</v>
+        <v>133381504</v>
       </c>
       <c r="B36" t="n">
-        <v>57162</v>
+        <v>79358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4685,10 +4688,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635611</v>
+        <v>635773</v>
       </c>
       <c r="R36" t="n">
-        <v>6998529</v>
+        <v>6998405</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4720,7 +4723,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4730,7 +4733,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4739,8 +4742,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4757,7 +4776,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133381504</v>
+        <v>133381496</v>
       </c>
       <c r="B37" t="n">
         <v>79358</v>
@@ -4795,10 +4814,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>635773</v>
+        <v>635761</v>
       </c>
       <c r="R37" t="n">
-        <v>6998405</v>
+        <v>6998603</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4830,7 +4849,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4840,7 +4859,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,17 +4874,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4883,10 +4902,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133381496</v>
+        <v>133383831</v>
       </c>
       <c r="B38" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4894,40 +4913,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635761</v>
+        <v>635587</v>
       </c>
       <c r="R38" t="n">
-        <v>6998603</v>
+        <v>6998661</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4956,7 +4972,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4966,7 +4982,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4975,34 +4991,18 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5116,48 +5116,51 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383873</v>
+        <v>133381502</v>
       </c>
       <c r="B40" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635593</v>
+        <v>635781</v>
       </c>
       <c r="R40" t="n">
-        <v>6998584</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5186,7 +5189,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5196,7 +5199,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5205,69 +5208,82 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133381502</v>
+        <v>133383873</v>
       </c>
       <c r="B41" t="n">
-        <v>91957</v>
+        <v>91920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635781</v>
+        <v>635593</v>
       </c>
       <c r="R41" t="n">
-        <v>6998384</v>
+        <v>6998584</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5296,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5306,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,41 +5331,25 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381512</v>
+        <v>133383867</v>
       </c>
       <c r="B42" t="n">
         <v>57162</v>
@@ -5382,7 +5382,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635708</v>
+        <v>635701</v>
       </c>
       <c r="R42" t="n">
-        <v>6998578</v>
+        <v>6998483</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5457,49 +5457,54 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381489</v>
+        <v>133381512</v>
       </c>
       <c r="B43" t="n">
-        <v>92228</v>
+        <v>57162</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5507,10 +5512,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635687</v>
+        <v>635708</v>
       </c>
       <c r="R43" t="n">
-        <v>6998661</v>
+        <v>6998578</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5542,7 +5547,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5552,7 +5557,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5561,24 +5571,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5595,42 +5589,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381478</v>
+        <v>133381489</v>
       </c>
       <c r="B44" t="n">
-        <v>57162</v>
+        <v>92228</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5638,10 +5627,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635628</v>
+        <v>635687</v>
       </c>
       <c r="R44" t="n">
-        <v>6998554</v>
+        <v>6998661</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5673,7 +5662,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,7 +5672,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5692,8 +5681,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5710,7 +5715,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133383867</v>
+        <v>133381478</v>
       </c>
       <c r="B45" t="n">
         <v>57162</v>
@@ -5743,7 +5748,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5753,13 +5758,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635701</v>
+        <v>635628</v>
       </c>
       <c r="R45" t="n">
-        <v>6998483</v>
+        <v>6998554</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5798,12 +5803,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,12 +5818,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6552,7 +6552,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133383836</v>
+        <v>133383824</v>
       </c>
       <c r="B52" t="n">
         <v>79358</v>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635678</v>
+        <v>635647</v>
       </c>
       <c r="R52" t="n">
-        <v>6998668</v>
+        <v>6998562</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6678,10 +6678,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133383846</v>
+        <v>133383828</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6689,45 +6689,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635727</v>
+        <v>635586</v>
       </c>
       <c r="R53" t="n">
-        <v>6998685</v>
+        <v>6998633</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6756,7 +6748,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6766,12 +6758,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6798,7 +6785,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133383824</v>
+        <v>133383836</v>
       </c>
       <c r="B54" t="n">
         <v>79358</v>
@@ -6836,10 +6823,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635647</v>
+        <v>635678</v>
       </c>
       <c r="R54" t="n">
-        <v>6998562</v>
+        <v>6998668</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6871,7 +6858,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6881,7 +6868,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6924,10 +6911,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133383828</v>
+        <v>133383846</v>
       </c>
       <c r="B55" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6935,37 +6922,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635586</v>
+        <v>635727</v>
       </c>
       <c r="R55" t="n">
-        <v>6998633</v>
+        <v>6998685</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6994,7 +6989,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7004,7 +6999,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7138,10 +7138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133383863</v>
+        <v>133381482</v>
       </c>
       <c r="B57" t="n">
-        <v>79358</v>
+        <v>56539</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,26 +7149,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7176,13 +7181,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635750</v>
+        <v>635585</v>
       </c>
       <c r="R57" t="n">
-        <v>6998423</v>
+        <v>6998647</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7211,7 +7216,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7221,7 +7226,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7230,76 +7235,64 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133383860</v>
+        <v>133381487</v>
       </c>
       <c r="B58" t="n">
-        <v>57975</v>
+        <v>99178</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7307,13 +7300,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>635875</v>
+        <v>635566</v>
       </c>
       <c r="R58" t="n">
-        <v>6998347</v>
+        <v>6998671</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,7 +7335,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7352,12 +7345,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7366,64 +7354,61 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133381487</v>
+        <v>133381508</v>
       </c>
       <c r="B59" t="n">
-        <v>99178</v>
+        <v>57162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7431,10 +7416,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>635566</v>
+        <v>635708</v>
       </c>
       <c r="R59" t="n">
-        <v>6998671</v>
+        <v>6998507</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7466,7 +7451,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7476,7 +7461,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7485,7 +7470,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7504,42 +7488,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133381508</v>
+        <v>133383863</v>
       </c>
       <c r="B60" t="n">
-        <v>57162</v>
+        <v>79358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7547,13 +7526,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>635708</v>
+        <v>635750</v>
       </c>
       <c r="R60" t="n">
-        <v>6998507</v>
+        <v>6998423</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7582,7 +7561,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7592,7 +7571,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7601,28 +7580,44 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133381482</v>
+        <v>133383860</v>
       </c>
       <c r="B61" t="n">
-        <v>56539</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7630,21 +7625,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7652,7 +7647,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7662,13 +7657,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>635585</v>
+        <v>635875</v>
       </c>
       <c r="R61" t="n">
-        <v>6998647</v>
+        <v>6998347</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7697,7 +7692,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7707,7 +7702,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7722,54 +7722,58 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133381495</v>
+        <v>133383829</v>
       </c>
       <c r="B62" t="n">
-        <v>57972</v>
+        <v>99178</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7777,13 +7781,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>635759</v>
+        <v>635584</v>
       </c>
       <c r="R62" t="n">
-        <v>6998610</v>
+        <v>6998640</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7812,7 +7816,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7822,7 +7826,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7831,50 +7835,51 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133381492</v>
+        <v>133383849</v>
       </c>
       <c r="B63" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7882,7 +7887,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7892,13 +7897,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>635679</v>
+        <v>635737</v>
       </c>
       <c r="R63" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7927,7 +7932,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7937,7 +7942,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7952,58 +7962,54 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133383829</v>
+        <v>133381495</v>
       </c>
       <c r="B64" t="n">
-        <v>99178</v>
+        <v>57972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8011,13 +8017,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>635584</v>
+        <v>635759</v>
       </c>
       <c r="R64" t="n">
-        <v>6998640</v>
+        <v>6998610</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8046,7 +8052,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8056,7 +8062,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8065,51 +8071,50 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133383849</v>
+        <v>133381492</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8117,7 +8122,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -8127,13 +8132,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>635737</v>
+        <v>635679</v>
       </c>
       <c r="R65" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8162,7 +8167,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8172,12 +8177,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8192,12 +8192,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8557,48 +8557,56 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133383843</v>
+        <v>133381515</v>
       </c>
       <c r="B69" t="n">
-        <v>91920</v>
+        <v>57153</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635701</v>
+        <v>635614</v>
       </c>
       <c r="R69" t="n">
-        <v>6998689</v>
+        <v>6998564</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8627,7 +8635,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8637,7 +8645,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8652,22 +8660,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133381515</v>
+        <v>133381513</v>
       </c>
       <c r="B70" t="n">
-        <v>57153</v>
+        <v>79358</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8675,31 +8683,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8707,13 +8710,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635614</v>
+        <v>635632</v>
       </c>
       <c r="R70" t="n">
-        <v>6998564</v>
+        <v>6998603</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8742,7 +8745,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8752,7 +8755,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8761,8 +8764,24 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8779,51 +8798,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133381513</v>
+        <v>133383843</v>
       </c>
       <c r="B71" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635632</v>
+        <v>635701</v>
       </c>
       <c r="R71" t="n">
-        <v>6998603</v>
+        <v>6998689</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8852,7 +8868,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8862,7 +8878,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8871,34 +8887,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -908,44 +908,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133383841</v>
+        <v>133381481</v>
       </c>
       <c r="B4" t="n">
-        <v>99178</v>
+        <v>98043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -955,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635692</v>
+        <v>635587</v>
       </c>
       <c r="R4" t="n">
-        <v>6998659</v>
+        <v>6998640</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,50 +1008,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381481</v>
+        <v>133381485</v>
       </c>
       <c r="B5" t="n">
-        <v>98043</v>
+        <v>91957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635587</v>
+        <v>635571</v>
       </c>
       <c r="R5" t="n">
-        <v>6998640</v>
+        <v>6998656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,6 +1115,21 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1140,32 +1146,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381485</v>
+        <v>133381486</v>
       </c>
       <c r="B6" t="n">
-        <v>91957</v>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635571</v>
+        <v>635569</v>
       </c>
       <c r="R6" t="n">
-        <v>6998656</v>
+        <v>6998651</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,37 +1272,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133381486</v>
+        <v>133383841</v>
       </c>
       <c r="B7" t="n">
-        <v>91920</v>
+        <v>99178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635569</v>
+        <v>635692</v>
       </c>
       <c r="R7" t="n">
-        <v>6998651</v>
+        <v>6998659</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,30 +1377,15 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133383823</v>
+        <v>133381480</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,31 +2547,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2579,13 +2574,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635652</v>
+        <v>635598</v>
       </c>
       <c r="R18" t="n">
-        <v>6998555</v>
+        <v>6998614</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,28 +2628,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133381480</v>
+        <v>133381501</v>
       </c>
       <c r="B19" t="n">
-        <v>91957</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,37 +2673,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rågsvedberget, Ång</t>
+          <t>Rågsvedsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635598</v>
+        <v>635890</v>
       </c>
       <c r="R19" t="n">
-        <v>6998614</v>
+        <v>6998459</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2724,7 +2740,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2750,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,24 +2759,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2777,10 +2777,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133381501</v>
+        <v>133381505</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,42 +2788,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rågsvedsberget, Ång</t>
+          <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635890</v>
+        <v>635742</v>
       </c>
       <c r="R20" t="n">
-        <v>6998459</v>
+        <v>6998412</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2855,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2874,8 +2869,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2892,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133381505</v>
+        <v>133381493</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,21 +2914,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2930,10 +2941,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635742</v>
+        <v>635756</v>
       </c>
       <c r="R21" t="n">
-        <v>6998412</v>
+        <v>6998647</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2965,7 +2976,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2975,7 +2986,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,17 +3001,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3018,10 +3029,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133381493</v>
+        <v>133383823</v>
       </c>
       <c r="B22" t="n">
-        <v>91957</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,26 +3040,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3056,13 +3072,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635756</v>
+        <v>635652</v>
       </c>
       <c r="R22" t="n">
-        <v>6998647</v>
+        <v>6998555</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3091,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,44 +3126,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133381506</v>
+        <v>133383854</v>
       </c>
       <c r="B23" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,26 +3155,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3182,13 +3187,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635731</v>
+        <v>635783</v>
       </c>
       <c r="R23" t="n">
-        <v>6998450</v>
+        <v>6998545</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3217,7 +3222,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3227,7 +3232,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,44 +3241,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133383854</v>
+        <v>133383837</v>
       </c>
       <c r="B24" t="n">
-        <v>57972</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,42 +3270,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635783</v>
+        <v>635681</v>
       </c>
       <c r="R24" t="n">
-        <v>6998545</v>
+        <v>6998667</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3348,7 +3329,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3358,7 +3339,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3385,10 +3366,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133383837</v>
+        <v>133383845</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,37 +3377,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635681</v>
+        <v>635723</v>
       </c>
       <c r="R25" t="n">
-        <v>6998667</v>
+        <v>6998687</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3455,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3465,7 +3454,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3492,56 +3486,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133383845</v>
+        <v>133383859</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>91920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635723</v>
+        <v>635892</v>
       </c>
       <c r="R26" t="n">
-        <v>6998687</v>
+        <v>6998470</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3570,7 +3556,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3580,12 +3566,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3612,7 +3593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133383859</v>
+        <v>133383862</v>
       </c>
       <c r="B27" t="n">
         <v>91920</v>
@@ -3647,10 +3628,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635892</v>
+        <v>635771</v>
       </c>
       <c r="R27" t="n">
-        <v>6998470</v>
+        <v>6998407</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3682,7 +3663,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3692,7 +3673,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3719,48 +3700,51 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133383862</v>
+        <v>133381506</v>
       </c>
       <c r="B28" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635771</v>
+        <v>635731</v>
       </c>
       <c r="R28" t="n">
-        <v>6998407</v>
+        <v>6998450</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3789,7 +3773,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3799,7 +3783,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3808,18 +3792,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>92228</v>
+        <v>91957</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,37 +5020,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R39" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5089,7 +5092,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5098,28 +5101,44 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5127,40 +5146,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5208,34 +5224,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133383867</v>
+        <v>133381512</v>
       </c>
       <c r="B42" t="n">
         <v>57162</v>
@@ -5382,7 +5382,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635701</v>
+        <v>635708</v>
       </c>
       <c r="R42" t="n">
-        <v>6998483</v>
+        <v>6998578</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5457,54 +5457,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381512</v>
+        <v>133381489</v>
       </c>
       <c r="B43" t="n">
-        <v>57162</v>
+        <v>92228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5512,10 +5507,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635708</v>
+        <v>635687</v>
       </c>
       <c r="R43" t="n">
-        <v>6998578</v>
+        <v>6998661</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5547,7 +5542,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5557,12 +5552,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5571,8 +5561,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5589,37 +5595,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381489</v>
+        <v>133381478</v>
       </c>
       <c r="B44" t="n">
-        <v>92228</v>
+        <v>57162</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5627,10 +5638,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635687</v>
+        <v>635628</v>
       </c>
       <c r="R44" t="n">
-        <v>6998661</v>
+        <v>6998554</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5662,7 +5673,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5672,7 +5683,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5681,24 +5692,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5715,7 +5710,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133381478</v>
+        <v>133383867</v>
       </c>
       <c r="B45" t="n">
         <v>57162</v>
@@ -5748,7 +5743,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5758,13 +5753,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635628</v>
+        <v>635701</v>
       </c>
       <c r="R45" t="n">
-        <v>6998554</v>
+        <v>6998483</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5803,7 +5798,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,12 +5818,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -5009,10 +5009,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B39" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,40 +5020,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R39" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5082,7 +5079,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5092,7 +5089,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5101,44 +5098,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B40" t="n">
-        <v>92228</v>
+        <v>91957</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5146,37 +5127,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5205,7 +5189,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5215,7 +5199,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5224,18 +5208,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133381512</v>
+        <v>133383867</v>
       </c>
       <c r="B42" t="n">
         <v>57162</v>
@@ -5382,7 +5382,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>övernattning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635708</v>
+        <v>635701</v>
       </c>
       <c r="R42" t="n">
-        <v>6998578</v>
+        <v>6998483</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillning.</t>
+          <t>Tarmtömning bredvid smal tall intill myr.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5457,49 +5457,54 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133381489</v>
+        <v>133381512</v>
       </c>
       <c r="B43" t="n">
-        <v>92228</v>
+        <v>57162</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5507,10 +5512,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635687</v>
+        <v>635708</v>
       </c>
       <c r="R43" t="n">
-        <v>6998661</v>
+        <v>6998578</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5542,7 +5547,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5552,7 +5557,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5561,24 +5571,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5595,42 +5589,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133381478</v>
+        <v>133381489</v>
       </c>
       <c r="B44" t="n">
-        <v>57162</v>
+        <v>92228</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5638,10 +5627,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635628</v>
+        <v>635687</v>
       </c>
       <c r="R44" t="n">
-        <v>6998554</v>
+        <v>6998661</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5673,7 +5662,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5683,7 +5672,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5692,8 +5681,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5710,7 +5715,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133383867</v>
+        <v>133381478</v>
       </c>
       <c r="B45" t="n">
         <v>57162</v>
@@ -5743,7 +5748,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>övernattning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5753,13 +5758,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635701</v>
+        <v>635628</v>
       </c>
       <c r="R45" t="n">
-        <v>6998483</v>
+        <v>6998554</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5798,12 +5803,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tarmtömning bredvid smal tall intill myr.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,12 +5818,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -8557,56 +8557,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133381515</v>
+        <v>133383843</v>
       </c>
       <c r="B69" t="n">
-        <v>57153</v>
+        <v>91920</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>635614</v>
+        <v>635701</v>
       </c>
       <c r="R69" t="n">
-        <v>6998564</v>
+        <v>6998689</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8635,7 +8627,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8645,7 +8637,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8660,22 +8652,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133381513</v>
+        <v>133381515</v>
       </c>
       <c r="B70" t="n">
-        <v>79358</v>
+        <v>57153</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8683,26 +8675,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8710,13 +8707,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>635632</v>
+        <v>635614</v>
       </c>
       <c r="R70" t="n">
-        <v>6998603</v>
+        <v>6998564</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8745,7 +8742,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8755,7 +8752,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8764,24 +8761,8 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8798,48 +8779,51 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133383843</v>
+        <v>133381513</v>
       </c>
       <c r="B71" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>635701</v>
+        <v>635632</v>
       </c>
       <c r="R71" t="n">
-        <v>6998689</v>
+        <v>6998603</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8868,7 +8852,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8878,7 +8862,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8887,18 +8871,34 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 42290-2025 artfynd.xlsx
+++ b/artfynd/A 42290-2025 artfynd.xlsx
@@ -908,36 +908,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133381481</v>
+        <v>133383841</v>
       </c>
       <c r="B4" t="n">
-        <v>98043</v>
+        <v>99178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635587</v>
+        <v>635692</v>
       </c>
       <c r="R4" t="n">
-        <v>6998640</v>
+        <v>6998659</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,49 +1016,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133381485</v>
+        <v>133381481</v>
       </c>
       <c r="B5" t="n">
-        <v>91957</v>
+        <v>98043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635571</v>
+        <v>635587</v>
       </c>
       <c r="R5" t="n">
-        <v>6998656</v>
+        <v>6998640</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,21 +1124,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1146,32 +1140,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133381486</v>
+        <v>133381485</v>
       </c>
       <c r="B6" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635569</v>
+        <v>635571</v>
       </c>
       <c r="R6" t="n">
-        <v>6998651</v>
+        <v>6998656</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,46 +1266,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133383841</v>
+        <v>133381486</v>
       </c>
       <c r="B7" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635692</v>
+        <v>635569</v>
       </c>
       <c r="R7" t="n">
-        <v>6998659</v>
+        <v>6998651</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1362,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133383832</v>
+        <v>133381502</v>
       </c>
       <c r="B39" t="n">
-        <v>92228</v>
+        <v>91957</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5020,37 +5020,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635589</v>
+        <v>635781</v>
       </c>
       <c r="R39" t="n">
-        <v>6998667</v>
+        <v>6998384</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5079,7 +5082,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5089,7 +5092,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5098,28 +5101,44 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133381502</v>
+        <v>133383832</v>
       </c>
       <c r="B40" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5127,40 +5146,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågsvedberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635781</v>
+        <v>635589</v>
       </c>
       <c r="R40" t="n">
-        <v>6998384</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5199,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5208,34 +5224,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6082,42 +6082,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133381509</v>
+        <v>133383830</v>
       </c>
       <c r="B48" t="n">
-        <v>57162</v>
+        <v>99178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6125,13 +6129,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635725</v>
+        <v>635569</v>
       </c>
       <c r="R48" t="n">
-        <v>6998515</v>
+        <v>6998652</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6160,7 +6164,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6179,25 +6183,26 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133381491</v>
+        <v>133381509</v>
       </c>
       <c r="B49" t="n">
         <v>57162</v>
@@ -6230,7 +6235,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6240,10 +6245,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635695</v>
+        <v>635725</v>
       </c>
       <c r="R49" t="n">
-        <v>6998652</v>
+        <v>6998515</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6275,7 +6280,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6285,7 +6290,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6312,46 +6317,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133383830</v>
+        <v>133381491</v>
       </c>
       <c r="B50" t="n">
-        <v>99178</v>
+        <v>57162</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6359,13 +6360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635569</v>
+        <v>635695</v>
       </c>
       <c r="R50" t="n">
         <v>6998652</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6394,7 +6395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6404,7 +6405,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6413,19 +6414,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
